--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41968A88-5B3A-414A-BA64-97E03FA8C117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061C58E5-4324-47A7-AB18-015CEE7C4F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="549">
   <si>
     <t>Study_ID</t>
   </si>
@@ -748,9 +748,6 @@
   </si>
   <si>
     <t>K-SADS composite</t>
-  </si>
-  <si>
-    <t>raw (imputed)</t>
   </si>
   <si>
     <t>K-SADS 16-item composite (study-specific 4-point averaged scale); MI imputed means (20 datasets, Rubin's rules); N reported = randomized N per Table 1 note.</t>
@@ -1352,14 +1349,6 @@
   </si>
   <si>
     <t>CI_upper_ctrl</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>reported_d_exp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>reported_d_ctrl</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2091,6 +2080,22 @@
   </si>
   <si>
     <t xml:space="preserve">  - With follow-up data                             </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">raw </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>raw</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>change_mean_exp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>change_mean_ctrl</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2611,16 +2616,16 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>17</v>
@@ -2629,10 +2634,10 @@
         <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
@@ -2676,7 +2681,7 @@
         <v>15.63</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>28</v>
@@ -2706,7 +2711,7 @@
         <v>36</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>37</v>
@@ -2747,7 +2752,7 @@
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>44</v>
@@ -2765,7 +2770,7 @@
         <v>48</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>49</v>
@@ -2777,7 +2782,7 @@
         <v>50</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>37</v>
@@ -2786,7 +2791,7 @@
         <v>51</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
@@ -2815,10 +2820,10 @@
         <v>55</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>56</v>
@@ -2857,7 +2862,7 @@
         <v>65</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="61.2" customHeight="1">
@@ -2889,7 +2894,7 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>69</v>
@@ -2925,7 +2930,7 @@
         <v>74</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>75</v>
@@ -2960,7 +2965,7 @@
         <v>14.63</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>44</v>
@@ -3342,7 +3347,7 @@
         <v>63</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AA11" s="2" t="s">
         <v>37</v>
@@ -3365,7 +3370,7 @@
         <v>2018</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>137</v>
@@ -3380,7 +3385,7 @@
         <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J12" s="2">
         <v>58.6</v>
@@ -3436,7 +3441,7 @@
         <v>2015</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>147</v>
@@ -3451,10 +3456,10 @@
         <v>26</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>44</v>
@@ -3472,7 +3477,7 @@
         <v>60</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>151</v>
@@ -3484,7 +3489,7 @@
         <v>63</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AA13" s="2" t="s">
         <v>37</v>
@@ -3501,7 +3506,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C14" s="2">
         <v>2014</v>
@@ -3555,13 +3560,13 @@
         <v>63</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AC14" s="2" t="s">
         <v>159</v>
@@ -3572,7 +3577,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C15" s="2">
         <v>2020</v>
@@ -3626,7 +3631,7 @@
         <v>63</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AA15" s="2" t="s">
         <v>37</v>
@@ -3652,7 +3657,7 @@
         <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F16" s="2">
         <v>128</v>
@@ -3673,7 +3678,7 @@
         <v>169</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>170</v>
@@ -3697,7 +3702,7 @@
         <v>50</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AA16" s="2" t="s">
         <v>37</v>
@@ -3706,7 +3711,7 @@
         <v>173</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -3714,16 +3719,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C17" s="2">
         <v>1998</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N17" s="10"/>
     </row>
@@ -3831,43 +3836,43 @@
         <v>188</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>405</v>
+        <v>547</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>406</v>
+        <v>548</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -3895,32 +3900,20 @@
       <c r="G2" s="2">
         <v>45.99</v>
       </c>
-      <c r="H2" s="2">
-        <v>10.52</v>
-      </c>
       <c r="I2" s="2">
         <v>45.12</v>
       </c>
-      <c r="J2" s="2">
-        <v>12.2</v>
-      </c>
       <c r="K2" s="2">
         <v>36.090000000000003</v>
       </c>
-      <c r="L2" s="2">
-        <v>18.66</v>
-      </c>
       <c r="M2" s="2">
         <v>38.99</v>
       </c>
-      <c r="N2" s="2">
-        <v>16.899999999999999</v>
-      </c>
       <c r="O2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>191</v>
@@ -3969,35 +3962,23 @@
       <c r="G3" s="2">
         <v>45.99</v>
       </c>
-      <c r="H3" s="2">
-        <v>10.52</v>
-      </c>
       <c r="I3" s="2">
         <v>45.12</v>
       </c>
-      <c r="J3" s="2">
-        <v>12.2</v>
-      </c>
       <c r="K3" s="2">
         <v>35.21</v>
       </c>
-      <c r="L3" s="2">
-        <v>20.74</v>
-      </c>
       <c r="M3" s="2">
         <v>35.86</v>
       </c>
-      <c r="N3" s="2">
-        <v>19.21</v>
-      </c>
       <c r="O3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4323,41 +4304,29 @@
       <c r="G9" s="2">
         <v>39.6</v>
       </c>
-      <c r="H9" s="2">
-        <v>9.1999999999999993</v>
-      </c>
       <c r="I9" s="2">
         <v>39.5</v>
       </c>
-      <c r="J9" s="2">
-        <v>8.9</v>
-      </c>
       <c r="K9" s="2">
         <v>24.9</v>
       </c>
-      <c r="L9" s="2">
-        <v>8.7899999999999991</v>
-      </c>
       <c r="M9" s="2">
         <v>38.4</v>
       </c>
-      <c r="N9" s="2">
-        <v>8.8000000000000007</v>
-      </c>
       <c r="O9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="R9" s="2">
+        <v>-18.600000000000001</v>
+      </c>
+      <c r="S9" s="2">
         <v>-10.7</v>
-      </c>
-      <c r="S9" s="2">
-        <v>-18.600000000000001</v>
       </c>
       <c r="T9" s="2">
         <v>-6.3</v>
@@ -4819,15 +4788,6 @@
       <c r="Q17" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="X17" s="2">
-        <v>-0.56999999999999995</v>
-      </c>
-      <c r="Y17" s="2">
-        <v>-0.12</v>
-      </c>
-      <c r="Z17" s="2">
-        <v>-0.35</v>
-      </c>
       <c r="AE17" s="2" t="s">
         <v>219</v>
       </c>
@@ -4879,19 +4839,19 @@
         <v>123</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="X18" s="2">
-        <v>-0.45</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="Y18" s="2">
-        <v>0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="Z18" s="2">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="AE18" s="2" t="s">
         <v>222</v>
@@ -4944,10 +4904,19 @@
         <v>123</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
+      </c>
+      <c r="X19" s="2">
+        <v>-0.45</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>-0.2</v>
       </c>
       <c r="AE19" s="2" t="s">
         <v>222</v>
@@ -5221,7 +5190,7 @@
         <v>11.9</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>196</v>
@@ -5274,7 +5243,7 @@
         <v>11</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>196</v>
@@ -5604,13 +5573,13 @@
         <v>234</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>235</v>
+        <v>545</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>196</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5660,13 +5629,13 @@
         <v>234</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>235</v>
+        <v>545</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>196</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -5716,13 +5685,13 @@
         <v>234</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>235</v>
+        <v>546</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>196</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="30.6">
@@ -5733,7 +5702,7 @@
         <v>233</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D34" s="2">
         <v>18</v>
@@ -5772,13 +5741,13 @@
         <v>234</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>235</v>
+        <v>545</v>
       </c>
       <c r="Q34" s="2" t="s">
         <v>196</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="30.6">
@@ -5828,13 +5797,13 @@
         <v>234</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>235</v>
+        <v>546</v>
       </c>
       <c r="Q35" s="2" t="s">
         <v>196</v>
       </c>
       <c r="AE35" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -5869,46 +5838,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -5916,43 +5885,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -5960,43 +5929,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6004,43 +5973,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6048,43 +6017,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6092,43 +6061,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6136,43 +6105,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="M7" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="132.6" customHeight="1">
@@ -6180,43 +6149,43 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="153" customHeight="1">
@@ -6224,43 +6193,43 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="132.6" customHeight="1">
@@ -6268,43 +6237,43 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="102" customHeight="1">
@@ -6312,43 +6281,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6356,43 +6325,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="173.4" customHeight="1">
@@ -6400,43 +6369,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="91.8" customHeight="1">
@@ -6444,43 +6413,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="51" customHeight="1">
@@ -6488,43 +6457,43 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="163.19999999999999">
@@ -6532,43 +6501,43 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -6590,19 +6559,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>239</v>
-      </c>
       <c r="C1" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6610,16 +6579,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6627,19 +6596,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6647,16 +6616,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6664,16 +6633,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6681,19 +6650,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>513</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6701,16 +6670,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6718,16 +6687,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6735,16 +6704,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6752,16 +6721,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6769,16 +6738,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6786,16 +6755,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6803,16 +6772,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6820,16 +6789,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>452</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6837,16 +6806,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6854,16 +6823,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6871,16 +6840,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6888,16 +6857,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6905,16 +6874,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6922,16 +6891,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6939,16 +6908,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6956,16 +6925,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6973,16 +6942,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6990,16 +6959,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7007,16 +6976,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7024,16 +6993,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7041,16 +7010,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7058,16 +7027,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7078,114 +7047,114 @@
     </row>
     <row r="31" spans="1:5">
       <c r="D31" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="D32" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -7205,20 +7174,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7226,7 +7195,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7234,7 +7203,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7242,7 +7211,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7250,7 +7219,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7258,7 +7227,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7266,7 +7235,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B13" s="4">
         <v>27</v>
@@ -7274,7 +7243,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7282,7 +7251,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7290,7 +7259,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7298,7 +7267,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7306,7 +7275,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7314,7 +7283,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B19" s="4">
         <v>2</v>
@@ -7322,7 +7291,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7330,7 +7299,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7338,7 +7307,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7346,7 +7315,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7354,7 +7323,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7362,7 +7331,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7370,7 +7339,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7378,15 +7347,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7394,7 +7363,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061C58E5-4324-47A7-AB18-015CEE7C4F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02494DD2-F241-49E9-8208-D8A762F8065C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15312" yWindow="0" windowWidth="15408" windowHeight="18480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="556">
   <si>
     <t>Study_ID</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>ba+cr+rx+3w</t>
-  </si>
-  <si>
-    <t>TAU</t>
   </si>
   <si>
     <t>Tech</t>
@@ -184,9 +181,6 @@
     <t>cr+ps+hw+rp+rx</t>
   </si>
   <si>
-    <t>Assessment-only</t>
-  </si>
-  <si>
     <t>24/7 access (bibliotherapy)</t>
   </si>
   <si>
@@ -220,9 +214,6 @@
     <t>cr+ba+ps+rx</t>
   </si>
   <si>
-    <t>WL</t>
-  </si>
-  <si>
     <t>Human</t>
   </si>
   <si>
@@ -341,30 +332,6 @@
   </si>
   <si>
     <t>239 randomized→161 retained (CES-D≥16 re-screen); EM imputation; differential attrition (χ²=5.30,p=.02)</t>
-  </si>
-  <si>
-    <t>Merry et al.</t>
-  </si>
-  <si>
-    <t>12-19</t>
-  </si>
-  <si>
-    <t>Clinical (primary care)</t>
-  </si>
-  <si>
-    <t>PHQ-9 10-19; CDRS-R≥30; no high self-harm risk</t>
-  </si>
-  <si>
-    <t>cr+ba+ps+rx+pe+ist+rp+hw+3w</t>
-  </si>
-  <si>
-    <t>7 modules/4-7 weeks</t>
-  </si>
-  <si>
-    <t>NZ Ministry of Health</t>
-  </si>
-  <si>
-    <t>Non-inferiority trial; TAU=counselling (mean 4.8 sessions); 13.3% TAU waitlisted; ITT+MI</t>
   </si>
   <si>
     <t>O'Dea et al.</t>
@@ -440,9 +407,6 @@
     <t>Girls had to score at or above the 70th percentile on depressive symptoms within the sample (RADS-2 score ≥ 59)</t>
   </si>
   <si>
-    <t>WL (active monitoring)</t>
-  </si>
-  <si>
     <t>7 levels, ~20–40 min/level, 7 weeks</t>
   </si>
   <si>
@@ -473,9 +437,6 @@
     <t>Text</t>
   </si>
   <si>
-    <t>Mild-to-Moderate</t>
-  </si>
-  <si>
     <t>National Institute of Mental Health grants K23 MH095866, K24 HD062645, and K24DA027109</t>
   </si>
   <si>
@@ -684,18 +645,6 @@
   </si>
   <si>
     <t>EM imputed (Table 5); p=.059</t>
-  </si>
-  <si>
-    <t>Merry 2012</t>
-  </si>
-  <si>
-    <t>ITT+MI (Table 2); clinician-rated; blinded RAs</t>
-  </si>
-  <si>
-    <t>fu_5mo</t>
-  </si>
-  <si>
-    <t>3mo post-intervention = 5mo from baseline; Table 2 ITT</t>
   </si>
   <si>
     <t>O'Dea 2020</t>
@@ -813,9 +762,6 @@
     <t>Randomization process: Computer-generated randomization was conducted by an independent researcher with no ongoing involvement in the trial. Minimisation was used to balance four prognostic factors across groups.
 Allocation concealment: Allocation appears to have been concealed from clinical staff involved in recruitment/treatment, although the exact mechanism was not fully described.
 Baseline balance: Baseline characteristics appeared balanced across groups, with no important imbalances reported for baseline scores or key prognostic factors.</t>
-  </si>
-  <si>
-    <t>Some</t>
   </si>
   <si>
     <t xml:space="preserve">Blinding: Participants unblinded due to app vs waitlist design; without active control.
@@ -944,9 +890,6 @@
     <t>Only D2 raises concern due to unblinded participants in open-label design</t>
   </si>
   <si>
-    <t>Markarushka, 2012</t>
-  </si>
-  <si>
     <t>Randomization process: 239 randomly assigned to 2 conditions; method of sequence generation not described.
 Allocation concealment: Not described.
 Baseline balance: No significant differences on any baseline demographics or outcomes.
@@ -969,35 +912,8 @@
     <t>No pre-registration (dissertation, 2012; pre-registration not yet standard). Multiple outcomes reported (CES-D, knowledge, ATQ, BADS, school functioning, self-efficacy). CES-D at follow-up was non-significant (p=.059) but reported transparently with effect size.</t>
   </si>
   <si>
-    <t>Some concerns across D1 (sequence generation and allocation concealment not described; post-randomization exclusion), D2 (unblinded, no active control), D3 (differential attrition, though handled with EM imputation), and D5 (no pre-registration). D4 low risk (computer-based self-report). No single domain reaches High risk.</t>
-  </si>
-  <si>
-    <t>Merry et al., 2012</t>
-  </si>
-  <si>
-    <t>Randomization process: Computer-generated sequence, stratified by site, permuted blocks of 4.
-Allocation concealment: Opaque sealed envelopes stored off-site, opened by local investigator after eligibility confirmed.
-Baseline balance: Comparable groups on demographics and baseline measures (Table 1).</t>
-  </si>
-  <si>
-    <t>Blinding: Participants and clinicians unblinded; research assistants blinded to allocation.
-Deviations: TAU was active treatment (mainly face-to-face counselling, mean 4.8 sessions); 13.3% of TAU were waitlisted. Non-inferiority design.</t>
-  </si>
-  <si>
-    <t>Attrition: 9% overall (SPARX 9/94, TAU 8/93); comparable between groups.
-Method for handling missing data: ITT with multiple imputation (10 imputations).
-Post-intervention: 91% assessed; 3mo FU: 90% assessed.</t>
-  </si>
-  <si>
     <t>Validation of measurement: CDRS-R (Cronbach α=0.84 in study); clinician-rated.
 Who is in charge of assessment: Trained research assistants blinded to treatment allocation.</t>
-  </si>
-  <si>
-    <t>Pre-registered: ACTRN12609000249257; protocol available on sparx.org.nz.
-All primary and secondary outcomes reported as pre-specified. Sample size recalculated mid-trial based on pooled variance (not treatment allocation).</t>
-  </si>
-  <si>
-    <t>Only D2 raises concern: unblinded participants, TAU is active treatment (face-to-face counselling). All other domains Low risk. Strong trial design (CONSORT-compliant, blinded assessors, excellent retention, pre-registered).</t>
   </si>
   <si>
     <t>O'Dea et al., 2020</t>
@@ -1091,10 +1007,6 @@
 the intervention and control groups.</t>
   </si>
   <si>
-    <t xml:space="preserve">Participants unblinded to group assignment (open-label design).No evidence of contamination or active co-intervention reported.
-</t>
-  </si>
-  <si>
     <t>8.6% attrition at 16-week primary endpoint (10/116); no differential attrition between groups. ITT analysis using mixed-effects models with likelihood-based estimation incorporating all available data.</t>
   </si>
   <si>
@@ -1103,9 +1015,6 @@
   </si>
   <si>
     <t>No trial registration number or published protocol reported. Reported outcomes consistent with those described in Methods; no obvious selective reporting detected.</t>
-  </si>
-  <si>
-    <t>D2 Some concerns + D5 Some concerns → Overall: Some concerns</t>
   </si>
   <si>
     <t>Smith et al., 2015</t>
@@ -1143,9 +1052,6 @@
     <t>Computer-generated randomization; sealed opaque envelopes prepared by uninvolved colleague; baseline broadly balanced.</t>
   </si>
   <si>
-    <t>Participants unblinded; counsellor blinding not formally verified; 22.2% cCBT participants guessed allocation correctly. Low co-intervention risk given purely self-help format.</t>
-  </si>
-  <si>
     <t>ITT with LOCF; completion 94% cCBT / 82% CPE; overall attrition ≤20%, balanced across arms.</t>
   </si>
   <si>
@@ -1162,9 +1068,6 @@
   </si>
   <si>
     <t>Remote computerised allocation by University of York Trials Unit; baseline balanced.</t>
-  </si>
-  <si>
-    <t>Participants unblinded; researcher present but provided no therapy; structural asymmetry between arms (homework vs. none).</t>
   </si>
   <si>
     <t>~40% attrition at 12 months (59.4% / 58.7% completion); no completers vs. non-completers analysis reported.</t>
@@ -1187,10 +1090,6 @@
 Baseline balance: No significant differences on demographics or outcomes at pretest. Conditions differed on perceived credibility/expectancy (p&lt;.001) — post-randomization, adjusted as covariate.</t>
   </si>
   <si>
-    <t>Blinding: Participants unblinded (open-label, three-arm comparison: CB group / CB bibliotherapy / brochure).
-Deviations: 34% received adjunctive treatment during follow-up, but rates did not differ by condition (p=.920); condition preference adjusted as covariate.</t>
-  </si>
-  <si>
     <t>Attrition: 7% at 1-yr, 10% at 18-mo, 12% at 2-yr; did not differ by condition.
 Method for handling missing data: Multiple imputation (20 datasets via IVEWare; Rubin's rules) for continuous outcomes; right-censoring for survival models.
 Differences between completers/non-completers: Higher baseline substance use associated with attrition (secondary outcome only, not depression).</t>
@@ -1217,9 +1116,6 @@
     <t>E6</t>
   </si>
   <si>
-    <t>No inactive control (WL/TAU)</t>
-  </si>
-  <si>
     <t>Egan et al., 2026</t>
   </si>
   <si>
@@ -1242,9 +1138,6 @@
   </si>
   <si>
     <t>Daras et al., 2025</t>
-  </si>
-  <si>
-    <t>The control group is under active intervention: school-based CBT</t>
   </si>
   <si>
     <t xml:space="preserve">Robinson et al., 2014 </t>
@@ -1421,19 +1314,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Mild-to-moderate </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Mild</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Mild-Moderate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mild-to-moderate</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2071,10 +1956,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>16  (= 15 + 1)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">  - With post-intervention data</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2096,6 +1977,220 @@
   </si>
   <si>
     <t>change_mean_ctrl</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ackerson 1998</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>14-18</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Community</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CDI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">10 and HRSD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10; grades 7–12; living at home with parent/guardian; no psychotic or suicidal symptoms; not in psychotherapy</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CDI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ps+hw+rp+rx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WL (delayed treatment)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 weeks; self-administered bibliotherapy; weekly monitoring calls</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weekly monitoring phone calls only; no counseling</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ind</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Biblio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>22 completers from 30 randomized (likely 15/15 by condition). Effect-size row uses completer data from Table 2. Weekly calls monitored pages/exercises only; counseling was not provided. No eligible comparative follow-up because the delayed-treatment group received the intervention after the waiting period. Component coding follows the existing Feeling Good bibliotherapy coding in this workbook; the paper itself provides limited component detail.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>post</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Completer data from Table 2. Immediate-treatment group: Time 1 to Time 2 after 4-week bibliotherapy; delayed-treatment group: Time 1 to Time 2 waiting period. No eligible randomized comparative follow-up because delayed group received treatment after Time 2.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ackerson et al., 1998</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random assignment to immediate-treatment vs delayed-treatment conditions reported, but sequence generation and allocation concealment were not described; baseline comparisons showed no significant group differences.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Open-label bibliotherapy vs delayed-treatment design; participants and researchers were aware of allocation. Weekly calls were made in both groups, and the paper states that counseling was not provided.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/30 randomized participants dropped out (26.7%; immediate 3/15=20%, delayed 5/15=33.3%). Analyses were based on 22 completers; no ITT or imputation was reported.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Depressive symptoms were assessed with validated measures (CDI, HRSD, CBCL-D), but assessors/participants were not reported as blinded; self-report and clinician-rated outcomes may be affected by open-label allocation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>No trial registration or published protocol was reported; multiple depression outcomes were reported (CDI, HRSD, CBCL-D), and a primary outcome was not clearly pre-specified.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall high risk, driven primarily by missing outcome data and completer-only analysis; additional concerns relate to unclear allocation concealment, open-label design, and lack of pre-registration.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assessment-only</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAU</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WL (active monitoring)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Some concerns</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makarushka, 2012</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control (self-help websites); researcher present but provided no therapy; structural asymmetry between arms (homework vs. none).</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control; counsellor blinding not formally verified; 22.2% cCBT participants guessed allocation correctly. Low co-intervention risk given purely self-help format.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Attention control.No evidence of contamination or active co-intervention reported.
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blinding: Information-only (brochure) control (open-label, three-arm comparison: CB group / CB bibliotherapy / brochure).
+Deviations: 34% received adjunctive treatment during follow-up, but rates did not differ by condition (p=.920); condition preference adjusted as covariate.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merry et al., 2012</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The effectiveness of SPARX, a computerised self help
+intervention for adolescents seeking help for
+depression: randomisedcontrolled non-inferiority trial</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>No inactive control (WL/TAU)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The control group is under active intervention: school-based CBT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The control group is under active intervention: face-to-face</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15  (= 14 + 1)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D5 Some concerns → Overall: Some concerns</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Some concerns across D1 (sequence generation and allocation concealment not described; post-randomization exclusion),  D3 (differential attrition, though handled with EM imputation), and D5 (no pre-registration). D4 low risk (computer-based self-report). No single domain reaches High risk.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2106,7 +2201,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2190,6 +2285,12 @@
       <name val="宋体"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2211,7 +2312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2246,6 +2347,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2548,7 +2652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="11" width="16" style="2" customWidth="1"/>
@@ -2616,16 +2720,16 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>17</v>
@@ -2634,10 +2738,10 @@
         <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
@@ -2681,7 +2785,7 @@
         <v>15.63</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>28</v>
@@ -2695,32 +2799,32 @@
       <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Z2" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="91.8" customHeight="1">
@@ -2728,16 +2832,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2">
         <v>2010</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F3" s="2">
         <v>80</v>
@@ -2746,52 +2850,52 @@
         <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="2">
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="V3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="AC3" s="2" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
@@ -2799,16 +2903,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2">
         <v>2023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
@@ -2817,52 +2921,52 @@
         <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="V4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="AC4" s="2" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="61.2" customHeight="1">
@@ -2870,16 +2974,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2">
         <v>2012</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2">
         <v>20</v>
@@ -2888,52 +2992,52 @@
         <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I5" s="2">
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="O5" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="V5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="AB5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC5" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="71.400000000000006" customHeight="1">
@@ -2941,16 +3045,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" s="2">
         <v>2016</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2">
         <v>130</v>
@@ -2959,52 +3063,52 @@
         <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2">
         <v>14.63</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="V6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="64.8" customHeight="1">
@@ -3012,16 +3116,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2">
         <v>2012</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F7" s="2">
         <v>76</v>
@@ -3030,7 +3134,7 @@
         <v>85</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2">
         <v>12.7</v>
@@ -3039,108 +3143,108 @@
         <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="V7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="20.399999999999999" customHeight="1">
+    </row>
+    <row r="8" spans="1:29" ht="51" customHeight="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2020</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="2">
+        <v>98</v>
+      </c>
+      <c r="G8" s="2">
+        <v>95</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="2">
-        <v>2012</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="2">
-        <v>94</v>
-      </c>
-      <c r="G8" s="2">
-        <v>93</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2">
+        <v>14.82</v>
+      </c>
+      <c r="J8" s="2">
+        <v>86.5</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="2">
-        <v>15.6</v>
-      </c>
-      <c r="J8" s="2">
-        <v>65.8</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>32</v>
+      <c r="O8" s="16" t="s">
+        <v>537</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>106</v>
       </c>
       <c r="V8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W8" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="Z8" s="2" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>107</v>
@@ -3149,621 +3253,606 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="51" customHeight="1">
+    <row r="9" spans="1:29" ht="105.6" customHeight="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="2">
-        <v>2020</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2">
+        <v>195</v>
+      </c>
+      <c r="G9" s="2">
+        <v>190</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="2">
+        <v>15.89</v>
+      </c>
+      <c r="J9" s="2">
+        <v>74.2</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="2">
-        <v>98</v>
-      </c>
-      <c r="G9" s="2">
-        <v>95</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="M9" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="2">
-        <v>14.82</v>
-      </c>
-      <c r="J9" s="2">
-        <v>86.5</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="O9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="V9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="105.6" customHeight="1">
+    </row>
+    <row r="10" spans="1:29" ht="187.2" customHeight="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C10" s="2">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2">
+        <v>51</v>
+      </c>
+      <c r="G10" s="2">
+        <v>51</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="2">
+        <v>13.35</v>
+      </c>
+      <c r="J10" s="13">
+        <v>100</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="2">
-        <v>195</v>
-      </c>
-      <c r="G10" s="2">
-        <v>190</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="2">
-        <v>15.89</v>
-      </c>
-      <c r="J10" s="2">
-        <v>74.2</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="V10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="N10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="187.2" customHeight="1">
+    </row>
+    <row r="11" spans="1:29" ht="81.599999999999994" customHeight="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="2">
+        <v>58</v>
+      </c>
+      <c r="G11" s="2">
+        <v>58</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J11" s="2">
+        <v>58.6</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="2">
-        <v>2016</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="M11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="2">
-        <v>51</v>
-      </c>
-      <c r="G11" s="2">
-        <v>51</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="V11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W11" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I11" s="2">
-        <v>13.35</v>
-      </c>
-      <c r="J11" s="13">
-        <v>100</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O11" s="2" t="s">
+      <c r="AC11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:29" ht="91.8" customHeight="1">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB11" s="2" t="s">
+      <c r="C12" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AC11" s="2" t="s">
+      <c r="F12" s="2">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2">
+        <v>57</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="81.599999999999994" customHeight="1">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="2">
-        <v>2018</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="2">
+      <c r="O12" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="105.6" customHeight="1">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2014</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="2">
+        <v>17</v>
+      </c>
+      <c r="G13" s="2">
+        <v>17</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>41</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="153" customHeight="1">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2020</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="2">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2">
+        <v>69</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I14" s="2">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2">
+        <v>64</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="204">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F15" s="2">
+        <v>128</v>
+      </c>
+      <c r="G15" s="2">
+        <v>124</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="J15" s="2">
+        <v>68</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="2">
-        <v>58</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J12" s="2">
-        <v>58.6</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="91.8" customHeight="1">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2015</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="2">
-        <v>55</v>
-      </c>
-      <c r="G13" s="2">
-        <v>57</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="105.6" customHeight="1">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2014</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F14" s="2">
-        <v>17</v>
-      </c>
-      <c r="G14" s="2">
-        <v>17</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="2">
-        <v>15.2</v>
-      </c>
-      <c r="J14" s="2">
-        <v>41</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="AC14" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="153" customHeight="1">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2020</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="2">
-        <v>70</v>
-      </c>
-      <c r="G15" s="2">
-        <v>69</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="V15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB15" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="I15" s="2">
+      <c r="AC15" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="112.2">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1998</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F16" s="2">
         <v>15</v>
       </c>
-      <c r="J15" s="2">
-        <v>64</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="204">
-      <c r="A16" s="2">
+      <c r="G16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2015</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F16" s="2">
-        <v>128</v>
-      </c>
-      <c r="G16" s="2">
-        <v>124</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>168</v>
+        <v>514</v>
       </c>
       <c r="I16" s="2">
-        <v>15.5</v>
+        <v>15.92</v>
       </c>
       <c r="J16" s="2">
-        <v>68</v>
+        <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>169</v>
+        <v>515</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="O16" s="16" t="s">
         <v>519</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="P16" s="2" t="s">
-        <v>61</v>
+        <v>520</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>172</v>
+        <v>521</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>522</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>35</v>
+        <v>523</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>50</v>
+        <v>524</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>37</v>
+        <v>525</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>173</v>
+        <v>385</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1998</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>537</v>
-      </c>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="17" spans="14:14">
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="14:14">
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="14:14">
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="14:14">
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="14:14" ht="9.6" customHeight="1">
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="14:14">
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="14:14">
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="14:14">
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="14:14">
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="14:14">
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="14:14">
       <c r="N27" s="10"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="N28" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -3774,7 +3863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AE35"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="30" width="13" style="2" customWidth="1"/>
@@ -3791,88 +3880,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>547</v>
+        <v>511</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>548</v>
+        <v>512</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -3883,10 +3972,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -3913,10 +4002,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>404</v>
+        <v>371</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -3937,7 +4026,7 @@
         <v>-6.13</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -3945,10 +4034,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -3975,10 +4064,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>404</v>
+        <v>371</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -3999,7 +4088,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4007,10 +4096,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -4046,16 +4135,16 @@
         <v>9.74</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4063,10 +4152,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -4102,16 +4191,16 @@
         <v>10.93</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4119,10 +4208,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -4158,16 +4247,16 @@
         <v>10.039999999999999</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4175,10 +4264,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -4214,16 +4303,16 @@
         <v>9.44</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4231,10 +4320,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4270,16 +4359,16 @@
         <v>8.86</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4287,10 +4376,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4314,13 +4403,13 @@
         <v>38.4</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>404</v>
+        <v>371</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4341,7 +4430,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4349,10 +4438,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4388,16 +4477,16 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE10" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4405,10 +4494,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -4444,16 +4533,16 @@
         <v>8.5</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4461,10 +4550,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -4500,16 +4589,16 @@
         <v>10.09</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -4517,10 +4606,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4556,370 +4645,370 @@
         <v>10.35</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" ht="30.6" customHeight="1">
       <c r="A14" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2">
-        <v>43.02</v>
+        <v>14.59</v>
       </c>
       <c r="H14" s="2">
-        <v>11.12</v>
+        <v>6.88</v>
       </c>
       <c r="I14" s="2">
-        <v>42.09</v>
+        <v>12.73</v>
       </c>
       <c r="J14" s="2">
-        <v>10.38</v>
+        <v>6.68</v>
       </c>
       <c r="K14" s="2">
-        <v>33.92</v>
+        <v>12.33</v>
       </c>
       <c r="L14" s="2">
-        <v>11.19</v>
+        <v>7.11</v>
       </c>
       <c r="M14" s="2">
-        <v>35.07</v>
+        <v>11.13</v>
       </c>
       <c r="N14" s="2">
-        <v>9.7100000000000009</v>
+        <v>7.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" ht="9.6" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="30.6" customHeight="1">
       <c r="A15" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D15" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F15" s="2">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2">
-        <v>43.02</v>
+        <v>14.59</v>
       </c>
       <c r="H15" s="2">
-        <v>11.12</v>
+        <v>6.88</v>
       </c>
       <c r="I15" s="2">
-        <v>42.09</v>
+        <v>12.73</v>
       </c>
       <c r="J15" s="2">
-        <v>10.38</v>
+        <v>6.68</v>
       </c>
       <c r="K15" s="2">
-        <v>28.96</v>
+        <v>12.05</v>
       </c>
       <c r="L15" s="2">
-        <v>9.11</v>
+        <v>7.1</v>
       </c>
       <c r="M15" s="2">
-        <v>29.37</v>
+        <v>11.27</v>
       </c>
       <c r="N15" s="2">
-        <v>9.8699999999999992</v>
+        <v>7.12</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
       <c r="A16" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E16" s="2">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="F16" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="G16" s="2">
-        <v>14.59</v>
+        <v>12.34</v>
       </c>
       <c r="H16" s="2">
-        <v>6.88</v>
+        <v>4.05</v>
       </c>
       <c r="I16" s="2">
-        <v>12.73</v>
+        <v>12.36</v>
       </c>
       <c r="J16" s="2">
-        <v>6.68</v>
-      </c>
-      <c r="K16" s="2">
-        <v>12.33</v>
-      </c>
-      <c r="L16" s="2">
-        <v>7.11</v>
-      </c>
-      <c r="M16" s="2">
-        <v>11.13</v>
-      </c>
-      <c r="N16" s="2">
-        <v>7.2</v>
+        <v>3.88</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>196</v>
+        <v>364</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>196</v>
+        <v>373</v>
+      </c>
+      <c r="X16" s="2">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>-0.12</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>-0.35</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="30.6" customHeight="1">
       <c r="A17" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>102</v>
+      </c>
+      <c r="F17" s="2">
+        <v>135</v>
+      </c>
+      <c r="G17" s="2">
+        <v>12.34</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4.05</v>
+      </c>
+      <c r="I17" s="2">
+        <v>12.36</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3.88</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="X17" s="2">
+        <v>-0.45</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31">
+      <c r="A18" s="2">
+        <v>10</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2">
+        <v>51</v>
+      </c>
+      <c r="G18" s="2">
+        <v>62.61</v>
+      </c>
+      <c r="H18" s="2">
+        <v>11.97</v>
+      </c>
+      <c r="I18" s="2">
+        <v>61.9</v>
+      </c>
+      <c r="J18" s="2">
+        <v>11.97</v>
+      </c>
+      <c r="K18" s="2">
+        <v>57.88</v>
+      </c>
+      <c r="L18" s="2">
+        <v>12.57</v>
+      </c>
+      <c r="M18" s="2">
+        <v>57.74</v>
+      </c>
+      <c r="N18" s="2">
+        <v>12.56</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31">
+      <c r="A19" s="2">
+        <v>10</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="2">
         <v>3</v>
       </c>
-      <c r="E17" s="2">
-        <v>55</v>
-      </c>
-      <c r="F17" s="2">
-        <v>60</v>
-      </c>
-      <c r="G17" s="2">
-        <v>14.59</v>
-      </c>
-      <c r="H17" s="2">
-        <v>6.88</v>
-      </c>
-      <c r="I17" s="2">
-        <v>12.73</v>
-      </c>
-      <c r="J17" s="2">
-        <v>6.68</v>
-      </c>
-      <c r="K17" s="2">
-        <v>12.05</v>
-      </c>
-      <c r="L17" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="M17" s="2">
-        <v>11.27</v>
-      </c>
-      <c r="N17" s="2">
-        <v>7.12</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE17" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" ht="30.6" customHeight="1">
-      <c r="A18" s="2">
-        <v>9</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>130</v>
-      </c>
-      <c r="F18" s="2">
-        <v>154</v>
-      </c>
-      <c r="G18" s="2">
-        <v>12.34</v>
-      </c>
-      <c r="H18" s="2">
-        <v>4.05</v>
-      </c>
-      <c r="I18" s="2">
-        <v>12.36</v>
-      </c>
-      <c r="J18" s="2">
-        <v>3.88</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="X18" s="2">
-        <v>-0.56999999999999995</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>-0.12</v>
-      </c>
-      <c r="Z18" s="2">
-        <v>-0.35</v>
-      </c>
-      <c r="AE18" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" ht="30.6" customHeight="1">
-      <c r="A19" s="2">
-        <v>9</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D19" s="2">
-        <v>4</v>
-      </c>
       <c r="E19" s="2">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2">
-        <v>12.34</v>
+        <v>62.61</v>
       </c>
       <c r="H19" s="2">
-        <v>4.05</v>
+        <v>11.97</v>
       </c>
       <c r="I19" s="2">
-        <v>12.36</v>
+        <v>61.9</v>
       </c>
       <c r="J19" s="2">
-        <v>3.88</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>27</v>
+        <v>11.97</v>
+      </c>
+      <c r="K19" s="2">
+        <v>54.78</v>
+      </c>
+      <c r="L19" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="M19" s="2">
+        <v>56.06</v>
+      </c>
+      <c r="N19" s="2">
+        <v>13.04</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>397</v>
+        <v>183</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="X19" s="2">
-        <v>-0.45</v>
-      </c>
-      <c r="Y19" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z19" s="2">
-        <v>-0.2</v>
+        <v>183</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -4927,13 +5016,13 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D20" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2">
         <v>51</v>
@@ -4954,28 +5043,28 @@
         <v>11.97</v>
       </c>
       <c r="K20" s="2">
-        <v>57.88</v>
+        <v>58.17</v>
       </c>
       <c r="L20" s="2">
-        <v>12.57</v>
+        <v>12.72</v>
       </c>
       <c r="M20" s="2">
-        <v>57.74</v>
+        <v>57.62</v>
       </c>
       <c r="N20" s="2">
-        <v>12.56</v>
+        <v>13.33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -4983,13 +5072,13 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2">
         <v>51</v>
@@ -5010,151 +5099,145 @@
         <v>11.97</v>
       </c>
       <c r="K21" s="2">
-        <v>54.78</v>
+        <v>57.08</v>
       </c>
       <c r="L21" s="2">
-        <v>10.3</v>
+        <v>14.21</v>
       </c>
       <c r="M21" s="2">
-        <v>56.06</v>
+        <v>61.22</v>
       </c>
       <c r="N21" s="2">
-        <v>13.04</v>
+        <v>15.03</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE21" s="2" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:31">
       <c r="A22" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="D22" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F22" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G22" s="2">
-        <v>62.61</v>
+        <v>13.6</v>
       </c>
       <c r="H22" s="2">
-        <v>11.97</v>
+        <v>8.6</v>
       </c>
       <c r="I22" s="2">
-        <v>61.9</v>
+        <v>13.4</v>
       </c>
       <c r="J22" s="2">
-        <v>11.97</v>
+        <v>10.1</v>
       </c>
       <c r="K22" s="2">
-        <v>58.17</v>
+        <v>14.8</v>
       </c>
       <c r="L22" s="2">
-        <v>12.72</v>
+        <v>12.4</v>
       </c>
       <c r="M22" s="2">
-        <v>57.62</v>
+        <v>15</v>
       </c>
       <c r="N22" s="2">
-        <v>13.33</v>
+        <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>225</v>
+        <v>386</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE22" s="2" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:31">
       <c r="A23" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>52</v>
+      </c>
+      <c r="F23" s="2">
+        <v>54</v>
+      </c>
+      <c r="G23" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="H23" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="I23" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="K23" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="L23" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="M23" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="N23" s="2">
+        <v>11</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="61.2" customHeight="1">
+      <c r="A24" s="2">
         <v>12</v>
       </c>
-      <c r="E23" s="2">
-        <v>51</v>
-      </c>
-      <c r="F23" s="2">
-        <v>51</v>
-      </c>
-      <c r="G23" s="2">
-        <v>62.61</v>
-      </c>
-      <c r="H23" s="2">
-        <v>11.97</v>
-      </c>
-      <c r="I23" s="2">
-        <v>61.9</v>
-      </c>
-      <c r="J23" s="2">
-        <v>11.97</v>
-      </c>
-      <c r="K23" s="2">
-        <v>57.08</v>
-      </c>
-      <c r="L23" s="2">
-        <v>14.21</v>
-      </c>
-      <c r="M23" s="2">
-        <v>61.22</v>
-      </c>
-      <c r="N23" s="2">
-        <v>15.03</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE23" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31">
-      <c r="A24" s="2">
-        <v>11</v>
-      </c>
       <c r="B24" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5166,364 +5249,370 @@
         <v>55</v>
       </c>
       <c r="G24" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="H24" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>24.8</v>
+      </c>
+      <c r="J24" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="K24" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="L24" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="M24" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="N24" s="2">
         <v>13.6</v>
       </c>
-      <c r="H24" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="I24" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="J24" s="2">
-        <v>10.1</v>
-      </c>
-      <c r="K24" s="2">
-        <v>14.8</v>
-      </c>
-      <c r="L24" s="2">
-        <v>12.4</v>
-      </c>
-      <c r="M24" s="2">
+      <c r="O24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="30.6" customHeight="1">
+      <c r="A25" s="2">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2">
+        <v>48.29</v>
+      </c>
+      <c r="H25" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="I25" s="2">
+        <v>45.47</v>
+      </c>
+      <c r="J25" s="2">
+        <v>9.44</v>
+      </c>
+      <c r="K25" s="2">
+        <v>30.41</v>
+      </c>
+      <c r="L25" s="2">
+        <v>7.38</v>
+      </c>
+      <c r="M25" s="2">
+        <v>36.29</v>
+      </c>
+      <c r="N25" s="2">
+        <v>13.77</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="30.6" customHeight="1">
+      <c r="A26" s="2">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2">
+        <v>48.29</v>
+      </c>
+      <c r="H26" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="I26" s="2">
+        <v>45.47</v>
+      </c>
+      <c r="J26" s="2">
+        <v>9.44</v>
+      </c>
+      <c r="K26" s="2">
+        <v>32.06</v>
+      </c>
+      <c r="L26" s="2">
+        <v>8.34</v>
+      </c>
+      <c r="M26" s="2">
+        <v>34</v>
+      </c>
+      <c r="N26" s="2">
+        <v>12.77</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="132.6" customHeight="1">
+      <c r="A27" s="2">
+        <v>14</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2">
+        <v>42</v>
+      </c>
+      <c r="F27" s="2">
+        <v>44</v>
+      </c>
+      <c r="G27" s="2">
+        <v>18</v>
+      </c>
+      <c r="H27" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="I27" s="2">
+        <v>16</v>
+      </c>
+      <c r="J27" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="K27" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="L27" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M27" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="N27" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE27" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="132.6" customHeight="1">
+      <c r="A28" s="2">
+        <v>14</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="2">
+        <v>12</v>
+      </c>
+      <c r="E28" s="2">
+        <v>38</v>
+      </c>
+      <c r="F28" s="2">
+        <v>37</v>
+      </c>
+      <c r="G28" s="2">
+        <v>18</v>
+      </c>
+      <c r="H28" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="I28" s="2">
+        <v>16</v>
+      </c>
+      <c r="J28" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="K28" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="L28" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="M28" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="N28" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE28" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="30.6">
+      <c r="A29" s="2">
         <v>15</v>
       </c>
-      <c r="N24" s="2">
-        <v>11.9</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31">
-      <c r="A25" s="2">
-        <v>11</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D25" s="2">
-        <v>4</v>
-      </c>
-      <c r="E25" s="2">
-        <v>52</v>
-      </c>
-      <c r="F25" s="2">
-        <v>54</v>
-      </c>
-      <c r="G25" s="2">
-        <v>13.6</v>
-      </c>
-      <c r="H25" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="I25" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="J25" s="2">
-        <v>10.1</v>
-      </c>
-      <c r="K25" s="2">
-        <v>12.5</v>
-      </c>
-      <c r="L25" s="2">
-        <v>12.8</v>
-      </c>
-      <c r="M25" s="2">
-        <v>11.7</v>
-      </c>
-      <c r="N25" s="2">
-        <v>11</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" ht="61.2" customHeight="1">
-      <c r="A26" s="2">
-        <v>12</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="2">
-        <v>55</v>
-      </c>
-      <c r="F26" s="2">
-        <v>55</v>
-      </c>
-      <c r="G26" s="2">
-        <v>25.6</v>
-      </c>
-      <c r="H26" s="2">
-        <v>11.1</v>
-      </c>
-      <c r="I26" s="2">
-        <v>24.8</v>
-      </c>
-      <c r="J26" s="2">
-        <v>11.8</v>
-      </c>
-      <c r="K26" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="L26" s="2">
-        <v>12.9</v>
-      </c>
-      <c r="M26" s="2">
-        <v>24.3</v>
-      </c>
-      <c r="N26" s="2">
-        <v>13.6</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE26" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" ht="30.6" customHeight="1">
-      <c r="A27" s="2">
-        <v>13</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="E29" s="2">
+        <v>128</v>
+      </c>
+      <c r="F29" s="2">
+        <v>124</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1.38</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="K29" s="2">
         <v>1.5</v>
       </c>
-      <c r="E27" s="2">
-        <v>16</v>
-      </c>
-      <c r="F27" s="2">
-        <v>13</v>
-      </c>
-      <c r="G27" s="2">
-        <v>48.29</v>
-      </c>
-      <c r="H27" s="2">
-        <v>6.49</v>
-      </c>
-      <c r="I27" s="2">
-        <v>45.47</v>
-      </c>
-      <c r="J27" s="2">
-        <v>9.44</v>
-      </c>
-      <c r="K27" s="2">
-        <v>30.41</v>
-      </c>
-      <c r="L27" s="2">
-        <v>7.38</v>
-      </c>
-      <c r="M27" s="2">
-        <v>36.29</v>
-      </c>
-      <c r="N27" s="2">
-        <v>13.77</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="30.6" customHeight="1">
-      <c r="A28" s="2">
-        <v>13</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2">
-        <v>16</v>
-      </c>
-      <c r="F28" s="2">
-        <v>13</v>
-      </c>
-      <c r="G28" s="2">
-        <v>48.29</v>
-      </c>
-      <c r="H28" s="2">
-        <v>6.49</v>
-      </c>
-      <c r="I28" s="2">
-        <v>45.47</v>
-      </c>
-      <c r="J28" s="2">
-        <v>9.44</v>
-      </c>
-      <c r="K28" s="2">
-        <v>32.06</v>
-      </c>
-      <c r="L28" s="2">
-        <v>8.34</v>
-      </c>
-      <c r="M28" s="2">
-        <v>34</v>
-      </c>
-      <c r="N28" s="2">
-        <v>12.77</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" ht="132.6" customHeight="1">
-      <c r="A29" s="2">
-        <v>14</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="2">
-        <v>4</v>
-      </c>
-      <c r="E29" s="2">
-        <v>42</v>
-      </c>
-      <c r="F29" s="2">
-        <v>44</v>
-      </c>
-      <c r="G29" s="2">
-        <v>18</v>
-      </c>
-      <c r="H29" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="I29" s="2">
-        <v>16</v>
-      </c>
-      <c r="J29" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="K29" s="2">
-        <v>14.4</v>
-      </c>
       <c r="L29" s="2">
-        <v>9.3000000000000007</v>
+        <v>0.42</v>
       </c>
       <c r="M29" s="2">
-        <v>15.4</v>
+        <v>1.51</v>
       </c>
       <c r="N29" s="2">
-        <v>9.1999999999999993</v>
+        <v>0.41</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>196</v>
+        <v>509</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" ht="132.6" customHeight="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" ht="30.6">
       <c r="A30" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D30" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="F30" s="2">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2">
-        <v>18</v>
+        <v>1.45</v>
       </c>
       <c r="H30" s="2">
-        <v>6.9</v>
+        <v>0.41</v>
       </c>
       <c r="I30" s="2">
-        <v>16</v>
+        <v>1.38</v>
       </c>
       <c r="J30" s="2">
-        <v>6.6</v>
+        <v>0.36</v>
       </c>
       <c r="K30" s="2">
-        <v>12.8</v>
+        <v>1.26</v>
       </c>
       <c r="L30" s="2">
-        <v>9.6999999999999993</v>
+        <v>0.32</v>
       </c>
       <c r="M30" s="2">
-        <v>12.3</v>
+        <v>1.28</v>
       </c>
       <c r="N30" s="2">
-        <v>8.9</v>
+        <v>0.33</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>196</v>
+        <v>509</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -5531,13 +5620,13 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D31" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2">
         <v>128</v>
@@ -5558,28 +5647,28 @@
         <v>0.36</v>
       </c>
       <c r="K31" s="2">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="L31" s="2">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="M31" s="2">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="N31" s="2">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>545</v>
+        <v>510</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5587,13 +5676,13 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="D32" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E32" s="2">
         <v>128</v>
@@ -5614,28 +5703,28 @@
         <v>0.36</v>
       </c>
       <c r="K32" s="2">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="L32" s="2">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="M32" s="2">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="N32" s="2">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -5643,13 +5732,13 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D33" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2">
         <v>128</v>
@@ -5670,140 +5759,84 @@
         <v>0.36</v>
       </c>
       <c r="K33" s="2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="L33" s="2">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="M33" s="2">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="N33" s="2">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" ht="30.6">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" ht="51">
       <c r="A34" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>233</v>
+        <v>513</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>236</v>
+        <v>527</v>
       </c>
       <c r="D34" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="F34" s="2">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="G34" s="2">
-        <v>1.45</v>
+        <v>19.2</v>
       </c>
       <c r="H34" s="2">
-        <v>0.41</v>
+        <v>7.1</v>
       </c>
       <c r="I34" s="2">
-        <v>1.38</v>
+        <v>16.8</v>
       </c>
       <c r="J34" s="2">
-        <v>0.36</v>
+        <v>4.5</v>
       </c>
       <c r="K34" s="2">
-        <v>1.34</v>
+        <v>9.4</v>
       </c>
       <c r="L34" s="2">
-        <v>0.46</v>
+        <v>6.7</v>
       </c>
       <c r="M34" s="2">
-        <v>1.31</v>
+        <v>15.8</v>
       </c>
       <c r="N34" s="2">
-        <v>0.35</v>
+        <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>234</v>
+        <v>517</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>545</v>
+        <v>510</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>196</v>
+        <v>510</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" ht="30.6">
-      <c r="A35" s="2">
-        <v>15</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="2">
-        <v>24</v>
-      </c>
-      <c r="E35" s="2">
-        <v>128</v>
-      </c>
-      <c r="F35" s="2">
-        <v>124</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1.45</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0.41</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1.38</v>
-      </c>
-      <c r="J35" s="2">
-        <v>0.36</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0.47</v>
-      </c>
-      <c r="M35" s="2">
-        <v>1.39</v>
-      </c>
-      <c r="N35" s="2">
-        <v>0.43</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE35" s="2" t="s">
-        <v>235</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -5838,46 +5871,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -5885,43 +5918,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -5929,43 +5962,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -5973,43 +6006,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="N4" s="5" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6017,43 +6050,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6061,43 +6094,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>252</v>
+        <v>542</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>254</v>
+        <v>542</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>254</v>
+        <v>542</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6105,444 +6138,445 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="153" customHeight="1">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="132.6" customHeight="1">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="M9" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F7" s="5" t="s">
+    </row>
+    <row r="10" spans="1:14" ht="102" customHeight="1">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="C10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="E10" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="G10" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="N7" s="5" t="s">
+      <c r="I10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="132.6" customHeight="1">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="M10" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D8" s="5" t="s">
+    </row>
+    <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="C11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="E11" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="153" customHeight="1">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="132.6" customHeight="1">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="102" customHeight="1">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>300</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>252</v>
+        <v>541</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="163.19999999999999" customHeight="1">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="173.4" customHeight="1">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="173.4" customHeight="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="91.8" customHeight="1">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>254</v>
+        <v>542</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>332</v>
+        <v>545</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>254</v>
+        <v>542</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="91.8" customHeight="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="51" customHeight="1">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>254</v>
+        <v>542</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>339</v>
+        <v>544</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>252</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>254</v>
+        <v>381</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="51" customHeight="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="163.19999999999999">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>254</v>
+        <v>542</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>346</v>
+        <v>547</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>348</v>
+        <v>483</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>252</v>
+        <v>541</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>414</v>
+        <v>541</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="163.19999999999999">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="91.8">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>351</v>
+        <v>529</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>252</v>
+        <v>541</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>352</v>
+        <v>530</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>353</v>
+        <v>531</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>354</v>
+        <v>532</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>252</v>
+        <v>542</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>355</v>
+        <v>534</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>254</v>
+        <v>381</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>356</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6559,19 +6593,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6579,16 +6613,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>517</v>
+        <v>482</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>516</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6596,19 +6630,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6616,16 +6650,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6633,16 +6667,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>511</v>
+        <v>476</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>512</v>
+        <v>477</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6650,19 +6684,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>510</v>
+        <v>475</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>362</v>
+        <v>550</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>371</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6670,16 +6704,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>509</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6687,16 +6721,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6704,16 +6738,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>506</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6721,16 +6755,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6738,16 +6772,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6755,16 +6789,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6772,16 +6806,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>442</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6789,16 +6823,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>448</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6806,16 +6840,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>450</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6823,338 +6857,355 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>457</v>
+        <v>422</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>461</v>
+        <v>426</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>465</v>
+        <v>430</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>472</v>
+        <v>437</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>476</v>
+        <v>441</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>482</v>
+        <v>447</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>489</v>
+        <v>454</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>492</v>
+        <v>457</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>538</v>
+        <v>503</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="C29" s="14"/>
-    </row>
-    <row r="30" spans="1:5">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30.6">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="C30" s="14"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>433</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>507</v>
+        <v>472</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>440</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>441</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -7174,20 +7225,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7195,7 +7246,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7203,7 +7254,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7211,7 +7262,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7219,7 +7270,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7227,7 +7278,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7235,15 +7286,15 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>394</v>
+        <v>361</v>
       </c>
       <c r="B13" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7251,7 +7302,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>523</v>
+        <v>488</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7259,7 +7310,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>524</v>
+        <v>489</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7267,7 +7318,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7275,7 +7326,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>526</v>
+        <v>491</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7283,15 +7334,15 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>527</v>
+        <v>492</v>
       </c>
       <c r="B19" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7299,7 +7350,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7307,7 +7358,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>530</v>
+        <v>495</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7315,7 +7366,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>531</v>
+        <v>496</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7323,7 +7374,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7331,7 +7382,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>533</v>
+        <v>498</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7339,7 +7390,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7347,15 +7398,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7363,7 +7414,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02494DD2-F241-49E9-8208-D8A762F8065C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C252A67F-AF9C-492C-9C4C-F04BBB8156BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15312" yWindow="0" windowWidth="15408" windowHeight="18480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15084" yWindow="0" windowWidth="15408" windowHeight="18480" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="562">
   <si>
     <t>Study_ID</t>
   </si>
@@ -497,9 +497,6 @@
     <t>Attention control (self-help websites)</t>
   </si>
   <si>
-    <t>8 sessions × 30–45 min</t>
-  </si>
-  <si>
     <t>NIHR Research for Patient Benefit (PB-PG-0609-19295)</t>
   </si>
   <si>
@@ -596,9 +593,6 @@
     <t>raw</t>
   </si>
   <si>
-    <t>2008 paper Table; N=completers</t>
-  </si>
-  <si>
     <t>2008 paper Table T3</t>
   </si>
   <si>
@@ -636,9 +630,6 @@
   </si>
   <si>
     <t>Table 3 T4; N=randomized</t>
-  </si>
-  <si>
-    <t>Makarushka 2012</t>
   </si>
   <si>
     <t>EM imputed (Table 4); N=assigned</t>
@@ -1068,9 +1059,6 @@
   </si>
   <si>
     <t>Remote computerised allocation by University of York Trials Unit; baseline balanced.</t>
-  </si>
-  <si>
-    <t>~40% attrition at 12 months (59.4% / 58.7% completion); no completers vs. non-completers analysis reported.</t>
   </si>
   <si>
     <t>Validated self-report measures (BDI, MFQ); no assessor bias.</t>
@@ -1722,50 +1710,6 @@
   <si>
     <t>A Relational Agent Intervention for Adolescents Seeking Mental Health Treatment: outcomes From a Randomized Controlled Trial Within a Children's Outpatient Hospital</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Validation: K-SADS semi-structured diagnostic interview (test-retest κ=.99; inter-rater κ=1.00 for diagnoses, ICC=.99 for items).
-Assessor: Trained assessors (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>40 hr training) blinded to condition; required κ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.80 maintained.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1988,10 +1932,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Community</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">CDI </t>
     </r>
@@ -2054,10 +1994,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Weekly monitoring phone calls only; no counseling</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Ind</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2070,10 +2006,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>22 completers from 30 randomized (likely 15/15 by condition). Effect-size row uses completer data from Table 2. Weekly calls monitored pages/exercises only; counseling was not provided. No eligible comparative follow-up because the delayed-treatment group received the intervention after the waiting period. Component coding follows the existing Feeling Good bibliotherapy coding in this workbook; the paper itself provides limited component detail.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>post</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2135,10 +2067,6 @@
   </si>
   <si>
     <t>Low</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Makarushka, 2012</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2152,11 +2080,6 @@
   <si>
     <t xml:space="preserve">Attention control.No evidence of contamination or active co-intervention reported.
 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Blinding: Information-only (brochure) control (open-label, three-arm comparison: CB group / CB bibliotherapy / brochure).
-Deviations: 34% received adjunctive treatment during follow-up, but rates did not differ by condition (p=.920); condition preference adjusted as covariate.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2191,6 +2114,129 @@
   </si>
   <si>
     <t>Some concerns across D1 (sequence generation and allocation concealment not described; post-randomization exclusion),  D3 (differential attrition, though handled with EM imputation), and D5 (no pre-registration). D4 low risk (computer-based self-report). No single domain reaches High risk.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>22 completers from 30 randomized (likely 15/15 by condition). Effect-size row uses completer data from Table 2. Weekly calls monitored pages/exercises only; counseling was not provided. No eligible comparative follow-up because the delayed-treatment group received the intervention after the waiting period. Component coding follows the existing Feeling Good bibliotherapy coding in this workbook; the paper itself provides limited component detail. 
+Although the inclusion citeria didn't meet the cut-off of the CDI, the baseline score had excceed the cut-off.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>School/hospital/advertisement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Study ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Primary</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Traditional</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rohde 2014</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Participants and intervention providers necessarily unblinded due to nature of conditions (book vs. brochure vs. group); three conditions differed significantly on perceived credibility, expected benefit, and satisfaction (all p &lt; .001); however, ITT analysis using multiple imputation (20 datasets, fully conditional specification) was applied for continuous outcomes, and rates of adjunctive mental health treatment did not differ across conditions during follow-up.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indicated Prevention</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Validation: K-SADS semi-structured diagnostic interview (test-retest κ=.99; inter-rater κ=1.00 for diagnoses, ICC=.99 for items).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Yet this is a revised version.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Assessor: Trained assessors (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>40 hr training) blinded to condition; required κ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.80 maintained.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>~40% attrition at 12 months (59.4% / 58.7% completion); no completers vs. non-completers analysis reported.Although the primary analysis was described as intention-to-treat and used covariance pattern mixed models to handle repeated measures, participants were included only if they had complete baseline data and at least one post-randomisation outcome. Thus, participants with no follow-up outcome data were excluded from the model. The mixed-model approach relies on assumptions about the missing-data mechanism, and insufficient information was provided to rule out outcome-dependent missingness.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 sessions × 30–45 min</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2008 &amp; 2010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2008 paper Table; N=completers; principle: using the first report if later report was different from the former</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makarushka 2011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makarushka, 2011</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2277,19 +2323,19 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Cambria Math"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2669,7 +2715,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="51">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2720,16 +2766,16 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>17</v>
@@ -2738,10 +2784,10 @@
         <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
@@ -2784,8 +2830,8 @@
       <c r="I2" s="2">
         <v>15.63</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>385</v>
+      <c r="J2" s="2">
+        <v>90.6</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>28</v>
@@ -2800,7 +2846,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2815,7 +2861,7 @@
         <v>35</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>36</v>
@@ -2834,8 +2880,8 @@
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2">
-        <v>2010</v>
+      <c r="C3" s="2" t="s">
+        <v>558</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -2856,7 +2902,7 @@
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>43</v>
@@ -2871,10 +2917,10 @@
         <v>46</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>47</v>
@@ -2886,7 +2932,7 @@
         <v>48</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>36</v>
@@ -2895,7 +2941,7 @@
         <v>49</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
@@ -2924,10 +2970,10 @@
         <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>54</v>
@@ -2942,7 +2988,7 @@
         <v>57</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>58</v>
@@ -2966,7 +3012,7 @@
         <v>62</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="61.2" customHeight="1">
@@ -2998,7 +3044,7 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>66</v>
@@ -3013,7 +3059,7 @@
         <v>69</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>58</v>
@@ -3031,10 +3077,10 @@
         <v>61</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>71</v>
+        <v>518</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>72</v>
@@ -3068,8 +3114,8 @@
       <c r="I6" s="2">
         <v>14.63</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>385</v>
+      <c r="J6" s="2">
+        <v>68.099999999999994</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>43</v>
@@ -3119,7 +3165,7 @@
         <v>86</v>
       </c>
       <c r="C7" s="2">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>40</v>
@@ -3226,7 +3272,7 @@
         <v>105</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>94</v>
@@ -3365,7 +3411,7 @@
         <v>69</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>32</v>
@@ -3380,7 +3426,7 @@
         <v>60</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AA10" s="2" t="s">
         <v>36</v>
@@ -3403,7 +3449,7 @@
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>125</v>
@@ -3418,7 +3464,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
@@ -3436,7 +3482,7 @@
         <v>92</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>94</v>
@@ -3451,7 +3497,7 @@
         <v>130</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AA11" s="2" t="s">
         <v>36</v>
@@ -3474,7 +3520,7 @@
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>134</v>
@@ -3489,10 +3535,10 @@
         <v>26</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>43</v>
@@ -3507,10 +3553,10 @@
         <v>137</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>138</v>
@@ -3522,7 +3568,7 @@
         <v>60</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AA12" s="2" t="s">
         <v>36</v>
@@ -3539,7 +3585,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -3586,6 +3632,9 @@
       <c r="Q13" s="2" t="s">
         <v>145</v>
       </c>
+      <c r="R13" s="2">
+        <v>21</v>
+      </c>
       <c r="V13" s="2" t="s">
         <v>34</v>
       </c>
@@ -3593,13 +3642,13 @@
         <v>60</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AA13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>146</v>
@@ -3610,7 +3659,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -3655,7 +3704,13 @@
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>151</v>
+        <v>557</v>
+      </c>
+      <c r="R14" s="2">
+        <v>45</v>
+      </c>
+      <c r="U14" s="2">
+        <v>7</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>34</v>
@@ -3664,16 +3719,16 @@
         <v>60</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AB14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AC14" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="204">
@@ -3681,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -3690,7 +3745,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3699,7 +3754,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -3708,16 +3763,16 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>93</v>
@@ -3726,7 +3781,10 @@
         <v>58</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>551</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>34</v>
@@ -3734,34 +3792,37 @@
       <c r="W15" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="X15" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="Z15" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AA15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="112.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="142.80000000000001">
       <c r="A16" s="2">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3770,55 +3831,61 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="I16" s="2">
-        <v>15.92</v>
+        <v>15.89</v>
       </c>
       <c r="J16" s="2">
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="R16" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="W16" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="X16" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="AA16" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="O16" s="16" t="s">
-        <v>519</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="AB16" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -3880,88 +3947,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="AA1" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -3972,10 +4039,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -4002,10 +4069,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -4025,8 +4092,14 @@
       <c r="W2" s="2">
         <v>-6.13</v>
       </c>
+      <c r="AC2" s="2">
+        <v>15</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>17</v>
+      </c>
       <c r="AE2" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -4034,10 +4107,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -4064,10 +4137,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4088,18 +4161,18 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="20.399999999999999">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -4138,13 +4211,19 @@
         <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>4</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>184</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4152,10 +4231,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -4194,13 +4273,13 @@
         <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AE5" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4208,10 +4287,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -4250,13 +4329,13 @@
         <v>45</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4264,10 +4343,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -4306,13 +4385,13 @@
         <v>45</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4320,10 +4399,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4362,13 +4441,19 @@
         <v>56</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>7</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4376,10 +4461,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4406,10 +4491,10 @@
         <v>68</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4429,8 +4514,14 @@
       <c r="W9" s="2">
         <v>-1.1000000000000001</v>
       </c>
+      <c r="AC9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0</v>
+      </c>
       <c r="AE9" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4438,10 +4529,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4480,13 +4571,19 @@
         <v>56</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>7</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4494,10 +4591,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -4536,13 +4633,13 @@
         <v>56</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4550,10 +4647,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -4592,13 +4689,19 @@
         <v>91</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>61</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>40</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -4606,10 +4709,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4648,13 +4751,13 @@
         <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -4662,10 +4765,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4704,13 +4807,19 @@
         <v>112</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -4718,10 +4827,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -4760,13 +4869,13 @@
         <v>112</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -4774,10 +4883,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D16" s="2">
         <v>1.2</v>
@@ -4816,10 +4925,10 @@
         <v>112</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="X16" s="2">
         <v>-0.56999999999999995</v>
@@ -4830,8 +4939,14 @@
       <c r="Z16" s="2">
         <v>-0.35</v>
       </c>
+      <c r="AC16" s="2">
+        <v>65</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>36</v>
+      </c>
       <c r="AE16" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="30.6" customHeight="1">
@@ -4839,10 +4954,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -4881,10 +4996,10 @@
         <v>112</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="X17" s="2">
         <v>-0.45</v>
@@ -4896,7 +5011,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -4904,10 +5019,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -4943,16 +5058,22 @@
         <v>12.56</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>2</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>0</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -4960,10 +5081,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -4999,16 +5120,16 @@
         <v>13.04</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5016,10 +5137,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
@@ -5055,16 +5176,16 @@
         <v>13.33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5072,10 +5193,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D21" s="2">
         <v>12</v>
@@ -5111,16 +5232,16 @@
         <v>15.03</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE21" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5128,10 +5249,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -5167,13 +5288,19 @@
         <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:31">
@@ -5181,10 +5308,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D23" s="2">
         <v>4</v>
@@ -5220,13 +5347,13 @@
         <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="61.2" customHeight="1">
@@ -5234,10 +5361,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5276,10 +5403,16 @@
         <v>136</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="2">
+        <v>2</v>
       </c>
       <c r="AE24" s="2" t="s">
         <v>140</v>
@@ -5290,10 +5423,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2">
         <v>1.5</v>
@@ -5332,10 +5465,16 @@
         <v>68</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC25" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="30.6" customHeight="1">
@@ -5343,10 +5482,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -5385,10 +5524,10 @@
         <v>68</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -5396,10 +5535,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5438,13 +5577,19 @@
         <v>45</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>28</v>
+      </c>
+      <c r="AD27" s="2">
+        <v>25</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="132.6" customHeight="1">
@@ -5452,10 +5597,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
@@ -5494,13 +5639,13 @@
         <v>45</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -5508,19 +5653,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>216</v>
+        <v>552</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
       </c>
       <c r="E29" s="2">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F29" s="2">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G29" s="2">
         <v>1.45</v>
@@ -5547,16 +5692,22 @@
         <v>0.41</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
+      </c>
+      <c r="AC29" s="2">
+        <v>6</v>
+      </c>
+      <c r="AD29" s="2">
+        <v>8</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -5564,19 +5715,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>216</v>
+        <v>552</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
       </c>
       <c r="E30" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F30" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G30" s="2">
         <v>1.45</v>
@@ -5603,16 +5754,16 @@
         <v>0.33</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -5620,19 +5771,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D31" s="2">
         <v>12</v>
       </c>
       <c r="E31" s="2">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F31" s="2">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G31" s="2">
         <v>1.45</v>
@@ -5659,16 +5810,16 @@
         <v>0.4</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5676,19 +5827,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="D32" s="2">
         <v>18</v>
       </c>
       <c r="E32" s="2">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F32" s="2">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G32" s="2">
         <v>1.45</v>
@@ -5715,16 +5866,16 @@
         <v>0.35</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -5732,19 +5883,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
       </c>
       <c r="E33" s="2">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="F33" s="2">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2">
         <v>1.45</v>
@@ -5771,16 +5922,16 @@
         <v>0.43</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="51">
@@ -5788,10 +5939,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -5827,16 +5978,22 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
+      </c>
+      <c r="AC34" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD34" s="2">
+        <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -5871,46 +6028,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -5918,43 +6075,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -5962,43 +6119,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6006,43 +6163,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6050,43 +6207,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6094,43 +6251,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6138,43 +6295,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="K7" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>275</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6182,43 +6339,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6226,43 +6383,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6270,43 +6427,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6314,43 +6471,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6358,43 +6515,43 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="M12" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6402,43 +6559,43 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="K13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -6446,87 +6603,87 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="M14" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="163.19999999999999">
+    </row>
+    <row r="15" spans="1:14" ht="204">
       <c r="A15" s="2">
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="91.8">
@@ -6534,43 +6691,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="L16" s="2" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -6593,19 +6750,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6613,16 +6770,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6630,19 +6787,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6650,16 +6807,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6667,16 +6824,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6684,19 +6841,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6704,16 +6861,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6721,16 +6878,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6738,16 +6895,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6755,16 +6912,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6772,16 +6929,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6789,16 +6946,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6806,16 +6963,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6823,16 +6980,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6840,16 +6997,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6857,16 +7014,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6874,16 +7031,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -6891,16 +7048,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -6908,16 +7065,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>430</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -6925,16 +7082,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -6942,16 +7099,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -6959,16 +7116,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -6976,16 +7133,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -6993,16 +7150,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7010,16 +7167,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7027,16 +7184,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7044,16 +7201,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7061,16 +7218,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7078,19 +7235,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7098,114 +7255,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -7225,20 +7382,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7246,7 +7403,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7254,7 +7411,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7262,7 +7419,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7270,7 +7427,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7278,7 +7435,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7286,7 +7443,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7294,7 +7451,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7302,7 +7459,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7310,7 +7467,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7318,7 +7475,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7326,7 +7483,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7334,7 +7491,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7342,7 +7499,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7350,7 +7507,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7358,7 +7515,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7366,7 +7523,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7374,7 +7531,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7382,7 +7539,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7390,7 +7547,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7398,15 +7555,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7414,7 +7571,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C252A67F-AF9C-492C-9C4C-F04BBB8156BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A266206B-D389-4256-A01E-6CA26DD03858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15084" yWindow="0" windowWidth="15408" windowHeight="18480" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15084" yWindow="0" windowWidth="15408" windowHeight="18480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="561">
   <si>
     <t>Study_ID</t>
   </si>
@@ -485,9 +485,6 @@
     <t>Double-blind placebo-controlled; control=CPE (computerized psychoeducation, matched for length/format); ANCOVA with LOCF; ES calculated as d=(mean change cCBT − mean change CPE)/√error MS</t>
   </si>
   <si>
-    <t>12-18</t>
-  </si>
-  <si>
     <t>Clinical（CAMHS primary mental health workers）</t>
   </si>
   <si>
@@ -593,9 +590,6 @@
     <t>raw</t>
   </si>
   <si>
-    <t>2008 paper Table T3</t>
-  </si>
-  <si>
     <t>Stice 2010</t>
   </si>
   <si>
@@ -608,9 +602,6 @@
     <t>fu_24mo</t>
   </si>
   <si>
-    <t>2010 paper Table</t>
-  </si>
-  <si>
     <t>Bohr 2023</t>
   </si>
   <si>
@@ -672,9 +663,6 @@
   </si>
   <si>
     <t>Stasiak 2014</t>
-  </si>
-  <si>
-    <t>fu_1mo</t>
   </si>
   <si>
     <t>Wright 2020</t>
@@ -2142,10 +2130,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Rohde 2014</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Participants and intervention providers necessarily unblinded due to nature of conditions (book vs. brochure vs. group); three conditions differed significantly on perceived credibility, expected benefit, and satisfaction (all p &lt; .001); however, ITT analysis using multiple imputation (20 datasets, fully conditional specification) was applied for continuous outcomes, and rates of adjunctive mental health treatment did not differ across conditions during follow-up.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2228,15 +2212,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>2008 paper Table; N=completers; principle: using the first report if later report was different from the former</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Makarushka 2011</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Makarushka, 2011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-18</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-16</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010 paper Table</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rohde 2015</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fu_1mo</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2715,7 +2715,7 @@
   <sheetData>
     <row r="1" spans="1:29" ht="51">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2766,16 +2766,16 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>17</v>
@@ -2784,10 +2784,10 @@
         <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
@@ -2846,7 +2846,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2861,7 +2861,7 @@
         <v>35</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>36</v>
@@ -2881,7 +2881,7 @@
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -2902,7 +2902,7 @@
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>43</v>
@@ -2917,10 +2917,10 @@
         <v>46</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>47</v>
@@ -2932,7 +2932,7 @@
         <v>48</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>36</v>
@@ -2941,7 +2941,7 @@
         <v>49</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
@@ -2970,10 +2970,10 @@
         <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>54</v>
@@ -2988,7 +2988,7 @@
         <v>57</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>58</v>
@@ -3012,7 +3012,7 @@
         <v>62</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="61.2" customHeight="1">
@@ -3044,7 +3044,7 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>66</v>
@@ -3059,7 +3059,7 @@
         <v>69</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>58</v>
@@ -3077,10 +3077,10 @@
         <v>61</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>72</v>
@@ -3272,7 +3272,7 @@
         <v>105</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>94</v>
@@ -3411,7 +3411,7 @@
         <v>69</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>32</v>
@@ -3426,7 +3426,7 @@
         <v>60</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AA10" s="2" t="s">
         <v>36</v>
@@ -3449,7 +3449,7 @@
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>125</v>
@@ -3464,7 +3464,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
@@ -3482,7 +3482,7 @@
         <v>92</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>94</v>
@@ -3497,7 +3497,7 @@
         <v>130</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AA11" s="2" t="s">
         <v>36</v>
@@ -3520,7 +3520,7 @@
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>134</v>
@@ -3532,13 +3532,13 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>26</v>
+        <v>557</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>43</v>
@@ -3553,10 +3553,10 @@
         <v>137</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>138</v>
@@ -3568,7 +3568,7 @@
         <v>60</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AA12" s="2" t="s">
         <v>36</v>
@@ -3585,7 +3585,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -3642,13 +3642,13 @@
         <v>60</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AA13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>146</v>
@@ -3659,7 +3659,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -3677,7 +3677,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>147</v>
+        <v>556</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -3686,10 +3686,10 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
@@ -3698,13 +3698,13 @@
         <v>137</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -3719,16 +3719,16 @@
         <v>60</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AB14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC14" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="204">
@@ -3736,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -3745,7 +3745,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3754,7 +3754,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -3763,16 +3763,16 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>93</v>
@@ -3781,10 +3781,10 @@
         <v>58</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>34</v>
@@ -3793,19 +3793,19 @@
         <v>48</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="AA15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="142.80000000000001">
@@ -3813,16 +3813,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3831,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -3840,52 +3840,52 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="N16" s="10" t="s">
+      <c r="V16" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="O16" s="16" t="s">
+      <c r="W16" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="X16" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AA16" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="AB16" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -3947,88 +3947,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="AA1" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -4039,10 +4039,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -4069,10 +4069,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -4093,13 +4093,13 @@
         <v>-6.13</v>
       </c>
       <c r="AC2" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD2" s="2">
         <v>15</v>
       </c>
-      <c r="AD2" s="2">
-        <v>17</v>
-      </c>
       <c r="AE2" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -4107,19 +4107,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
       </c>
       <c r="E3" s="2">
+        <v>61</v>
+      </c>
+      <c r="F3" s="2">
         <v>68</v>
-      </c>
-      <c r="F3" s="2">
-        <v>70</v>
       </c>
       <c r="G3" s="2">
         <v>45.99</v>
@@ -4137,10 +4137,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4161,27 +4161,27 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" ht="20.399999999999999">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G4" s="2">
         <v>18.2</v>
@@ -4211,10 +4211,10 @@
         <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -4223,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4231,19 +4231,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F5" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G5" s="2">
         <v>18.2</v>
@@ -4273,13 +4273,13 @@
         <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>183</v>
+        <v>558</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4287,19 +4287,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
       </c>
       <c r="E6" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F6" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2">
         <v>18.2</v>
@@ -4329,13 +4329,13 @@
         <v>45</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4343,19 +4343,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
       </c>
       <c r="E7" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G7" s="2">
         <v>18.2</v>
@@ -4385,13 +4385,13 @@
         <v>45</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>188</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4399,10 +4399,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4414,10 +4414,10 @@
         <v>19</v>
       </c>
       <c r="G8" s="2">
-        <v>21.2</v>
+        <v>22.9</v>
       </c>
       <c r="H8" s="2">
-        <v>7.6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I8" s="2">
         <v>25.5</v>
@@ -4426,25 +4426,25 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="K8" s="2">
+        <v>23.21</v>
+      </c>
+      <c r="L8" s="2">
+        <v>8.86</v>
+      </c>
+      <c r="M8" s="2">
         <v>23.68</v>
       </c>
-      <c r="L8" s="2">
+      <c r="N8" s="2">
         <v>8.58</v>
-      </c>
-      <c r="M8" s="2">
-        <v>23.21</v>
-      </c>
-      <c r="N8" s="2">
-        <v>8.86</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -4453,7 +4453,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4461,10 +4461,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4491,10 +4491,10 @@
         <v>68</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4529,10 +4529,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4571,10 +4571,10 @@
         <v>56</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4591,10 +4591,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -4633,13 +4633,13 @@
         <v>56</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4647,10 +4647,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -4689,19 +4689,19 @@
         <v>91</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC12" s="2">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="AD12" s="2">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -4709,10 +4709,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4751,13 +4751,13 @@
         <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -4765,10 +4765,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4807,10 +4807,10 @@
         <v>112</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -4819,7 +4819,7 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -4827,10 +4827,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -4869,13 +4869,13 @@
         <v>112</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -4883,13 +4883,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D16" s="2">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E16" s="2">
         <v>130</v>
@@ -4925,10 +4925,10 @@
         <v>112</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="X16" s="2">
         <v>-0.56999999999999995</v>
@@ -4946,7 +4946,7 @@
         <v>36</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="30.6" customHeight="1">
@@ -4954,10 +4954,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -4996,10 +4996,10 @@
         <v>112</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="X17" s="2">
         <v>-0.45</v>
@@ -5011,7 +5011,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5019,10 +5019,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -5058,13 +5058,13 @@
         <v>12.56</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC18" s="2">
         <v>2</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5081,10 +5081,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -5120,16 +5120,16 @@
         <v>13.04</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5137,10 +5137,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
@@ -5176,16 +5176,16 @@
         <v>13.33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5193,10 +5193,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D21" s="2">
         <v>12</v>
@@ -5232,16 +5232,16 @@
         <v>15.03</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE21" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5249,10 +5249,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -5288,13 +5288,13 @@
         <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC22" s="2">
         <v>3</v>
@@ -5308,10 +5308,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D23" s="2">
         <v>4</v>
@@ -5347,13 +5347,13 @@
         <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="61.2" customHeight="1">
@@ -5361,10 +5361,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5403,10 +5403,10 @@
         <v>136</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC24" s="2">
         <v>0</v>
@@ -5423,19 +5423,19 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D25" s="2">
         <v>1.5</v>
       </c>
       <c r="E25" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F25" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G25" s="2">
         <v>48.29</v>
@@ -5465,10 +5465,10 @@
         <v>68</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC25" s="2">
         <v>1</v>
@@ -5482,19 +5482,19 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>210</v>
+        <v>560</v>
       </c>
       <c r="D26" s="2">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E26" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G26" s="2">
         <v>48.29</v>
@@ -5524,10 +5524,10 @@
         <v>68</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -5535,10 +5535,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5577,10 +5577,10 @@
         <v>45</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC27" s="2">
         <v>28</v>
@@ -5589,7 +5589,7 @@
         <v>25</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="132.6" customHeight="1">
@@ -5597,10 +5597,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
@@ -5639,13 +5639,13 @@
         <v>45</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -5653,19 +5653,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
       </c>
       <c r="E29" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F29" s="2">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G29" s="2">
         <v>1.45</v>
@@ -5692,13 +5692,13 @@
         <v>0.41</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC29" s="2">
         <v>6</v>
@@ -5707,7 +5707,7 @@
         <v>8</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -5715,19 +5715,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
       </c>
       <c r="E30" s="2">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F30" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2">
         <v>1.45</v>
@@ -5754,16 +5754,16 @@
         <v>0.33</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -5771,19 +5771,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D31" s="2">
         <v>12</v>
       </c>
       <c r="E31" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F31" s="2">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G31" s="2">
         <v>1.45</v>
@@ -5810,16 +5810,16 @@
         <v>0.4</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5827,19 +5827,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D32" s="2">
         <v>18</v>
       </c>
       <c r="E32" s="2">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F32" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G32" s="2">
         <v>1.45</v>
@@ -5866,16 +5866,16 @@
         <v>0.35</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -5883,19 +5883,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
       </c>
       <c r="E33" s="2">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F33" s="2">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G33" s="2">
         <v>1.45</v>
@@ -5922,16 +5922,16 @@
         <v>0.43</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="51">
@@ -5939,10 +5939,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -5978,13 +5978,13 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -5993,7 +5993,7 @@
         <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -6028,46 +6028,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -6075,43 +6075,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6119,43 +6119,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6163,43 +6163,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6207,43 +6207,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6251,43 +6251,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6295,43 +6295,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6339,43 +6339,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6383,43 +6383,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6427,43 +6427,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6471,43 +6471,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6515,43 +6515,43 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="M12" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6559,43 +6559,43 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -6603,43 +6603,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="204">
@@ -6647,43 +6647,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="91.8">
@@ -6691,43 +6691,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -6750,19 +6750,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6770,16 +6770,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6787,19 +6787,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6807,16 +6807,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6824,16 +6824,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6841,19 +6841,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6861,16 +6861,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6878,16 +6878,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6895,16 +6895,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6912,16 +6912,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6929,16 +6929,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6946,16 +6946,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -6963,16 +6963,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6980,16 +6980,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6997,16 +6997,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7014,16 +7014,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7031,16 +7031,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7048,16 +7048,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7065,16 +7065,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>426</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7082,16 +7082,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7099,16 +7099,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7116,16 +7116,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7133,16 +7133,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7150,16 +7150,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7167,16 +7167,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7184,16 +7184,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7201,16 +7201,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7218,16 +7218,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7235,19 +7235,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>538</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7255,114 +7255,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -7382,20 +7382,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7411,7 +7411,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7443,7 +7443,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7451,7 +7451,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7459,7 +7459,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7491,7 +7491,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7523,7 +7523,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7547,7 +7547,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7555,15 +7555,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A266206B-D389-4256-A01E-6CA26DD03858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78F498D-1A4A-4409-AA9A-4C8D28E5A9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15084" yWindow="0" windowWidth="15408" windowHeight="18480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4518,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="AD9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
         <v>189</v>
@@ -5067,7 +5067,7 @@
         <v>181</v>
       </c>
       <c r="AC18" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD18" s="2">
         <v>0</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78F498D-1A4A-4409-AA9A-4C8D28E5A9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FF973B-9DDE-4A44-87FE-CC51E0E44219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15084" yWindow="0" windowWidth="15408" windowHeight="18480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FF973B-9DDE-4A44-87FE-CC51E0E44219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8FEA1-42AA-4636-8F6B-03E6670CF21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="560">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1315,10 +1315,6 @@
   </si>
   <si>
     <t>human_contact</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>core_complete</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2698,7 +2694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="11" width="16" style="2" customWidth="1"/>
@@ -2706,16 +2702,16 @@
     <col min="13" max="13" width="16" style="2" customWidth="1"/>
     <col min="14" max="14" width="18.44140625" style="2" customWidth="1"/>
     <col min="15" max="16" width="16" style="2" customWidth="1"/>
-    <col min="17" max="21" width="25" style="2" customWidth="1"/>
-    <col min="22" max="28" width="16" style="2" customWidth="1"/>
-    <col min="29" max="29" width="30" style="2" customWidth="1"/>
-    <col min="30" max="30" width="8.88671875" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="8.88671875" style="2"/>
+    <col min="17" max="20" width="25" style="2" customWidth="1"/>
+    <col min="21" max="27" width="16" style="2" customWidth="1"/>
+    <col min="28" max="28" width="30" style="2" customWidth="1"/>
+    <col min="29" max="29" width="8.88671875" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="51">
+    <row r="1" spans="1:28" ht="51">
       <c r="A1" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2775,34 +2771,31 @@
         <v>386</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>387</v>
+        <v>17</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>372</v>
+        <v>19</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="61.2" customHeight="1">
+    <row r="2" spans="1:28" ht="61.2" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2846,7 +2839,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2854,26 +2847,29 @@
       <c r="Q2" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="Y2" s="2" t="s">
+        <v>381</v>
+      </c>
       <c r="Z2" s="2" t="s">
-        <v>381</v>
+        <v>36</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="91.8" customHeight="1">
+    <row r="3" spans="1:28" ht="91.8" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2881,7 +2877,7 @@
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -2917,7 +2913,7 @@
         <v>46</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>377</v>
@@ -2925,26 +2921,29 @@
       <c r="Q3" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="Y3" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="Z3" s="2" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC3" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
+    <row r="4" spans="1:28" ht="40.799999999999997" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>57</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>58</v>
@@ -2996,26 +2995,29 @@
       <c r="Q4" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="S4" s="2">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W4" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="Y4" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="Z4" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC4" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="61.2" customHeight="1">
+    <row r="5" spans="1:28" ht="61.2" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3059,7 +3061,7 @@
         <v>69</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>58</v>
@@ -3067,26 +3069,29 @@
       <c r="Q5" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="S5" s="2">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W5" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="Y5" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="Z5" s="2" t="s">
-        <v>61</v>
+        <v>513</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>514</v>
+        <v>377</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AC5" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="71.400000000000006" customHeight="1">
+    <row r="6" spans="1:28" ht="71.400000000000006" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3138,26 +3143,29 @@
       <c r="Q6" s="2" t="s">
         <v>81</v>
       </c>
+      <c r="S6" s="2">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W6" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="Y6" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="Z6" s="2" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC6" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="64.8" customHeight="1">
+    <row r="7" spans="1:28" ht="64.8" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3209,28 +3217,31 @@
       <c r="Q7" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W7" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="Y7" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="Z7" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AC7" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="51" customHeight="1">
+    <row r="8" spans="1:28" ht="51" customHeight="1">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>98</v>
@@ -3272,7 +3283,7 @@
         <v>105</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>94</v>
@@ -3280,28 +3291,31 @@
       <c r="Q8" s="2" t="s">
         <v>106</v>
       </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W8" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="Y8" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="Z8" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AC8" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="105.6" customHeight="1">
+    <row r="9" spans="1:28" ht="105.6" customHeight="1">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>98</v>
@@ -3351,25 +3365,28 @@
       <c r="Q9" s="2" t="s">
         <v>114</v>
       </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W9" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="Y9" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="Z9" s="2" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB9" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="187.2" customHeight="1">
+    <row r="10" spans="1:28" ht="187.2" customHeight="1">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>117</v>
@@ -3411,7 +3428,7 @@
         <v>69</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>32</v>
@@ -3419,28 +3436,31 @@
       <c r="Q10" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W10" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="Y10" s="2" t="s">
+        <v>379</v>
+      </c>
       <c r="Z10" s="2" t="s">
-        <v>379</v>
+        <v>36</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC10" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="81.599999999999994" customHeight="1">
+    <row r="11" spans="1:28" ht="81.599999999999994" customHeight="1">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>124</v>
@@ -3482,7 +3502,7 @@
         <v>92</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>94</v>
@@ -3490,26 +3510,29 @@
       <c r="Q11" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W11" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="Y11" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="Z11" s="2" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC11" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="91.8" customHeight="1">
+    <row r="12" spans="1:28" ht="91.8" customHeight="1">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -3532,7 +3555,7 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>377</v>
@@ -3553,7 +3576,7 @@
         <v>137</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>382</v>
@@ -3561,26 +3584,29 @@
       <c r="Q12" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W12" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="Y12" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="Z12" s="2" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC12" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="105.6" customHeight="1">
+    <row r="13" spans="1:28" ht="105.6" customHeight="1">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -3635,26 +3661,29 @@
       <c r="R13" s="2">
         <v>21</v>
       </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W13" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="Y13" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="Z13" s="2" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>36</v>
+        <v>377</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AC13" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="153" customHeight="1">
+    <row r="14" spans="1:28" ht="153" customHeight="1">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -3677,7 +3706,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -3704,34 +3733,37 @@
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
       </c>
-      <c r="U14" s="2">
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
         <v>7</v>
       </c>
+      <c r="U14" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="V14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W14" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="Y14" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="Z14" s="2" t="s">
-        <v>380</v>
+        <v>36</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC14" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="204">
+    <row r="15" spans="1:28" ht="204">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -3745,7 +3777,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3766,7 +3798,7 @@
         <v>154</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>155</v>
@@ -3784,36 +3816,39 @@
         <v>157</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
+      </c>
+      <c r="S15" s="2">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>379</v>
+        <v>36</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="142.80000000000001">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="142.80000000000001">
       <c r="A16" s="2">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
@@ -3822,7 +3857,7 @@
         <v>375</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3831,7 +3866,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -3840,52 +3875,55 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="O16" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="O16" s="16" t="s">
+      <c r="P16" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="S16" s="2">
+        <v>1</v>
+      </c>
+      <c r="U16" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="V16" s="2" t="s">
         <v>512</v>
       </c>
       <c r="W16" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="Z16" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="X16" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="AA16" s="2" t="s">
-        <v>514</v>
+        <v>377</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -4004,10 +4042,10 @@
         <v>362</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>367</v>
@@ -4223,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4279,7 +4317,7 @@
         <v>181</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4391,7 +4429,7 @@
         <v>181</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4647,7 +4685,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>175</v>
@@ -4709,7 +4747,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>178</v>
@@ -5485,7 +5523,7 @@
         <v>206</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D26" s="2">
         <v>2.5</v>
@@ -5653,7 +5691,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>175</v>
@@ -5695,7 +5733,7 @@
         <v>210</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>181</v>
@@ -5715,7 +5753,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>178</v>
@@ -5757,7 +5795,7 @@
         <v>210</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q30" s="2" t="s">
         <v>181</v>
@@ -5813,7 +5851,7 @@
         <v>210</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>181</v>
@@ -5869,7 +5907,7 @@
         <v>210</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>181</v>
@@ -5925,7 +5963,7 @@
         <v>210</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>181</v>
@@ -5939,10 +5977,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -5978,13 +6016,13 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -5993,7 +6031,7 @@
         <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -6028,7 +6066,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>214</v>
@@ -6084,7 +6122,7 @@
         <v>229</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>230</v>
@@ -6108,7 +6146,7 @@
         <v>233</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>234</v>
@@ -6122,13 +6160,13 @@
         <v>235</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>236</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>237</v>
@@ -6146,13 +6184,13 @@
         <v>239</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>240</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>241</v>
@@ -6166,13 +6204,13 @@
         <v>242</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>243</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>244</v>
@@ -6190,7 +6228,7 @@
         <v>247</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>248</v>
@@ -6216,7 +6254,7 @@
         <v>251</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>252</v>
@@ -6228,7 +6266,7 @@
         <v>253</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>254</v>
@@ -6240,7 +6278,7 @@
         <v>255</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>256</v>
@@ -6254,13 +6292,13 @@
         <v>257</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>258</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>259</v>
@@ -6284,7 +6322,7 @@
         <v>262</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>263</v>
@@ -6295,22 +6333,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>264</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>265</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>266</v>
@@ -6322,16 +6360,16 @@
         <v>267</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>268</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6348,7 +6386,7 @@
         <v>271</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>272</v>
@@ -6372,7 +6410,7 @@
         <v>275</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>276</v>
@@ -6392,13 +6430,13 @@
         <v>278</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>279</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>280</v>
@@ -6416,7 +6454,7 @@
         <v>282</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>283</v>
@@ -6436,13 +6474,13 @@
         <v>285</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>286</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>287</v>
@@ -6460,7 +6498,7 @@
         <v>288</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>289</v>
@@ -6480,10 +6518,10 @@
         <v>291</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>228</v>
@@ -6498,16 +6536,16 @@
         <v>293</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>294</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6524,7 +6562,7 @@
         <v>296</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>297</v>
@@ -6548,7 +6586,7 @@
         <v>300</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>301</v>
@@ -6568,10 +6606,10 @@
         <v>303</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>228</v>
@@ -6592,7 +6630,7 @@
         <v>306</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>307</v>
@@ -6612,16 +6650,16 @@
         <v>309</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>245</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>228</v>
@@ -6656,10 +6694,10 @@
         <v>314</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>228</v>
@@ -6668,19 +6706,19 @@
         <v>315</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>316</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>317</v>
@@ -6691,43 +6729,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>373</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>373</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -6773,13 +6811,13 @@
         <v>321</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6790,10 +6828,10 @@
         <v>323</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>325</v>
@@ -6810,13 +6848,13 @@
         <v>327</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6827,13 +6865,13 @@
         <v>329</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>467</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>469</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6844,16 +6882,16 @@
         <v>330</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>322</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6864,13 +6902,13 @@
         <v>331</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>465</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6881,13 +6919,13 @@
         <v>332</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6895,16 +6933,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>461</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6912,16 +6950,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>455</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6929,16 +6967,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6946,13 +6984,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>459</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>334</v>
@@ -6963,16 +7001,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>457</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -6980,16 +7018,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -6997,16 +7035,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>409</v>
-      </c>
       <c r="D15" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7014,16 +7052,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7031,16 +7069,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7048,16 +7086,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>417</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7065,16 +7103,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7082,16 +7120,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7099,16 +7137,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7116,16 +7154,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7133,16 +7171,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>437</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7150,16 +7188,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7167,16 +7205,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7184,16 +7222,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7201,16 +7239,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>450</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7218,16 +7256,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7235,19 +7273,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>536</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7266,7 +7304,7 @@
         <v>338</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="33" spans="4:5">
@@ -7274,7 +7312,7 @@
         <v>339</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="4:5">
@@ -7282,7 +7320,7 @@
         <v>340</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="4:5">
@@ -7290,7 +7328,7 @@
         <v>324</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="4:5">
@@ -7298,7 +7336,7 @@
         <v>335</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="4:5">
@@ -7306,7 +7344,7 @@
         <v>322</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="38" spans="4:5">
@@ -7314,7 +7352,7 @@
         <v>341</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="39" spans="4:5">
@@ -7322,7 +7360,7 @@
         <v>342</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="4:5">
@@ -7330,7 +7368,7 @@
         <v>328</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="41" spans="4:5">
@@ -7338,7 +7376,7 @@
         <v>343</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" spans="4:5">
@@ -7346,7 +7384,7 @@
         <v>344</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" spans="4:5">
@@ -7354,15 +7392,15 @@
         <v>333</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -7403,7 +7441,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7451,7 +7489,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7459,7 +7497,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7467,7 +7505,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7475,7 +7513,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7483,7 +7521,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7491,7 +7529,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7499,7 +7537,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7507,7 +7545,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7515,7 +7553,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7523,7 +7561,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7531,7 +7569,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7539,7 +7577,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7547,7 +7585,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7555,15 +7593,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7571,7 +7609,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8FEA1-42AA-4636-8F6B-03E6670CF21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAC87B2-1424-4D2E-86DB-8ED8D7AEECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,9 +353,6 @@
   </si>
   <si>
     <t>PHQ-9</t>
-  </si>
-  <si>
-    <t>cr+pr+ist</t>
   </si>
   <si>
     <t xml:space="preserve">Single session; ~1 hour/4 weeks </t>
@@ -2233,6 +2230,10 @@
   </si>
   <si>
     <t>fu_1mo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ps+ist</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2711,7 +2712,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="51">
       <c r="A1" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2762,13 +2763,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -2777,10 +2778,10 @@
         <v>18</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -2839,7 +2840,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2850,6 +2851,9 @@
       <c r="S2" s="2">
         <v>0</v>
       </c>
+      <c r="T2" s="2">
+        <v>4</v>
+      </c>
       <c r="U2" s="2" t="s">
         <v>34</v>
       </c>
@@ -2857,7 +2861,7 @@
         <v>35</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>36</v>
@@ -2877,7 +2881,7 @@
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -2898,7 +2902,7 @@
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>43</v>
@@ -2913,10 +2917,10 @@
         <v>46</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>47</v>
@@ -2924,6 +2928,9 @@
       <c r="S3" s="2">
         <v>0</v>
       </c>
+      <c r="T3" s="2">
+        <v>5</v>
+      </c>
       <c r="U3" s="2" t="s">
         <v>34</v>
       </c>
@@ -2931,7 +2938,7 @@
         <v>48</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>36</v>
@@ -2940,7 +2947,7 @@
         <v>49</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="40.799999999999997" customHeight="1">
@@ -2969,10 +2976,10 @@
         <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>54</v>
@@ -2987,7 +2994,7 @@
         <v>57</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>58</v>
@@ -2998,6 +3005,9 @@
       <c r="S4" s="2">
         <v>1</v>
       </c>
+      <c r="T4" s="2">
+        <v>4</v>
+      </c>
       <c r="U4" s="2" t="s">
         <v>34</v>
       </c>
@@ -3014,7 +3024,7 @@
         <v>62</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="61.2" customHeight="1">
@@ -3046,7 +3056,7 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>66</v>
@@ -3061,7 +3071,7 @@
         <v>69</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>58</v>
@@ -3072,6 +3082,9 @@
       <c r="S5" s="2">
         <v>1</v>
       </c>
+      <c r="T5" s="2">
+        <v>7</v>
+      </c>
       <c r="U5" s="2" t="s">
         <v>34</v>
       </c>
@@ -3082,10 +3095,10 @@
         <v>61</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>72</v>
@@ -3146,6 +3159,9 @@
       <c r="S6" s="2">
         <v>1</v>
       </c>
+      <c r="T6" s="2">
+        <v>2</v>
+      </c>
       <c r="U6" s="2" t="s">
         <v>34</v>
       </c>
@@ -3220,6 +3236,9 @@
       <c r="S7" s="2">
         <v>0</v>
       </c>
+      <c r="T7" s="2">
+        <v>4</v>
+      </c>
       <c r="U7" s="2" t="s">
         <v>34</v>
       </c>
@@ -3280,20 +3299,23 @@
         <v>104</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>105</v>
+        <v>559</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>94</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S8" s="2">
         <v>0</v>
       </c>
+      <c r="T8" s="2">
+        <v>3</v>
+      </c>
       <c r="U8" s="2" t="s">
         <v>34</v>
       </c>
@@ -3307,10 +3329,10 @@
         <v>36</v>
       </c>
       <c r="AA8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB8" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="105.6" customHeight="1">
@@ -3327,7 +3349,7 @@
         <v>99</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2">
         <v>195</v>
@@ -3345,16 +3367,16 @@
         <v>74.2</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>79</v>
@@ -3363,11 +3385,14 @@
         <v>94</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="S9" s="2">
         <v>0</v>
       </c>
+      <c r="T9" s="2">
+        <v>3</v>
+      </c>
       <c r="U9" s="2" t="s">
         <v>34</v>
       </c>
@@ -3378,10 +3403,10 @@
         <v>61</v>
       </c>
       <c r="Z9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="187.2" customHeight="1">
@@ -3389,13 +3414,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2">
         <v>2016</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>52</v>
@@ -3407,7 +3432,7 @@
         <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I10" s="2">
         <v>13.35</v>
@@ -3419,7 +3444,7 @@
         <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>68</v>
@@ -3428,17 +3453,20 @@
         <v>69</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S10" s="2">
         <v>0</v>
       </c>
+      <c r="T10" s="2">
+        <v>7</v>
+      </c>
       <c r="U10" s="2" t="s">
         <v>34</v>
       </c>
@@ -3446,16 +3474,16 @@
         <v>60</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="81.599999999999994" customHeight="1">
@@ -3463,16 +3491,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="2">
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F11" s="2">
         <v>58</v>
@@ -3481,19 +3509,19 @@
         <v>58</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>104</v>
@@ -3502,34 +3530,37 @@
         <v>92</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>94</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S11" s="2">
         <v>0</v>
       </c>
+      <c r="T11" s="2">
+        <v>4</v>
+      </c>
       <c r="U11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="91.8" customHeight="1">
@@ -3537,16 +3568,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2">
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F12" s="2">
         <v>55</v>
@@ -3555,38 +3586,41 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="O12" s="16" t="s">
-        <v>524</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="S12" s="2">
         <v>0</v>
       </c>
+      <c r="T12" s="2">
+        <v>7</v>
+      </c>
       <c r="U12" s="2" t="s">
         <v>34</v>
       </c>
@@ -3594,16 +3628,16 @@
         <v>60</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="105.6" customHeight="1">
@@ -3611,7 +3645,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -3620,7 +3654,7 @@
         <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F13" s="2">
         <v>17</v>
@@ -3638,16 +3672,16 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>79</v>
@@ -3656,7 +3690,7 @@
         <v>32</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R13" s="2">
         <v>21</v>
@@ -3664,6 +3698,9 @@
       <c r="S13" s="2">
         <v>0</v>
       </c>
+      <c r="T13" s="2">
+        <v>6</v>
+      </c>
       <c r="U13" s="2" t="s">
         <v>34</v>
       </c>
@@ -3671,16 +3708,16 @@
         <v>60</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="153" customHeight="1">
@@ -3688,7 +3725,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -3697,7 +3734,7 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F14" s="2">
         <v>70</v>
@@ -3706,7 +3743,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -3715,25 +3752,25 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -3751,16 +3788,16 @@
         <v>60</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="204">
@@ -3768,7 +3805,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -3777,7 +3814,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3786,7 +3823,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -3795,16 +3832,16 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>93</v>
@@ -3813,14 +3850,17 @@
         <v>58</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="S15" s="2">
         <v>1</v>
       </c>
+      <c r="T15" s="2">
+        <v>5</v>
+      </c>
       <c r="U15" s="2" t="s">
         <v>34</v>
       </c>
@@ -3828,19 +3868,19 @@
         <v>48</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="142.80000000000001">
@@ -3848,16 +3888,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3866,7 +3906,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -3875,55 +3915,58 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="O16" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="O16" s="16" t="s">
+      <c r="P16" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="R16" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="S16" s="2">
         <v>1</v>
       </c>
+      <c r="T16" s="2">
+        <v>5</v>
+      </c>
       <c r="U16" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="V16" s="2" t="s">
+      <c r="W16" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="Z16" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="W16" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="AA16" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -3985,88 +4028,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="X1" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -4077,10 +4120,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -4107,10 +4150,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -4137,7 +4180,7 @@
         <v>15</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -4145,10 +4188,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -4175,10 +4218,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4199,7 +4242,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4207,10 +4250,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -4249,10 +4292,10 @@
         <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -4261,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4269,10 +4312,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -4311,13 +4354,13 @@
         <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4325,10 +4368,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -4367,13 +4410,13 @@
         <v>45</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4381,10 +4424,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -4423,13 +4466,13 @@
         <v>45</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4437,10 +4480,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4479,10 +4522,10 @@
         <v>56</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -4491,7 +4534,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4499,10 +4542,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4529,10 +4572,10 @@
         <v>68</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4559,7 +4602,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4567,10 +4610,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4609,10 +4652,10 @@
         <v>56</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -4621,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4629,10 +4672,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -4671,13 +4714,13 @@
         <v>56</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4685,10 +4728,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -4727,10 +4770,10 @@
         <v>91</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC12" s="2">
         <v>15</v>
@@ -4739,7 +4782,7 @@
         <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -4747,10 +4790,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4789,13 +4832,13 @@
         <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -4803,10 +4846,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4842,13 +4885,13 @@
         <v>7.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -4857,7 +4900,7 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -4865,10 +4908,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -4904,16 +4947,16 @@
         <v>7.12</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -4921,10 +4964,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D16" s="2">
         <v>1.5</v>
@@ -4960,13 +5003,13 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="X16" s="2">
         <v>-0.56999999999999995</v>
@@ -4984,7 +5027,7 @@
         <v>36</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="30.6" customHeight="1">
@@ -4992,10 +5035,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -5031,13 +5074,13 @@
         <v>27</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="X17" s="2">
         <v>-0.45</v>
@@ -5049,7 +5092,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5057,10 +5100,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -5096,13 +5139,13 @@
         <v>12.56</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC18" s="2">
         <v>4</v>
@@ -5111,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5119,10 +5162,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -5158,16 +5201,16 @@
         <v>13.04</v>
       </c>
       <c r="O19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE19" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE19" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5175,10 +5218,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
@@ -5214,16 +5257,16 @@
         <v>13.33</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE20" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5231,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" s="2">
         <v>12</v>
@@ -5270,16 +5313,16 @@
         <v>15.03</v>
       </c>
       <c r="O21" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE21" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5287,10 +5330,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -5326,13 +5369,13 @@
         <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC22" s="2">
         <v>3</v>
@@ -5346,10 +5389,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D23" s="2">
         <v>4</v>
@@ -5385,13 +5428,13 @@
         <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="61.2" customHeight="1">
@@ -5399,10 +5442,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5438,13 +5481,13 @@
         <v>13.6</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC24" s="2">
         <v>0</v>
@@ -5453,7 +5496,7 @@
         <v>2</v>
       </c>
       <c r="AE24" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="30.6" customHeight="1">
@@ -5461,10 +5504,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2">
         <v>1.5</v>
@@ -5503,10 +5546,10 @@
         <v>68</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC25" s="2">
         <v>1</v>
@@ -5520,10 +5563,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D26" s="2">
         <v>2.5</v>
@@ -5562,10 +5605,10 @@
         <v>68</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -5573,10 +5616,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5615,10 +5658,10 @@
         <v>45</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC27" s="2">
         <v>28</v>
@@ -5627,7 +5670,7 @@
         <v>25</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="132.6" customHeight="1">
@@ -5635,10 +5678,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
@@ -5677,13 +5720,13 @@
         <v>45</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -5691,10 +5734,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
@@ -5730,13 +5773,13 @@
         <v>0.41</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC29" s="2">
         <v>6</v>
@@ -5745,7 +5788,7 @@
         <v>8</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -5753,10 +5796,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
@@ -5792,16 +5835,16 @@
         <v>0.33</v>
       </c>
       <c r="O30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE30" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE30" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -5809,10 +5852,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D31" s="2">
         <v>12</v>
@@ -5848,16 +5891,16 @@
         <v>0.4</v>
       </c>
       <c r="O31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE31" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5865,10 +5908,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D32" s="2">
         <v>18</v>
@@ -5904,16 +5947,16 @@
         <v>0.35</v>
       </c>
       <c r="O32" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE32" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE32" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -5921,10 +5964,10 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -5960,16 +6003,16 @@
         <v>0.43</v>
       </c>
       <c r="O33" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE33" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE33" s="2" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="51">
@@ -5977,10 +6020,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -6016,13 +6059,13 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -6031,7 +6074,7 @@
         <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -6066,46 +6109,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -6113,43 +6156,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6157,43 +6200,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6201,43 +6244,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6245,43 +6288,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6289,43 +6332,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6333,43 +6376,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>268</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6377,43 +6420,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6421,43 +6464,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6465,43 +6508,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6509,43 +6552,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6553,43 +6596,43 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6597,43 +6640,43 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -6641,43 +6684,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="204">
@@ -6685,43 +6728,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="91.8">
@@ -6729,43 +6772,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -6788,19 +6831,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="C1" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6808,16 +6851,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6825,19 +6868,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6845,16 +6888,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6862,16 +6905,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>468</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6879,19 +6922,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>535</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6899,16 +6942,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6916,16 +6959,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6933,16 +6976,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6950,16 +6993,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>454</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6967,16 +7010,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6984,16 +7027,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>458</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7001,16 +7044,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>456</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7018,16 +7061,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7035,16 +7078,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>408</v>
-      </c>
       <c r="D15" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7052,16 +7095,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7069,16 +7112,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7086,16 +7129,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>416</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7103,16 +7146,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7120,16 +7163,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7137,16 +7180,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7154,16 +7197,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7171,16 +7214,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>436</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7188,16 +7231,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7205,16 +7248,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>441</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7222,16 +7265,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7239,16 +7282,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>449</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7256,16 +7299,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7273,19 +7316,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>533</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>535</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7293,114 +7336,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -7420,20 +7463,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7441,7 +7484,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7449,7 +7492,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7457,7 +7500,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7465,7 +7508,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7473,7 +7516,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7481,7 +7524,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7489,7 +7532,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7497,7 +7540,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7505,7 +7548,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7513,7 +7556,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7521,7 +7564,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7529,7 +7572,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7537,7 +7580,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7545,7 +7588,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7553,7 +7596,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7561,7 +7604,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7569,7 +7612,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7577,7 +7620,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7585,7 +7628,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7593,15 +7636,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7609,7 +7652,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAC87B2-1424-4D2E-86DB-8ED8D7AEECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06835C2A-A63C-4F86-B73F-54C6BD8C68DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15372" yWindow="156" windowWidth="15408" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="558">
   <si>
     <t>Study_ID</t>
   </si>
@@ -720,10 +720,6 @@
   </si>
   <si>
     <t>D5 Justification</t>
-  </si>
-  <si>
-    <t>Overall
-(Low/Some/High)</t>
   </si>
   <si>
     <t>Overall Justification</t>
@@ -1248,16 +1244,6 @@
   </si>
   <si>
     <t>dose_intensity_total</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>intent
-prevention (indicated) / treatment (diagnosed or clinically referred)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>depression_role
-primary / secondary</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2115,19 +2101,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Primary</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Traditional</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Participants and intervention providers necessarily unblinded due to nature of conditions (book vs. brochure vs. group); three conditions differed significantly on perceived credibility, expected benefit, and satisfaction (all p &lt; .001); however, ITT analysis using multiple imputation (20 datasets, fully conditional specification) was applied for continuous outcomes, and rates of adjunctive mental health treatment did not differ across conditions during follow-up.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Indicated Prevention</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2236,6 +2214,18 @@
     <t>cr+ps+ist</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>depression_role</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>clinical_sub</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2244,7 +2234,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2334,6 +2324,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2355,7 +2352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2392,6 +2389,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2710,9 +2710,9 @@
     <col min="30" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="51">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2762,14 +2762,14 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>369</v>
+      <c r="R1" s="17" t="s">
+        <v>368</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -2777,11 +2777,11 @@
       <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>370</v>
+      <c r="W1" s="17" t="s">
+        <v>556</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>371</v>
+        <v>555</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -2840,7 +2840,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2860,8 +2860,11 @@
       <c r="V2" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="X2" s="2">
+        <v>0</v>
+      </c>
       <c r="Y2" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>36</v>
@@ -2881,7 +2884,7 @@
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -2902,7 +2905,7 @@
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>43</v>
@@ -2917,10 +2920,10 @@
         <v>46</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>47</v>
@@ -2937,8 +2940,11 @@
       <c r="V3" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="X3" s="2">
+        <v>1</v>
+      </c>
       <c r="Y3" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>36</v>
@@ -2947,7 +2953,7 @@
         <v>49</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="40.799999999999997" customHeight="1">
@@ -2976,10 +2982,10 @@
         <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>54</v>
@@ -2994,7 +3000,7 @@
         <v>57</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>58</v>
@@ -3014,6 +3020,9 @@
       <c r="V4" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X4" s="2">
+        <v>1</v>
+      </c>
       <c r="Y4" s="2" t="s">
         <v>61</v>
       </c>
@@ -3024,7 +3033,7 @@
         <v>62</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="61.2" customHeight="1">
@@ -3056,7 +3065,7 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>66</v>
@@ -3071,7 +3080,7 @@
         <v>69</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>58</v>
@@ -3091,14 +3100,17 @@
       <c r="V5" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X5" s="2">
+        <v>1</v>
+      </c>
       <c r="Y5" s="2" t="s">
         <v>61</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>72</v>
@@ -3168,6 +3180,9 @@
       <c r="V6" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="X6" s="2">
+        <v>1</v>
+      </c>
       <c r="Y6" s="2" t="s">
         <v>83</v>
       </c>
@@ -3245,6 +3260,9 @@
       <c r="V7" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="X7" s="2">
+        <v>1</v>
+      </c>
       <c r="Y7" s="2" t="s">
         <v>83</v>
       </c>
@@ -3299,10 +3317,10 @@
         <v>104</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>94</v>
@@ -3321,6 +3339,9 @@
       </c>
       <c r="V8" s="2" t="s">
         <v>35</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>61</v>
@@ -3399,6 +3420,9 @@
       <c r="V9" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="X9" s="2">
+        <v>1</v>
+      </c>
       <c r="Y9" s="2" t="s">
         <v>61</v>
       </c>
@@ -3453,7 +3477,7 @@
         <v>69</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>32</v>
@@ -3473,8 +3497,11 @@
       <c r="V10" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X10" s="2">
+        <v>1</v>
+      </c>
       <c r="Y10" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>36</v>
@@ -3497,7 +3524,7 @@
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>124</v>
@@ -3512,7 +3539,7 @@
         <v>125</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
@@ -3530,7 +3557,7 @@
         <v>92</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>94</v>
@@ -3550,8 +3577,11 @@
       <c r="V11" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
       <c r="Y11" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>36</v>
@@ -3574,7 +3604,7 @@
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>133</v>
@@ -3586,13 +3616,13 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>43</v>
@@ -3607,10 +3637,10 @@
         <v>136</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>137</v>
@@ -3627,8 +3657,11 @@
       <c r="V12" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X12" s="2">
+        <v>1</v>
+      </c>
       <c r="Y12" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>36</v>
@@ -3645,7 +3678,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -3707,14 +3740,17 @@
       <c r="V13" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X13" s="2">
+        <v>1</v>
+      </c>
       <c r="Y13" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>145</v>
@@ -3725,7 +3761,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -3743,7 +3779,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -3770,7 +3806,7 @@
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -3787,8 +3823,11 @@
       <c r="V14" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X14" s="2">
+        <v>1</v>
+      </c>
       <c r="Y14" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>36</v>
@@ -3814,7 +3853,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3835,7 +3874,7 @@
         <v>153</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>154</v>
@@ -3853,7 +3892,7 @@
         <v>156</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="S15" s="2">
         <v>1</v>
@@ -3867,11 +3906,11 @@
       <c r="V15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="W15" s="2" t="s">
-        <v>547</v>
+      <c r="X15" s="2">
+        <v>1</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>36</v>
@@ -3880,7 +3919,7 @@
         <v>157</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="142.80000000000001">
@@ -3888,16 +3927,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3906,7 +3945,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -3915,28 +3954,28 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="O16" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="S16" s="2">
         <v>1</v>
@@ -3945,28 +3984,25 @@
         <v>5</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>544</v>
+        <v>508</v>
+      </c>
+      <c r="X16" s="2">
+        <v>1</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -4073,43 +4109,43 @@
         <v>172</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="V1" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="X1" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -4150,7 +4186,7 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>175</v>
@@ -4218,10 +4254,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4304,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4360,7 +4396,7 @@
         <v>180</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4472,7 +4508,7 @@
         <v>180</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4572,10 +4608,10 @@
         <v>68</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4728,7 +4764,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>174</v>
@@ -4790,7 +4826,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>177</v>
@@ -5006,10 +5042,10 @@
         <v>111</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="X16" s="2">
         <v>-0.56999999999999995</v>
@@ -5077,10 +5113,10 @@
         <v>111</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="X17" s="2">
         <v>-0.45</v>
@@ -5369,7 +5405,7 @@
         <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>180</v>
@@ -5428,7 +5464,7 @@
         <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>180</v>
@@ -5566,7 +5602,7 @@
         <v>205</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="D26" s="2">
         <v>2.5</v>
@@ -5734,7 +5770,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>174</v>
@@ -5776,7 +5812,7 @@
         <v>209</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>180</v>
@@ -5796,7 +5832,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>177</v>
@@ -5838,7 +5874,7 @@
         <v>209</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Q30" s="2" t="s">
         <v>180</v>
@@ -5894,7 +5930,7 @@
         <v>209</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>180</v>
@@ -5950,7 +5986,7 @@
         <v>209</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="Q32" s="2" t="s">
         <v>180</v>
@@ -6006,7 +6042,7 @@
         <v>209</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>180</v>
@@ -6020,10 +6056,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -6059,13 +6095,13 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -6074,7 +6110,7 @@
         <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -6109,7 +6145,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>213</v>
@@ -6145,10 +6181,10 @@
         <v>223</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -6156,43 +6192,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6200,43 +6236,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6244,43 +6280,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6288,43 +6324,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6332,43 +6368,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6376,43 +6412,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>267</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6420,43 +6456,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6464,43 +6500,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6508,43 +6544,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6552,43 +6588,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6596,43 +6632,43 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6640,43 +6676,43 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -6684,43 +6720,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="204">
@@ -6728,43 +6764,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="91.8">
@@ -6772,43 +6808,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="I16" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -6837,13 +6873,13 @@
         <v>213</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6851,16 +6887,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6868,19 +6904,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6888,16 +6924,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6905,16 +6941,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6922,19 +6958,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6942,16 +6978,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6959,16 +6995,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6976,16 +7012,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6993,16 +7029,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7010,16 +7046,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7027,16 +7063,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7044,16 +7080,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7061,16 +7097,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>404</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7078,16 +7114,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7095,16 +7131,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7112,16 +7148,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7129,16 +7165,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7146,16 +7182,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7163,16 +7199,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7180,16 +7216,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7197,16 +7233,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7214,16 +7250,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7231,16 +7267,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7248,16 +7284,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7265,16 +7301,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7282,16 +7318,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7299,16 +7335,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7316,19 +7352,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C29" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7336,114 +7372,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7463,20 +7499,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7484,7 +7520,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7492,7 +7528,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7500,7 +7536,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7508,7 +7544,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7516,7 +7552,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7524,7 +7560,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7532,7 +7568,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7540,7 +7576,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7548,7 +7584,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7556,7 +7592,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7564,7 +7600,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7572,7 +7608,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7580,7 +7616,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7588,7 +7624,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7596,7 +7632,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7604,7 +7640,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7612,7 +7648,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7620,7 +7656,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7628,7 +7664,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7636,15 +7672,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7652,7 +7688,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06835C2A-A63C-4F86-B73F-54C6BD8C68DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86911B9E-70C7-4058-A8D2-33FE074E0AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15372" yWindow="156" windowWidth="15408" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -453,9 +453,6 @@
   </si>
   <si>
     <t>cr+ba+ps+ist+pe+hw+rp</t>
-  </si>
-  <si>
-    <t>8 sessions, 8 weeks</t>
   </si>
   <si>
     <t>Guy's &amp; St Thomas' Charity, London (G100111)</t>
@@ -2224,6 +2221,10 @@
   </si>
   <si>
     <t>Overall</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 sessions, 8 weeks (× 30–45 min)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2712,7 +2713,7 @@
   <sheetData>
     <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2763,13 +2764,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -2778,10 +2779,10 @@
         <v>18</v>
       </c>
       <c r="W1" s="17" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>19</v>
@@ -2840,7 +2841,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2864,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>36</v>
@@ -2884,7 +2885,7 @@
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
@@ -2905,7 +2906,7 @@
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>43</v>
@@ -2920,10 +2921,10 @@
         <v>46</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>47</v>
@@ -2944,7 +2945,7 @@
         <v>1</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>36</v>
@@ -2953,7 +2954,7 @@
         <v>49</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="40.799999999999997" customHeight="1">
@@ -2982,10 +2983,10 @@
         <v>53</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>54</v>
@@ -3000,7 +3001,7 @@
         <v>57</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>58</v>
@@ -3033,7 +3034,7 @@
         <v>62</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="61.2" customHeight="1">
@@ -3065,7 +3066,7 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>66</v>
@@ -3080,7 +3081,7 @@
         <v>69</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>58</v>
@@ -3107,10 +3108,10 @@
         <v>61</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>72</v>
@@ -3317,10 +3318,10 @@
         <v>104</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>94</v>
@@ -3477,7 +3478,7 @@
         <v>69</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>32</v>
@@ -3501,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>36</v>
@@ -3524,7 +3525,7 @@
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>124</v>
@@ -3539,7 +3540,7 @@
         <v>125</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
@@ -3557,7 +3558,7 @@
         <v>92</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>94</v>
@@ -3581,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>36</v>
@@ -3604,7 +3605,7 @@
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>133</v>
@@ -3616,13 +3617,13 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>43</v>
@@ -3637,13 +3638,13 @@
         <v>136</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>137</v>
+        <v>557</v>
       </c>
       <c r="S12" s="2">
         <v>0</v>
@@ -3661,16 +3662,16 @@
         <v>1</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="105.6" customHeight="1">
@@ -3678,7 +3679,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -3687,7 +3688,7 @@
         <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F13" s="2">
         <v>17</v>
@@ -3705,16 +3706,16 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>79</v>
@@ -3723,7 +3724,7 @@
         <v>32</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R13" s="2">
         <v>21</v>
@@ -3744,16 +3745,16 @@
         <v>1</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="153" customHeight="1">
@@ -3761,7 +3762,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -3779,7 +3780,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -3788,10 +3789,10 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
@@ -3800,13 +3801,13 @@
         <v>136</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -3827,16 +3828,16 @@
         <v>1</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="204">
@@ -3844,7 +3845,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -3853,7 +3854,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3862,7 +3863,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -3871,16 +3872,16 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>93</v>
@@ -3889,10 +3890,10 @@
         <v>58</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="S15" s="2">
         <v>1</v>
@@ -3910,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>36</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="142.80000000000001">
@@ -3927,16 +3928,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3945,7 +3946,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -3954,28 +3955,28 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="O16" s="16" t="s">
         <v>503</v>
       </c>
-      <c r="O16" s="16" t="s">
+      <c r="P16" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="R16" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="S16" s="2">
         <v>1</v>
@@ -3984,25 +3985,25 @@
         <v>5</v>
       </c>
       <c r="U16" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="X16" s="2">
         <v>1</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -4064,88 +4065,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="X1" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -4156,10 +4157,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -4186,10 +4187,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -4216,7 +4217,7 @@
         <v>15</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -4224,10 +4225,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -4254,10 +4255,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4278,7 +4279,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4286,10 +4287,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -4328,10 +4329,10 @@
         <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -4340,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4348,10 +4349,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -4390,13 +4391,13 @@
         <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4404,10 +4405,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -4446,13 +4447,13 @@
         <v>45</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4460,10 +4461,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -4502,13 +4503,13 @@
         <v>45</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4516,10 +4517,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4558,10 +4559,10 @@
         <v>56</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -4570,7 +4571,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4578,10 +4579,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4608,10 +4609,10 @@
         <v>68</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4638,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4646,10 +4647,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4688,10 +4689,10 @@
         <v>56</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -4700,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4708,10 +4709,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -4750,13 +4751,13 @@
         <v>56</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4764,10 +4765,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -4806,10 +4807,10 @@
         <v>91</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC12" s="2">
         <v>15</v>
@@ -4818,7 +4819,7 @@
         <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -4826,10 +4827,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4868,13 +4869,13 @@
         <v>91</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -4882,10 +4883,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4924,10 +4925,10 @@
         <v>111</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -4936,7 +4937,7 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -4944,10 +4945,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -4986,13 +4987,13 @@
         <v>111</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -5000,10 +5001,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D16" s="2">
         <v>1.5</v>
@@ -5042,10 +5043,10 @@
         <v>111</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="X16" s="2">
         <v>-0.56999999999999995</v>
@@ -5063,7 +5064,7 @@
         <v>36</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="30.6" customHeight="1">
@@ -5071,10 +5072,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -5113,10 +5114,10 @@
         <v>111</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="X17" s="2">
         <v>-0.45</v>
@@ -5128,7 +5129,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5136,10 +5137,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -5175,13 +5176,13 @@
         <v>12.56</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC18" s="2">
         <v>4</v>
@@ -5190,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5198,10 +5199,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -5237,16 +5238,16 @@
         <v>13.04</v>
       </c>
       <c r="O19" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE19" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE19" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5254,10 +5255,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
@@ -5293,16 +5294,16 @@
         <v>13.33</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE20" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5310,10 +5311,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D21" s="2">
         <v>12</v>
@@ -5349,16 +5350,16 @@
         <v>15.03</v>
       </c>
       <c r="O21" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE21" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5366,10 +5367,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -5405,13 +5406,13 @@
         <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC22" s="2">
         <v>3</v>
@@ -5425,10 +5426,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D23" s="2">
         <v>4</v>
@@ -5464,13 +5465,13 @@
         <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="61.2" customHeight="1">
@@ -5478,10 +5479,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5520,10 +5521,10 @@
         <v>135</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC24" s="2">
         <v>0</v>
@@ -5532,7 +5533,7 @@
         <v>2</v>
       </c>
       <c r="AE24" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="30.6" customHeight="1">
@@ -5540,10 +5541,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D25" s="2">
         <v>1.5</v>
@@ -5582,10 +5583,10 @@
         <v>68</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC25" s="2">
         <v>1</v>
@@ -5599,10 +5600,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D26" s="2">
         <v>2.5</v>
@@ -5641,10 +5642,10 @@
         <v>68</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -5652,10 +5653,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5694,10 +5695,10 @@
         <v>45</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC27" s="2">
         <v>28</v>
@@ -5706,7 +5707,7 @@
         <v>25</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="132.6" customHeight="1">
@@ -5714,10 +5715,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
@@ -5756,13 +5757,13 @@
         <v>45</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -5770,10 +5771,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
@@ -5809,13 +5810,13 @@
         <v>0.41</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC29" s="2">
         <v>6</v>
@@ -5824,7 +5825,7 @@
         <v>8</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -5832,10 +5833,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
@@ -5871,16 +5872,16 @@
         <v>0.33</v>
       </c>
       <c r="O30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE30" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE30" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -5888,10 +5889,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D31" s="2">
         <v>12</v>
@@ -5927,16 +5928,16 @@
         <v>0.4</v>
       </c>
       <c r="O31" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE31" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5944,10 +5945,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D32" s="2">
         <v>18</v>
@@ -5983,16 +5984,16 @@
         <v>0.35</v>
       </c>
       <c r="O32" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE32" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE32" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -6000,10 +6001,10 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -6039,16 +6040,16 @@
         <v>0.43</v>
       </c>
       <c r="O33" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE33" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE33" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="51">
@@ -6056,10 +6057,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -6095,13 +6096,13 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -6110,7 +6111,7 @@
         <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -6145,46 +6146,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -6192,43 +6193,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6236,43 +6237,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6280,43 +6281,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6324,43 +6325,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6368,43 +6369,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6412,43 +6413,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>266</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6456,43 +6457,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6500,43 +6501,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6544,43 +6545,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6588,43 +6589,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>292</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6632,43 +6633,43 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6676,43 +6677,43 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -6720,43 +6721,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="204">
@@ -6764,43 +6765,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="I15" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="K15" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="91.8">
@@ -6808,43 +6809,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -6867,19 +6868,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="C1" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6887,16 +6888,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6904,19 +6905,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6924,16 +6925,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6941,16 +6942,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>464</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6958,19 +6959,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6978,16 +6979,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6995,16 +6996,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7012,16 +7013,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>456</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7029,16 +7030,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>450</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7046,16 +7047,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7063,16 +7064,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>454</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7080,16 +7081,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>452</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7097,16 +7098,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7114,16 +7115,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>404</v>
-      </c>
       <c r="D15" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7131,16 +7132,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7148,16 +7149,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7165,16 +7166,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>412</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7182,16 +7183,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7199,16 +7200,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7216,16 +7217,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7233,16 +7234,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7250,16 +7251,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>432</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7267,16 +7268,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7284,16 +7285,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7301,16 +7302,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>440</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7318,16 +7319,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>445</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7335,16 +7336,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7352,19 +7353,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>531</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7372,114 +7373,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7499,20 +7500,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7520,7 +7521,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7528,7 +7529,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7536,7 +7537,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7544,7 +7545,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7552,7 +7553,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7560,7 +7561,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7568,7 +7569,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7576,7 +7577,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7584,7 +7585,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7592,7 +7593,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7600,7 +7601,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7608,7 +7609,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7616,7 +7617,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7624,7 +7625,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7632,7 +7633,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7640,7 +7641,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7648,7 +7649,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7656,7 +7657,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7664,7 +7665,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7672,15 +7673,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7688,7 +7689,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86911B9E-70C7-4058-A8D2-33FE074E0AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C419CE-D2DF-4458-964F-915E97A74F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15312" yWindow="0" windowWidth="15408" windowHeight="18480" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="559">
   <si>
     <t>Study_ID</t>
   </si>
@@ -157,9 +157,6 @@
 2. MFQ is a continuous symptom measure; no official universal severity categories/cut-points are prescribed. Study-specific cutoffs may be used.</t>
   </si>
   <si>
-    <t>Stice et al.</t>
-  </si>
-  <si>
     <t>US</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
   </si>
   <si>
     <t>cr+ps+hw+rp+rx</t>
-  </si>
-  <si>
-    <t>24/7 access (bibliotherapy)</t>
   </si>
   <si>
     <t>Biblio</t>
@@ -401,9 +395,6 @@
     <t>11–16</t>
   </si>
   <si>
-    <t>Girls had to score at or above the 70th percentile on depressive symptoms within the sample (RADS-2 score ≥ 59)</t>
-  </si>
-  <si>
     <t>7 levels, ~20–40 min/level, 7 weeks</t>
   </si>
   <si>
@@ -413,9 +404,6 @@
     <t>Inclusion based on sample-internal 70th percentile cutoff (RADS-2≥59) rather than published clinical cutoff (≥76); baseline M=62.61, subclinical range; flagged for sensitivity analysis</t>
   </si>
   <si>
-    <t>Ranney et al.</t>
-  </si>
-  <si>
     <t>iDove</t>
   </si>
   <si>
@@ -425,9 +413,6 @@
     <t>Clinical (Emergency Department)</t>
   </si>
   <si>
-    <t>Past-year physical peer violence (victimization or perpetration) with 5≤PHQ-9≤19</t>
-  </si>
-  <si>
     <t>1 brief in-ED intervention session + 8 weeks automated text messaging</t>
   </si>
   <si>
@@ -437,18 +422,9 @@
     <t>National Institute of Mental Health grants K23 MH095866, K24 HD062645, and K24DA027109</t>
   </si>
   <si>
-    <t>With brief in-person session</t>
-  </si>
-  <si>
-    <t>Smith et al.</t>
-  </si>
-  <si>
     <t>Stressbusters</t>
   </si>
   <si>
-    <t>MFQ-C≥ 20, students who are having severe symptoms and/or significant risk requiring immediate intervention were present were exclued</t>
-  </si>
-  <si>
     <t>MFQ-C</t>
   </si>
   <si>
@@ -464,21 +440,9 @@
     <t>The Journey</t>
   </si>
   <si>
-    <t>School (counsellor referral)</t>
-  </si>
-  <si>
-    <t>CDRS-R≥30 or RADS-2≥76; self-referred for low mood</t>
-  </si>
-  <si>
     <t xml:space="preserve">cr+ba+ps+rx+rp+hw </t>
   </si>
   <si>
-    <t>7 modules, ~25–30 min/module, 4–10 weeks</t>
-  </si>
-  <si>
-    <t>Double-blind placebo-controlled; control=CPE (computerized psychoeducation, matched for length/format); ANCOVA with LOCF; ES calculated as d=(mean change cCBT − mean change CPE)/√error MS</t>
-  </si>
-  <si>
     <t>Clinical（CAMHS primary mental health workers）</t>
   </si>
   <si>
@@ -491,12 +455,6 @@
     <t>NIHR Research for Patient Benefit (PB-PG-0609-19295)</t>
   </si>
   <si>
-    <t>Wright et al. (2017) and Wright et al. (2020) are overlapping reports from the same Stressbusters RCT programme (ISRCTN31219579). The 2017 paper reports feasibility results and 4-month outcomes for the initial phase (n=91); the 2020 paper presents a combined analysis of both phases (n=139) with 4- and 12-month follow-up. Quantitative data extracted from Wright et al. (2020) only to avoid double-counting. Wright et al. (2017) retained as a supplementary report for feasibility and process information.</t>
-  </si>
-  <si>
-    <t>Rohde et al.</t>
-  </si>
-  <si>
     <t>13-19</t>
   </si>
   <si>
@@ -504,12 +462,6 @@
   </si>
   <si>
     <t>K-SADS 16-item composite</t>
-  </si>
-  <si>
-    <t>cr+ba+ps+pe+hw</t>
-  </si>
-  <si>
-    <t>Self-paced (book); 2 reminder phone calls</t>
   </si>
   <si>
     <t>NIMH R01 MH079164</t>
@@ -879,10 +831,6 @@
   </si>
   <si>
     <t>No pre-registration (dissertation, 2012; pre-registration not yet standard). Multiple outcomes reported (CES-D, knowledge, ATQ, BADS, school functioning, self-efficacy). CES-D at follow-up was non-significant (p=.059) but reported transparently with effect size.</t>
-  </si>
-  <si>
-    <t>Validation of measurement: CDRS-R (Cronbach α=0.84 in study); clinician-rated.
-Who is in charge of assessment: Trained research assistants blinded to treatment allocation.</t>
   </si>
   <si>
     <t>O'Dea et al., 2020</t>
@@ -951,16 +899,7 @@
 conditionsonthedemographicvariables</t>
   </si>
   <si>
-    <t>Participants unblinded (open-label design); active monitoring control (weekly questionnaires + personalized reminders) may have introduced co-intervention effects, limiting comparability.</t>
-  </si>
-  <si>
-    <t>ITT analysis conducted with multiple imputation (20 imputations). Attrition at post-test: SPARX 25.5% (13/51) vs. control 7.8% (4/51); differential dropout may introduce bias despite ITT approach. No baseline comparison of completers vs. non-completers reported.</t>
-  </si>
-  <si>
     <t>Pre-registered (NTR3737, Dutch Trial Register); reported primary outcome (RADS-2 depressive symptoms) consistent with registration.</t>
-  </si>
-  <si>
-    <t>D2 Some concerns + D3 Some concerns → Overall: Some concerns.</t>
   </si>
   <si>
     <t>Ranney et al., 2018</t>
@@ -974,9 +913,6 @@
 Baseline balance:  No statis
 tically significant differences in the baseline characteristics between
 the intervention and control groups.</t>
-  </si>
-  <si>
-    <t>8.6% attrition at 16-week primary endpoint (10/116); no differential attrition between groups. ITT analysis using mixed-effects models with likelihood-based estimation incorporating all available data.</t>
   </si>
   <si>
     <t xml:space="preserve">Outcome assessed via validated self-report (BDI-2; α = .92–.93); not susceptible to assessor bias.
@@ -1000,65 +936,28 @@
 the intervention and control groups.</t>
   </si>
   <si>
-    <t>Participants unblinded to group assignment. No evidence of contamination or active co-intervention reported.</t>
-  </si>
-  <si>
     <t>1.8% attrition at post (N=110/112); MLE-based mixed models used; missing data minimal</t>
   </si>
   <si>
-    <t>Validated self-report (MFQ-C, α=0.90); measurement not dependent on assessor blinding</t>
-  </si>
-  <si>
     <t>Pre-registered (ISRCTN83507297); primary outcome (MFQ-C) reported as pre-specified</t>
   </si>
   <si>
-    <t xml:space="preserve"> D2 Some concerns due to open-label waitlist design (participants unblinded); all other domains Low.</t>
-  </si>
-  <si>
     <t>Stasiak et al., 2014</t>
   </si>
   <si>
-    <t>Computer-generated randomization; sealed opaque envelopes prepared by uninvolved colleague; baseline broadly balanced.</t>
-  </si>
-  <si>
     <t>ITT with LOCF; completion 94% cCBT / 82% CPE; overall attrition ≤20%, balanced across arms.</t>
   </si>
   <si>
     <t>Assessors are blind to allocation. Validation of measurement: CDRS-R (Cronbach α=0.84 in study.</t>
   </si>
   <si>
-    <t>Registered (ACTRN12606000142538); outcomes consistent with methods.</t>
-  </si>
-  <si>
-    <t>Driven by D2..</t>
-  </si>
-  <si>
     <t>Wright et al., 2020</t>
   </si>
   <si>
-    <t>Remote computerised allocation by University of York Trials Unit; baseline balanced.</t>
-  </si>
-  <si>
-    <t>Validated self-report measures (BDI, MFQ); no assessor bias.</t>
-  </si>
-  <si>
     <t>Pre-registered (ISRCTN31219579); outcomes consistent with registration.</t>
   </si>
   <si>
-    <t>Driven by D3.</t>
-  </si>
-  <si>
     <t>Rohde et al., 2015</t>
-  </si>
-  <si>
-    <t>Randomization process: Computer-generated random numbers, blocked by gender and school; assigned by project coordinator.
-Allocation concealment: Not explicitly described.
-Baseline balance: No significant differences on demographics or outcomes at pretest. Conditions differed on perceived credibility/expectancy (p&lt;.001) — post-randomization, adjusted as covariate.</t>
-  </si>
-  <si>
-    <t>Attrition: 7% at 1-yr, 10% at 18-mo, 12% at 2-yr; did not differ by condition.
-Method for handling missing data: Multiple imputation (20 datasets via IVEWare; Rubin's rules) for continuous outcomes; right-censoring for survival models.
-Differences between completers/non-completers: Higher baseline substance use associated with attrition (secondary outcome only, not depression).</t>
   </si>
   <si>
     <t>No pre-registration mentioned in this report (effectiveness trial conducted 2009-2011; pre-registration not yet uniformly standard). Multiple outcomes reported (MDD onset, depressive symptoms, social adjustment, substance use); no obvious selective reporting. Moderation analyses focused on baseline depressive symptoms (other 7 baseline factors tested in companion paper Brière et al. 2014).</t>
@@ -1676,110 +1575,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">CES-D-based 1-page screener: endorsed </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2 items; current MDD &amp; acute SI excluded</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Effectiveness trial; sister report Rohde et al. 2014 (J Consult Clin Psychol) covers post+6mo, 2015 covers 12/18/24mo follow-up — same RCT (N=378, three arms: CB group / CB bibliotherapy / brochure).
-2. Only CB bibliotherapy arm (n=128) vs. brochure control (n=124) extracted; CB group arm excluded as therapist-led (not unguided self-help).
-3. K-SADS 16-item DSM-IV symptom composite is a study-specific averaged-4-point scale, not a standard validated symptom measure </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> flag for sensitivity analysis.
-4. CES-D-based 1-page screener with non-standard cutoff (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">2 items endorsed), not full CES-D </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>≥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> flag.
-5. Baseline differed on credibility/expectancy across conditions (p&lt;.001); adjusted as covariate.</t>
-    </r>
-  </si>
-  <si>
     <t>Duplicates removed</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1892,7 +1687,194 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>14-18</t>
+    <t>CDI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WL (delayed treatment)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ind</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Biblio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Journal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>post</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Completer data from Table 2. Immediate-treatment group: Time 1 to Time 2 after 4-week bibliotherapy; delayed-treatment group: Time 1 to Time 2 waiting period. No eligible randomized comparative follow-up because delayed group received treatment after Time 2.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ackerson et al., 1998</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random assignment to immediate-treatment vs delayed-treatment conditions reported, but sequence generation and allocation concealment were not described; baseline comparisons showed no significant group differences.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Depressive symptoms were assessed with validated measures (CDI, HRSD, CBCL-D), but assessors/participants were not reported as blinded; self-report and clinician-rated outcomes may be affected by open-label allocation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assessment-only</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAU</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WL (active monitoring)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Some concerns</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control; counsellor blinding not formally verified; 22.2% cCBT participants guessed allocation correctly. Low co-intervention risk given purely self-help format.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Attention control.No evidence of contamination or active co-intervention reported.
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merry et al., 2012</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The effectiveness of SPARX, a computerised self help
+intervention for adolescents seeking help for
+depression: randomisedcontrolled non-inferiority trial</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>No inactive control (WL/TAU)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The control group is under active intervention: school-based CBT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The control group is under active intervention: face-to-face</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15  (= 14 + 1)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Some concerns across D1 (sequence generation and allocation concealment not described; post-randomization exclusion),  D3 (differential attrition, though handled with EM imputation), and D5 (no pre-registration). D4 low risk (computer-based self-report). No single domain reaches High risk.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>School/hospital/advertisement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Study ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Participants and intervention providers necessarily unblinded due to nature of conditions (book vs. brochure vs. group); three conditions differed significantly on perceived credibility, expected benefit, and satisfaction (all p &lt; .001); however, ITT analysis using multiple imputation (20 datasets, fully conditional specification) was applied for continuous outcomes, and rates of adjunctive mental health treatment did not differ across conditions during follow-up.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>~40% attrition at 12 months (59.4% / 58.7% completion); no completers vs. non-completers analysis reported.Although the primary analysis was described as intention-to-treat and used covariance pattern mixed models to handle repeated measures, participants were included only if they had complete baseline data and at least one post-randomisation outcome. Thus, participants with no follow-up outcome data were excluded from the model. The mixed-model approach relies on assumptions about the missing-data mechanism, and insufficient information was provided to rule out outcome-dependent missingness.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 sessions × 30–45 min</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2008 &amp; 2010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makarushka 2011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makarushka, 2011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-18</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-16</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010 paper Table</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rohde 2015</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fu_1mo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ps+ist</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>depression_role</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 sessions, 8 weeks (× 30–45 min)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 access </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stice et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>initial_screening</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1933,176 +1915,148 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>10; grades 7–12; living at home with parent/guardian; no psychotic or suicidal symptoms; not in psychotherapy</t>
+      <t>10; grades 7–12; living at home with parent/guardian; no psychotic or suicidal symptoms; not in psychotherapy; reading level above a 6th-grade equivalence</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>CDI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>cr+ps+hw+rp+rx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WL (delayed treatment)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Human</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>4 weeks; self-administered bibliotherapy; weekly monitoring calls</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ind</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Biblio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Journal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>post</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Completer data from Table 2. Immediate-treatment group: Time 1 to Time 2 after 4-week bibliotherapy; delayed-treatment group: Time 1 to Time 2 waiting period. No eligible randomized comparative follow-up because delayed group received treatment after Time 2.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ackerson et al., 1998</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Random assignment to immediate-treatment vs delayed-treatment conditions reported, but sequence generation and allocation concealment were not described; baseline comparisons showed no significant group differences.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Open-label bibliotherapy vs delayed-treatment design; participants and researchers were aware of allocation. Weekly calls were made in both groups, and the paper states that counseling was not provided.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>8/30 randomized participants dropped out (26.7%; immediate 3/15=20%, delayed 5/15=33.3%). Analyses were based on 22 completers; no ITT or imputation was reported.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Depressive symptoms were assessed with validated measures (CDI, HRSD, CBCL-D), but assessors/participants were not reported as blinded; self-report and clinician-rated outcomes may be affected by open-label allocation.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>No trial registration or published protocol was reported; multiple depression outcomes were reported (CDI, HRSD, CBCL-D), and a primary outcome was not clearly pre-specified.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overall high risk, driven primarily by missing outcome data and completer-only analysis; additional concerns relate to unclear allocation concealment, open-label design, and lack of pre-registration.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assessment-only</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WL</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TAU</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WL (active monitoring)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attention control</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Some concerns</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attention control (self-help websites); researcher present but provided no therapy; structural asymmetry between arms (homework vs. none).</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attention control; counsellor blinding not formally verified; 22.2% cCBT participants guessed allocation correctly. Low co-intervention risk given purely self-help format.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Attention control.No evidence of contamination or active co-intervention reported.
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Merry et al., 2012</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>The effectiveness of SPARX, a computerised self help
-intervention for adolescents seeking help for
-depression: randomisedcontrolled non-inferiority trial</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>No inactive control (WL/TAU)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>The control group is under active intervention: school-based CBT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>The control group is under active intervention: face-to-face</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>15  (= 14 + 1)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>D5 Some concerns → Overall: Some concerns</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Some concerns across D1 (sequence generation and allocation concealment not described; post-randomization exclusion),  D3 (differential attrition, though handled with EM imputation), and D5 (no pre-registration). D4 low risk (computer-based self-report). No single domain reaches High risk.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>22 completers from 30 randomized (likely 15/15 by condition). Effect-size row uses completer data from Table 2. Weekly calls monitored pages/exercises only; counseling was not provided. No eligible comparative follow-up because the delayed-treatment group received the intervention after the waiting period. Component coding follows the existing Feeling Good bibliotherapy coding in this workbook; the paper itself provides limited component detail. 
-Although the inclusion citeria didn't meet the cut-off of the CDI, the baseline score had excceed the cut-off.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>School/hospital/advertisement</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Study ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Traditional</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Participants and intervention providers necessarily unblinded due to nature of conditions (book vs. brochure vs. group); three conditions differed significantly on perceived credibility, expected benefit, and satisfaction (all p &lt; .001); however, ITT analysis using multiple imputation (20 datasets, fully conditional specification) was applied for continuous outcomes, and rates of adjunctive mental health treatment did not differ across conditions during follow-up.</t>
+    <t>14-18 (inferred from the article)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">22 completers from 30 randomized (likely 15/15 by condition). Effect-size row uses completer data from Table 2. Weekly calls monitored pages/exercises only. No eligible comparative follow-up because the delayed-treatment group received the intervention after the waiting period. Component coding follows the existing Feeling Good bibliotherapy coding in this workbook; the paper itself provides limited component detail. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+pe+hw+rp+ist</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 weeks; self-paced; weekly monitoring calls</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Open-label bibliotherapy vs delayed-treatment design; participants and researchers were aware of allocation. Weekly calls were made in both groups, and the paper states that counseling was not provided; completer analysis;  the study noted that noncompleters had significantly lower reading ability, which could bias the results in favor of the treatment</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/30 randomized participants dropped out (26.7%; immediate 3/15=20%, delayed 5/15=33.3%). Analyses were based on 22 completers; no ITT or imputation was reported;  the study noted that noncompleters had significantly lower reading ability, which could bias the results in favor of the treatment</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">No trial registration or published protocol was reported; multiple depression outcomes were reported (CDI, HRSD, CBCL-D), and a primary outcome was not clearly pre-specified. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overall high risk, driven primarily by missing outcome data and completer-only analysis; additional concerns relate to unclear allocation concealment, open-label design.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CES-D-based 1-page screener: endorsed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2 items; current MDD &amp; acute SI excluded; written consent from gaurdians and paricipants</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>indicated_prevention</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 weeks, self-paced (book); 2 reminder phone calls, only for pure encouragement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. Effectiveness trial; sister report Rohde et al. 2014 (J Consult Clin Psychol) covers post+6mo, 2015 covers 12/18/24mo follow-up — same RCT (N=378, three arms: CB group / CB bibliotherapy / brochure).
+2. Only CB bibliotherapy arm (n=128) vs. brochure control (n=124) extracted; CB group arm excluded as therapist-led (not unguided self-help).
+3. K-SADS 16-item DSM-IV symptom composite is a study-specific averaged-4-point scale, not a standard validated symptom measure 
+4. CES-D-based 1-page screener with non-standard cutoff (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2 items endorsed), not full CES-D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> flag.
+5. Baseline differed on credibility/expectancy across conditions (p&lt;.001); adjusted as covariate.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Randomization process: Computer-generated random numbers, blocked by gender and school; assigned by project coordinator.
+Allocation concealment: conducted by project coordinator
+Baseline balance: No significant differences on demographics or outcomes at pretest. Conditions differed on perceived credibility/expectancy (p&lt;.001) — post-randomization, adjusted as covariate.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attrition: 7% at 1-yr, 10% at 18-mo, 12% at 2-yr; did not differ by condition.
+Method for handling missing data: Multiple imputation (20 datasets via IVEWare; Rubin's rules) for continuous outcomes; right-censoring for survival models.
+Differences between completers/non-completers: Higher baseline substance use associated with attrition (secondary outcome only, not depression).</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2163,68 +2117,346 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.80 maintained.</t>
+      <t>.80 maintained. Justification for self-report</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>~40% attrition at 12 months (59.4% / 58.7% completion); no completers vs. non-completers analysis reported.Although the primary analysis was described as intention-to-treat and used covariance pattern mixed models to handle repeated measures, participants were included only if they had complete baseline data and at least one post-randomisation outcome. Thus, participants with no follow-up outcome data were excluded from the model. The mixed-model approach relies on assumptions about the missing-data mechanism, and insufficient information was provided to rule out outcome-dependent missingness.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>8 sessions × 30–45 min</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2008 &amp; 2010</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Makarushka 2011</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Makarushka, 2011</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>12-18</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>12-16</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2010 paper Table</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rohde 2015</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>fu_1mo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>cr+ps+ist</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>depression_role</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>clinical_sub</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overall</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>8 sessions, 8 weeks (× 30–45 min)</t>
+    <t>Computer-generated randomization; sealed opaque envelopes prepared by uninvolved colleague; baseline broadly balanced.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remote computerised allocation by University of York Trials Unit; baseline balanced by covariance pattern mixed model</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control (self-help websites); researcher present but provided no therapy,  structural asymmetry between arms (homework vs. none). ITT was applied, however, participants were only included in the model if they provided full data at baseline and outcome data for at least one post-randomisation time point</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validated self-report measures (BDI, MFQ); no assessor bias. In the self-reported measures, particpants are not bilnded; RA who for data collection and offering support during intervention were not bilinded to the allocation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Registered (ACTRN12606000142538); outcomes consistent with methods. Outcome was well-reported</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The primary drivers for the "High Risk" or "Some Concerns" ratings in these studies are the lack of blinding affecting the measurement of outcomes (D4) and the high attrition rates coupled with a modified Intention-to-Treat (ITT) analysis (D3).</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>School (counsellor referral within past 1 year)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CDRS-R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30 or RADS-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>76; self-referred for low mood; excluding students with high risk of suicidality; moderate-to-severe learning disorder; low ability of English and using computer; written form of consent by participants and their gaurdians</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 modules, ~25–30 min/module, 4–10 weeks; 1 weekly challenge at the end of each session</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control (computerized psycho-education)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Double-blind placebo-controlled; control=CPE (computerized psychoeducation, matched for length/format); uneven gender proportion; ANCOVA with LOCF; ES calculated as d=(mean change cCBT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mean change CPE)/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>√</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>error MS; in school setting</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MFQ-C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 20, students who are having severe symptoms and/or significant risk requiring immediate intervention or having learning disability that might interfere with the intervention were exclued; written</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>from</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>gaurdians</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>paricipants</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rohde et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wright et al. (2017) and Wright et al. (2020) are overlapping reports from the same Stressbusters RCT programme (ISRCTN31219579). The 2017 paper reports feasibility results and 4-month outcomes for the initial phase (n=91); the 2020 paper presents a combined analysis of both phases (n=139) with 4- and 12-month follow-up. Quantitative data extracted from Wright et al. (2020) only to avoid double-counting. Wright et al. (2017) retained as a supplementary report for feasibility and process information.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smith et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>With brief in-person session</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Only the post-treatment assessment represents a true randomized controlled comparison. The 3- and 6-month follow-ups included only the Stressbusters group; the waiting-list group was offered Stressbusters after the waiting period, so these later follow-up data cannot be treated as comparative exp-versus-control follow-up outcomes.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Participants unblinded to group assignment. No evidence of contamination or active co-intervention reported. While low contamination were reported</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validated self-report (MFQ-C, α=0.90); measurement not dependent on assessor blinding; despite the aforementioned risks, the study findings demonstrated a consistent trend of improvement across multiple informants (both adolescents and parents)
+, and treatment gains were sustained throughout the 3- and 6-month follow-up periods
+, which enhances the reliability of the results</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranney et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The inclusion criteria for the study required participants to be English-speaking adolescents aged 13 to 17 who presented to the emergency department for any reason
+; had to report experiencing physical peer violence (either as a victim or a perpetrator) within the past year and demonstrate mild-to-moderate depressive symptoms, defined as a Patient Health Questionnaire-9 (PHQ-9) score between 5 and 19
+; participants were required to possess a mobile phone with text-messaging capabilities and have a parent or guardian present who was capable of providing informed consent.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Attention control </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+pe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auto</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The iDOVE pilot randomized controlled trial evaluated a digital intervention for 116 high-risk adolescents in an emergency department who reported past-year peer violence and depressive symptoms
+. The program consisted of a brief in-person session based on motivational interviewing and cognitive-behavioral therapy (CBT), followed by eight weeks of automated text messages providing tailored CBT responses based on daily mood queries
+. The study demonstrated high feasibility and acceptability, maintaining retention rates above 90 percent at the final follow-up
+. While overall group differences were not statistically significant, the intervention led to significant reductions in physical violence and improvements in depressive symptoms among the most symptomatic participants at eight weeks
+. Additionally, mood ratings at day seven were identified as a critical predictor of intervention responsiveness</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D5 Some concerns → Overall: Some concerns (trial reg x)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Girls had to score at or above the 70th percentile on depressive symptoms within the sample (RADS-2 score </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 59); girls with suicidal ideation or involving in ongoing psychotherapy were excluded; have a parent or guardian present who was capable of providing informed consent</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Participants unblinded (open-label design); active monitoring control (weekly questionnaires + personalized reminders) may have introduced co-intervention effects, limiting comparability + sensitivity analysis were conducted (consitent with ITT)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ITT analysis conducted with multiple imputation (20 imputations). Attrition at post-test: SPARX 25.5% (13/51) vs. control 7.8% (4/51); differential dropout may introduce bias despite ITT approach. No baseline comparison of completers vs. non-completers reported. </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validation of measurement: CDRS-R (Cronbach α=0.84 in study); However, both the participants and the assessors were unblinded; self-reported measures</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2 Some concerns + D3 Some concerns → Overall: Some concerns. (mainly due to failure in blindness)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2235,7 +2467,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2332,6 +2564,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2353,7 +2597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2393,6 +2637,15 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2696,7 +2949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="11" width="16" style="2" customWidth="1"/>
@@ -2705,15 +2958,15 @@
     <col min="14" max="14" width="18.44140625" style="2" customWidth="1"/>
     <col min="15" max="16" width="16" style="2" customWidth="1"/>
     <col min="17" max="20" width="25" style="2" customWidth="1"/>
-    <col min="21" max="27" width="16" style="2" customWidth="1"/>
-    <col min="28" max="28" width="30" style="2" customWidth="1"/>
-    <col min="29" max="29" width="8.88671875" style="2" customWidth="1"/>
-    <col min="30" max="16384" width="8.88671875" style="2"/>
+    <col min="21" max="28" width="16" style="2" customWidth="1"/>
+    <col min="29" max="29" width="30" style="2" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" style="2" customWidth="1"/>
+    <col min="31" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
-        <v>538</v>
+        <v>492</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2764,13 +3017,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -2778,26 +3031,29 @@
       <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="17" t="s">
-        <v>555</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>554</v>
+      <c r="W1" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="X1" s="17" t="s">
+        <v>511</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="61.2" customHeight="1">
+    <row r="2" spans="1:29" ht="61.2" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2841,7 +3097,7 @@
         <v>31</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>520</v>
+        <v>478</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>32</v>
@@ -2861,37 +3117,37 @@
       <c r="V2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X2" s="2">
+      <c r="Y2" s="2">
         <v>0</v>
       </c>
-      <c r="Y2" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="Z2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="91.8" customHeight="1">
+    <row r="3" spans="1:29" ht="91.8" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="F3" s="2">
         <v>80</v>
@@ -2900,34 +3156,34 @@
         <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="2">
         <v>15.6</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="O3" s="16" t="s">
-        <v>518</v>
+        <v>476</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>47</v>
+        <v>509</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
@@ -2939,39 +3195,39 @@
         <v>34</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3" s="2">
+        <v>46</v>
+      </c>
+      <c r="Y3" s="2">
         <v>1</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="Z3" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA3" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="AB3" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" ht="40.799999999999997" customHeight="1">
+        <v>47</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2">
         <v>2023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
@@ -2980,34 +3236,34 @@
         <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>519</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="S4" s="2">
         <v>1</v>
@@ -3019,39 +3275,39 @@
         <v>34</v>
       </c>
       <c r="V4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="X4" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" ht="61.2" customHeight="1">
+      <c r="AC4" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="61.2" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2">
         <v>2012</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2">
         <v>20</v>
@@ -3060,34 +3316,34 @@
         <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2">
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="O5" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>519</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="S5" s="2">
         <v>1</v>
@@ -3099,39 +3355,39 @@
         <v>34</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X5" s="2">
+        <v>58</v>
+      </c>
+      <c r="Y5" s="2">
         <v>1</v>
       </c>
-      <c r="Y5" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="Z5" s="2" t="s">
-        <v>508</v>
+        <v>59</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>372</v>
+        <v>470</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" ht="71.400000000000006" customHeight="1">
+        <v>340</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="71.400000000000006" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>2016</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F6" s="2">
         <v>130</v>
@@ -3140,7 +3396,7 @@
         <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2">
         <v>14.63</v>
@@ -3149,25 +3405,25 @@
         <v>68.099999999999994</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="S6" s="2">
         <v>1</v>
@@ -3179,39 +3435,39 @@
         <v>34</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="X6" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="Z6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="64.8" customHeight="1">
+    </row>
+    <row r="7" spans="1:29" ht="64.8" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2">
         <v>2011</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F7" s="2">
         <v>76</v>
@@ -3220,7 +3476,7 @@
         <v>85</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2">
         <v>12.7</v>
@@ -3229,25 +3485,25 @@
         <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
@@ -3259,39 +3515,39 @@
         <v>34</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="X7" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y7" s="2">
         <v>1</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="Z7" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="51" customHeight="1">
+        <v>94</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="51" customHeight="1">
       <c r="A8" s="2">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2">
         <v>2020</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F8" s="2">
         <v>98</v>
@@ -3300,7 +3556,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2">
         <v>14.82</v>
@@ -3309,25 +3565,25 @@
         <v>86.5</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="N8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="O8" s="16" t="s">
-        <v>519</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="S8" s="2">
         <v>0</v>
@@ -3341,37 +3597,37 @@
       <c r="V8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X8" s="2">
+      <c r="Y8" s="2">
         <v>0</v>
       </c>
-      <c r="Y8" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="Z8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA8" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="AB8" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" ht="105.6" customHeight="1">
+        <v>104</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="105.6" customHeight="1">
       <c r="A9" s="2">
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2">
         <v>2025</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F9" s="2">
         <v>195</v>
@@ -3389,25 +3645,25 @@
         <v>74.2</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="O9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="S9" s="2">
         <v>0</v>
@@ -3421,34 +3677,37 @@
       <c r="V9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X9" s="2">
+      <c r="W9" s="2">
         <v>1</v>
       </c>
-      <c r="Y9" s="2" t="s">
-        <v>61</v>
+      <c r="Y9" s="2">
+        <v>1</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" ht="187.2" customHeight="1">
+        <v>112</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="187.2" customHeight="1">
       <c r="A10" s="2">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10" s="2">
         <v>2016</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2">
         <v>51</v>
@@ -3457,7 +3716,7 @@
         <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2">
         <v>13.35</v>
@@ -3466,25 +3725,25 @@
         <v>100</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>119</v>
+        <v>554</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>32</v>
+        <v>479</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>467</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="S10" s="2">
         <v>0</v>
@@ -3496,39 +3755,45 @@
         <v>34</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="W10" s="2">
+        <v>1</v>
       </c>
       <c r="X10" s="2">
         <v>1</v>
       </c>
-      <c r="Y10" s="2" t="s">
-        <v>374</v>
+      <c r="Y10" s="2">
+        <v>1</v>
       </c>
       <c r="Z10" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA10" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="AB10" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" ht="81.599999999999994" customHeight="1">
+        <v>118</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="81.599999999999994" customHeight="1">
       <c r="A11" s="2">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>547</v>
       </c>
       <c r="C11" s="2">
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F11" s="2">
         <v>58</v>
@@ -3537,34 +3802,34 @@
         <v>58</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>127</v>
+        <v>548</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>92</v>
+        <v>550</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>94</v>
+        <v>551</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="S11" s="2">
         <v>0</v>
@@ -3576,39 +3841,45 @@
         <v>34</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
+      </c>
+      <c r="W11" s="2">
+        <v>1</v>
       </c>
       <c r="X11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2">
         <v>0</v>
       </c>
-      <c r="Y11" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="Z11" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA11" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="AB11" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" ht="91.8" customHeight="1">
+        <v>125</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="91.8" customHeight="1">
       <c r="A12" s="2">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>132</v>
+      <c r="B12" s="20" t="s">
+        <v>542</v>
       </c>
       <c r="C12" s="2">
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F12" s="2">
         <v>55</v>
@@ -3617,34 +3888,34 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>549</v>
+        <v>501</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>134</v>
+        <v>539</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>519</v>
+        <v>477</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>557</v>
+        <v>508</v>
       </c>
       <c r="S12" s="2">
         <v>0</v>
@@ -3656,39 +3927,45 @@
         <v>34</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="W12" s="2">
+        <v>1</v>
       </c>
       <c r="X12" s="2">
         <v>1</v>
       </c>
-      <c r="Y12" s="2" t="s">
-        <v>375</v>
+      <c r="Y12" s="2">
+        <v>1</v>
       </c>
       <c r="Z12" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA12" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AB12" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" ht="105.6" customHeight="1">
+        <v>129</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="105.6" customHeight="1">
       <c r="A13" s="2">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>379</v>
+      <c r="B13" s="20" t="s">
+        <v>347</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F13" s="2">
         <v>17</v>
@@ -3697,7 +3974,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I13" s="2">
         <v>15.2</v>
@@ -3706,25 +3983,25 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>140</v>
+        <v>534</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>141</v>
+        <v>535</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>79</v>
+        <v>537</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>143</v>
+        <v>536</v>
       </c>
       <c r="R13" s="2">
         <v>21</v>
@@ -3739,30 +4016,36 @@
         <v>34</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="W13" s="2">
+        <v>1</v>
       </c>
       <c r="X13" s="2">
         <v>1</v>
       </c>
-      <c r="Y13" s="2" t="s">
-        <v>375</v>
+      <c r="Y13" s="2">
+        <v>1</v>
       </c>
       <c r="Z13" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA13" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="AB13" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" ht="153" customHeight="1">
+        <v>340</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="153" customHeight="1">
       <c r="A14" s="2">
         <v>14</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>378</v>
+      <c r="B14" s="5" t="s">
+        <v>346</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -3771,7 +4054,7 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F14" s="2">
         <v>70</v>
@@ -3780,7 +4063,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>548</v>
+        <v>500</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -3789,25 +4072,25 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>544</v>
+        <v>496</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -3822,39 +4105,45 @@
         <v>34</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
       </c>
       <c r="X14" s="2">
         <v>1</v>
       </c>
-      <c r="Y14" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="Z14" s="2" t="s">
+      <c r="Y14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA14" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="AB14" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" ht="204">
+        <v>136</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="295.8">
       <c r="A15" s="2">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>150</v>
+      <c r="B15" s="19" t="s">
+        <v>540</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -3863,7 +4152,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -3872,28 +4161,28 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>469</v>
+        <v>521</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>154</v>
+        <v>139</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>515</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>155</v>
+        <v>523</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="S15" s="2">
         <v>1</v>
@@ -3905,39 +4194,45 @@
         <v>34</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="W15" s="2">
+        <v>1</v>
       </c>
       <c r="X15" s="2">
         <v>1</v>
       </c>
-      <c r="Y15" s="2" t="s">
-        <v>374</v>
+      <c r="Y15" s="2">
+        <v>1</v>
       </c>
       <c r="Z15" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AA15" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="AB15" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" ht="142.80000000000001">
+        <v>140</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="102">
       <c r="A16" s="2">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -3946,7 +4241,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -3955,28 +4250,28 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>537</v>
+        <v>491</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>502</v>
+        <v>465</v>
+      </c>
+      <c r="N16" s="18" t="s">
+        <v>515</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="S16" s="2">
         <v>1</v>
@@ -3985,25 +4280,31 @@
         <v>5</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>506</v>
+        <v>468</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>507</v>
+        <v>469</v>
+      </c>
+      <c r="W16" s="2">
+        <v>1</v>
       </c>
       <c r="X16" s="2">
         <v>1</v>
       </c>
-      <c r="Y16" s="2" t="s">
-        <v>375</v>
+      <c r="Y16" s="2">
+        <v>1</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>508</v>
+        <v>343</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>372</v>
+        <v>470</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>536</v>
+        <v>340</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -4065,88 +4366,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -4157,10 +4458,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -4187,10 +4488,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -4217,7 +4518,7 @@
         <v>15</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -4225,10 +4526,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -4255,10 +4556,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4279,7 +4580,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4287,10 +4588,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -4326,13 +4627,13 @@
         <v>9.74</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -4341,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>550</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4349,10 +4650,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -4388,16 +4689,16 @@
         <v>10.93</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>550</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4405,10 +4706,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -4444,16 +4745,16 @@
         <v>10.039999999999999</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4461,10 +4762,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -4500,16 +4801,16 @@
         <v>9.44</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>550</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4517,10 +4818,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4556,13 +4857,13 @@
         <v>8.58</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -4571,7 +4872,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4579,10 +4880,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4606,13 +4907,13 @@
         <v>38.4</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4639,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4647,10 +4948,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4686,13 +4987,13 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -4701,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -4709,10 +5010,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -4748,16 +5049,16 @@
         <v>8.5</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -4765,10 +5066,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>546</v>
+        <v>498</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -4804,13 +5105,13 @@
         <v>10.09</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC12" s="2">
         <v>15</v>
@@ -4819,7 +5120,7 @@
         <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -4827,10 +5128,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>546</v>
+        <v>498</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -4866,16 +5167,16 @@
         <v>10.35</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -4883,10 +5184,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -4922,13 +5223,13 @@
         <v>7.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -4937,7 +5238,7 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -4945,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -4984,16 +5285,16 @@
         <v>7.12</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -5001,10 +5302,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D16" s="2">
         <v>1.5</v>
@@ -5040,13 +5341,13 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="X16" s="2">
         <v>-0.56999999999999995</v>
@@ -5064,7 +5365,7 @@
         <v>36</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="30.6" customHeight="1">
@@ -5072,10 +5373,10 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D17" s="2">
         <v>4</v>
@@ -5111,13 +5412,13 @@
         <v>27</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="X17" s="2">
         <v>-0.45</v>
@@ -5129,7 +5430,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5137,10 +5438,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -5176,13 +5477,13 @@
         <v>12.56</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC18" s="2">
         <v>4</v>
@@ -5191,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5199,10 +5500,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -5238,16 +5539,16 @@
         <v>13.04</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5255,10 +5556,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D20" s="2">
         <v>6</v>
@@ -5294,16 +5595,16 @@
         <v>13.33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -5311,10 +5612,10 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D21" s="2">
         <v>12</v>
@@ -5350,16 +5651,16 @@
         <v>15.03</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE21" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5367,10 +5668,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D22" s="2">
         <v>2</v>
@@ -5406,13 +5707,13 @@
         <v>11.9</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC22" s="2">
         <v>3</v>
@@ -5426,19 +5727,19 @@
         <v>11</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="D23" s="2">
         <v>4</v>
       </c>
       <c r="E23" s="2">
+        <v>54</v>
+      </c>
+      <c r="F23" s="2">
         <v>52</v>
-      </c>
-      <c r="F23" s="2">
-        <v>54</v>
       </c>
       <c r="G23" s="2">
         <v>13.6</v>
@@ -5465,13 +5766,13 @@
         <v>11</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="61.2" customHeight="1">
@@ -5479,10 +5780,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -5518,13 +5819,13 @@
         <v>13.6</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC24" s="2">
         <v>0</v>
@@ -5533,7 +5834,7 @@
         <v>2</v>
       </c>
       <c r="AE24" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="30.6" customHeight="1">
@@ -5541,10 +5842,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D25" s="2">
         <v>1.5</v>
@@ -5580,13 +5881,13 @@
         <v>13.77</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC25" s="2">
         <v>1</v>
@@ -5600,10 +5901,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>552</v>
+        <v>504</v>
       </c>
       <c r="D26" s="2">
         <v>2.5</v>
@@ -5639,13 +5940,13 @@
         <v>12.77</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -5653,10 +5954,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -5692,13 +5993,13 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC27" s="2">
         <v>28</v>
@@ -5707,7 +6008,7 @@
         <v>25</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="132.6" customHeight="1">
@@ -5715,10 +6016,10 @@
         <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D28" s="2">
         <v>12</v>
@@ -5754,16 +6055,16 @@
         <v>8.9</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -5771,10 +6072,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>551</v>
+        <v>503</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
@@ -5810,13 +6111,13 @@
         <v>0.41</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AC29" s="2">
         <v>6</v>
@@ -5825,7 +6126,7 @@
         <v>8</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -5833,10 +6134,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>551</v>
+        <v>503</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D30" s="2">
         <v>6</v>
@@ -5872,16 +6173,16 @@
         <v>0.33</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -5889,10 +6190,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D31" s="2">
         <v>12</v>
@@ -5928,16 +6229,16 @@
         <v>0.4</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -5945,10 +6246,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D32" s="2">
         <v>18</v>
@@ -5984,16 +6285,16 @@
         <v>0.35</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="30.6">
@@ -6001,10 +6302,10 @@
         <v>15</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="D33" s="2">
         <v>24</v>
@@ -6040,16 +6341,16 @@
         <v>0.43</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="51">
@@ -6057,10 +6358,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>509</v>
+        <v>471</v>
       </c>
       <c r="D34" s="2">
         <v>1</v>
@@ -6096,13 +6397,13 @@
         <v>5.2</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>501</v>
+        <v>465</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="AC34" s="2">
         <v>3</v>
@@ -6111,19 +6412,19 @@
         <v>5</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>510</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="1" width="12" style="2" customWidth="1"/>
@@ -6146,46 +6447,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>539</v>
+        <v>493</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -6193,43 +6494,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6237,43 +6538,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6281,43 +6582,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6325,43 +6626,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6369,43 +6670,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6413,43 +6714,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>547</v>
+        <v>499</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>535</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6457,43 +6758,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6501,43 +6802,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6545,43 +6846,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>283</v>
+        <v>555</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>225</v>
+        <v>556</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>336</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>285</v>
-      </c>
       <c r="M10" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>286</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6589,43 +6890,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>527</v>
+        <v>483</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>289</v>
+        <v>552</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6633,43 +6934,40 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>523</v>
+        <v>272</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>481</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>294</v>
+        <v>545</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>296</v>
+        <v>546</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>225</v>
+        <v>481</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>298</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6677,43 +6975,40 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>300</v>
+        <v>528</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>526</v>
+        <v>482</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>303</v>
+        <v>532</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>304</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -6721,132 +7016,135 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>480</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>225</v>
+        <v>495</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>336</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>307</v>
+        <v>531</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="204">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="214.2">
       <c r="A15" s="2">
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>311</v>
+        <v>525</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>225</v>
+        <v>494</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>481</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>312</v>
+        <v>526</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>523</v>
+        <v>481</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="91.8">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="142.80000000000001">
       <c r="A16" s="2">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>511</v>
+        <v>473</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>523</v>
+        <v>474</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>480</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>515</v>
+        <v>475</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>523</v>
+        <v>481</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>517</v>
-      </c>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="17" spans="11:11">
+      <c r="K17" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -6868,19 +7166,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6888,16 +7186,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6905,19 +7203,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -6925,16 +7223,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -6942,16 +7240,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -6959,19 +7257,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>530</v>
+        <v>486</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>531</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6979,16 +7277,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6996,16 +7294,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7013,16 +7311,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7030,16 +7328,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>447</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7047,16 +7345,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>396</v>
+        <v>364</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7064,16 +7362,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>453</v>
+        <v>421</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7081,16 +7379,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>393</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7098,16 +7396,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>397</v>
+        <v>365</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>398</v>
+        <v>366</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>399</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7115,16 +7413,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>401</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7132,16 +7430,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7149,16 +7447,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>407</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7166,16 +7464,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7183,16 +7481,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7200,16 +7498,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7217,16 +7515,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>394</v>
+        <v>362</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7234,16 +7532,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>425</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7251,16 +7549,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7268,16 +7566,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>433</v>
+        <v>401</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>435</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7285,16 +7583,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7302,16 +7600,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7319,16 +7617,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>447</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7336,16 +7634,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7353,19 +7651,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>530</v>
+        <v>486</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>532</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7373,114 +7671,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>392</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -7500,20 +7798,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7521,7 +7819,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>471</v>
+        <v>437</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7529,7 +7827,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7537,7 +7835,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7545,7 +7843,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7553,7 +7851,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7561,7 +7859,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7569,7 +7867,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7577,7 +7875,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>473</v>
+        <v>439</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7585,7 +7883,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7593,7 +7891,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7601,7 +7899,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7609,7 +7907,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7617,7 +7915,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7625,7 +7923,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7633,7 +7931,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7641,7 +7939,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7649,7 +7947,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7657,7 +7955,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>483</v>
+        <v>449</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7665,7 +7963,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7673,15 +7971,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>533</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7689,7 +7987,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C419CE-D2DF-4458-964F-915E97A74F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B548F8FA-2858-4DE6-B2AE-7A52611AFC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15312" yWindow="0" windowWidth="15408" windowHeight="18480" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="561">
   <si>
     <t>Study_ID</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>MFQ</t>
-  </si>
-  <si>
-    <t>ba+cr+rx+3w</t>
   </si>
   <si>
     <t>Tech</t>
@@ -169,27 +166,15 @@
     <t>School</t>
   </si>
   <si>
-    <t>CES-D≥20; no current MDD</t>
-  </si>
-  <si>
     <t>BDI</t>
   </si>
   <si>
-    <t>cr+ps+hw+rp+rx</t>
-  </si>
-  <si>
     <t>Biblio</t>
   </si>
   <si>
     <t>NIH MH67183</t>
   </si>
   <si>
-    <t>Bohr et al.</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
     <t>SPARX</t>
   </si>
   <si>
@@ -199,15 +184,9 @@
     <t>Community</t>
   </si>
   <si>
-    <t>Depressive presentations / elevated depressive symptoms recognized by professionals (not explicitly severity-classified by authors).</t>
-  </si>
-  <si>
     <t>CESD-R</t>
   </si>
   <si>
-    <t>cr+ba+ps+rx</t>
-  </si>
-  <si>
     <t>Human</t>
   </si>
   <si>
@@ -223,21 +202,12 @@
     <t>Nunavut Dept of Health</t>
   </si>
   <si>
-    <t>Fleming et al.</t>
-  </si>
-  <si>
     <t>New Zealand</t>
   </si>
   <si>
     <t>13-16</t>
   </si>
   <si>
-    <t>School (Alt Ed)</t>
-  </si>
-  <si>
-    <t>CDRS-R ≥30</t>
-  </si>
-  <si>
     <t>CDRS-R</t>
   </si>
   <si>
@@ -265,21 +235,9 @@
     <t>13-17</t>
   </si>
   <si>
-    <t>12≤CESD-R≤40; no MDD/schizophrenia/bipolar</t>
-  </si>
-  <si>
-    <t>cr+ba</t>
-  </si>
-  <si>
     <t>Attention control</t>
   </si>
   <si>
-    <t>Tech+Human</t>
-  </si>
-  <si>
-    <t>10 modules/8 months</t>
-  </si>
-  <si>
     <t>Web</t>
   </si>
   <si>
@@ -292,60 +250,36 @@
     <t>CATCH-IT adaptation; N_completed NR; 7 withdrawn from exp</t>
   </si>
   <si>
-    <t>Makarushka</t>
-  </si>
-  <si>
     <t>Blues Blaster</t>
   </si>
   <si>
     <t>11-15</t>
   </si>
   <si>
-    <t>School+Community</t>
-  </si>
-  <si>
-    <t>CES-D≥16; no current mood disorder</t>
-  </si>
-  <si>
     <t>CES-D</t>
   </si>
   <si>
-    <t>cr+ba+pe+rx</t>
-  </si>
-  <si>
     <t>Information-only</t>
   </si>
   <si>
     <t>Auto</t>
   </si>
   <si>
-    <t>30 sessions/6 weeks</t>
-  </si>
-  <si>
     <t>NIMH SBIR R44 MH068989</t>
   </si>
   <si>
     <t>239 randomized→161 retained (CES-D≥16 re-screen); EM imputation; differential attrition (χ²=5.30,p=.02)</t>
   </si>
   <si>
-    <t>O'Dea et al.</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
     <t>WeClick</t>
   </si>
   <si>
-    <t>12-16</t>
-  </si>
-  <si>
     <t>Social media (Facebook)</t>
   </si>
   <si>
-    <t>No specific inclusion criteria regarding assessment;no depression severity threshold</t>
-  </si>
-  <si>
     <t>PHQ-9</t>
   </si>
   <si>
@@ -355,24 +289,10 @@
     <t>Philanthropic (Buxton Family Foundation); University (UNSW Brain Sciences)</t>
   </si>
   <si>
-    <t xml:space="preserve">Waitlist control had unrestricted access to other mental health apps.
-Primary outcome (depressive symptoms) non-significant (d = 0.26, p = .138) .
-Predominantly female sample (86.5%) </t>
-  </si>
-  <si>
     <t>ClearlyMe</t>
   </si>
   <si>
-    <t>School + community</t>
-  </si>
-  <si>
-    <t>5≤PHQ-A-≤19</t>
-  </si>
-  <si>
     <t>PHQ-A</t>
-  </si>
-  <si>
-    <t>cr+ps+ist</t>
   </si>
   <si>
     <t>9 collection in total; ~20min x 9 /6 weeks</t>
@@ -386,9 +306,6 @@
 (NHMRC) Grants</t>
   </si>
   <si>
-    <t>Poppelaars et al.</t>
-  </si>
-  <si>
     <t>The Netherlands</t>
   </si>
   <si>
@@ -695,15 +612,8 @@
 Differences bewteen completers and non-completers: No significant differences on any sub-scale.</t>
   </si>
   <si>
-    <t>Validattion of measurement: Validated self-report measures (MFQ).
-Who is in charage of assessment: Data collected by blinded research assistants.</t>
-  </si>
-  <si>
     <t>Pre-registration: Pre-registered (ISRCTN10541045) with published protocol (Greenhalgh et al., 2021); 
 Outcome consistency: reported outcomes consistent with registration</t>
-  </si>
-  <si>
-    <t>Only D2 raises concern due to unblinded participants in open-label design; all other domains low risk</t>
   </si>
   <si>
     <t>Stice et al., 2008 &amp; 2010</t>
@@ -714,26 +624,7 @@
 Baseline balance: Baseline depressive symptom scores differed significantly across conditions; the authors therefore included baseline depressive symptoms as a covariate in all outcome analyses.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bliding: Participants unblinded due to research design.
-Deviations: Clinical staff and assessors blinded; the differences in baseline depressive symptom were well-handled.
-</t>
-  </si>
-  <si>
-    <t>Attrition: &lt;=20% (3% overall attrition (intervention 5%, control 1%); balanced across arms(χ²=0.95, p=.81); ITT analysis).
-Method for handling missing data: ITT + maximum-likelihood estimation (SPSS Missing Value Analysis module).
-Differences bewteen completers and non-completers: Attrition did not differ significantly across the four conditions (χ2 [3, N =
-338] = 0.95, p = .81).</t>
-  </si>
-  <si>
-    <t>Validattion of measurement: Beck Depression Inventory (BDI).
-Who is in charage of assessment: Data collected by blinded research assistants.</t>
-  </si>
-  <si>
     <t>No pre-registered protocol (study conducted 2004–2007, pre-registration not yet standard). Multiple outcomes reported (depressive symptoms, BDI, social adjustment, substance use, bulimic symptoms); no evidence of selective suppression. Effect sizes reported for all comparisons.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Some concerns across D1 (allocation concealment not described), D2 (participants unblinded, waitlist control), and D5 (no pre-registered protocol). D3 low risk (ITT, low attrition). D4 low risk (self-report measures, assessors blinded).</t>
   </si>
   <si>
     <t>Bohr et al., 2023</t>
@@ -752,9 +643,6 @@
   <si>
     <t>Attrition: EXP 35%, CTRL 32%. No ITT analysis reported. 
 Method for handling missing data: No method described for handling missing data.</t>
-  </si>
-  <si>
-    <t>Validattion of measurement: CESD-R. Who is in charage of assessment: Facilitators present but not assessing outcomes.</t>
   </si>
   <si>
     <t>No pre-registration. CESD-R not significant; only secondary outcomes (hopelessness, rumination) reported as significant. Possible selective emphasis on positive findings.</t>
@@ -802,15 +690,6 @@
     <t>Intervention group attrition 5.4% &lt; 20% + ITT analysis conducted.</t>
   </si>
   <si>
-    <t>Primary outcome CESD-R is self-reported; outcome assessors were blinded to group allocation</t>
-  </si>
-  <si>
-    <t>This study is registered with Clinicaltrials.gov (Identifier: NCT01783652)</t>
-  </si>
-  <si>
-    <t>Only D2 raises concern due to unblinded participants in open-label design</t>
-  </si>
-  <si>
     <t>Randomization process: 239 randomly assigned to 2 conditions; method of sequence generation not described.
 Allocation concealment: Not described.
 Baseline balance: No significant differences on any baseline demographics or outcomes.
@@ -826,23 +705,10 @@
 Differences between completers and non-completers: No main effects on baseline demographics or outcomes.</t>
   </si>
   <si>
-    <t>Validation of measurement: CES-D (α=.83 in this trial).
-Who is in charge of assessment: Computer-based self-report assessments via Survey Console; no assessor involvement.</t>
-  </si>
-  <si>
     <t>No pre-registration (dissertation, 2012; pre-registration not yet standard). Multiple outcomes reported (CES-D, knowledge, ATQ, BADS, school functioning, self-efficacy). CES-D at follow-up was non-significant (p=.059) but reported transparently with effect size.</t>
   </si>
   <si>
     <t>O'Dea et al., 2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Randomization process: Computerised adaptive randomisation.
-Allocation concealment: The allocation was fully automatic
-with no interference from researchers.
-Baseline balance: A stratification approach with a block size of 4 (1: 1 ratio) was
-used to ensure balance across age (12
-14 years vs. 15–16 years) and gender (male vs. female).
-</t>
   </si>
   <si>
     <t>Blinding: Participants and researchers unblinded to allocation;
@@ -854,21 +720,6 @@
 Method for handling missing data: MMRM analysis on all randomised participants</t>
   </si>
   <si>
-    <t>Validation of measurement: PHQ-A(Cronbach’s
-a = .89).
-Who is in charge of assessment:  Conducted entirely online with
-limited contact from the research team</t>
-  </si>
-  <si>
-    <t>Pre-registered:This trial was registered with the Australian New Zealand Clinical Trials Registry (ANZCTR):
-ACTRN12618001982202.
-All primary and secondary outcomes reported as pre-specified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allocation were not blinded to the researchers.
-Only D2 raises concern: unblinded participants, </t>
-  </si>
-  <si>
     <t>O'Dea et al., 2025</t>
   </si>
   <si>
@@ -878,16 +729,10 @@
     <t xml:space="preserve"> Blinding: Statistician and chief investigators were blinded to allocation for primary outcome analyses. Participants were not directly informed of their allocation but may have deduced it from differences across conditions. Staff providing guided support were unblinded but not involved in analysis. Deviations: No per-protocol restrictions reported.</t>
   </si>
   <si>
-    <t>24.4% attrition at primary endpoint (self-directed: 33.3%, guided: 20.7%, control: 18.9%). Differential attrition between self-directed and control arms (~14%). ITT analysis using MMRM with all 569 randomized participants included. Some concerns due to differential attrition despite appropriate handling.</t>
-  </si>
-  <si>
     <t>Depressive symptoms assessed using validated self-report measure (PHQ-A). Outcome not influenced by assessor blinding; no evidence of differential measurement between groups.</t>
   </si>
   <si>
     <t>Pre-registered (ACTRN12622000131752); published protocol (Li et al., 2022). Primary outcome (PHQ-A change post-intervention) consistent with registration and protocol.</t>
-  </si>
-  <si>
-    <t>Differential attrition（self-directed 33.3% vs control 18.9%）</t>
   </si>
   <si>
     <t>Poppelaars et al., 2016</t>
@@ -1866,10 +1711,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">24/7 access </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Stice et al.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2457,6 +2298,2102 @@
   </si>
   <si>
     <t>D2 Some concerns + D3 Some concerns → Overall: Some concerns. (mainly due to failure in blindness)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>O'Dea et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human+Tech</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PHQ-A-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>19; access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>smartphone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Internet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>having</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>an</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mobile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>phone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>number; ability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>read</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>English</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>at</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Grade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>level; consent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>from</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>parent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>guardian; not</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>currently</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>receiving</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>planning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>professional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>psychological</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>treatment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>taking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>prescribed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>medication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>depression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>anxiety; no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>report</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>severe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>suicidal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ideation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>past</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>two</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>weeks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>serious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>thoughts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>intentions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>self</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>harm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>suicide</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>attempts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>within</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>past</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>month</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHQ-A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+ps+ist+rx+pe+3w</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4% attrition at primary endpoint (self-directed: 33.3%, guided: 20.7%, control: 18.9%). Differential attrition between self-directed and control arms (~14%). ITT analysis using MMRM with all 569 randomized participants included, assuming MAR. Missingness was associated with observed baseline variables (age, location, baseline ERQ-CA/CBTSQ-CR), consistent with MAR and addressable by MMRM. A post hoc sensitivity analysis (treating endpoint-missing as control-equivalent) retained significance for the self-directed arm (p=.042). Some concerns due to differential attrition, despite appropriate handling.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Missingness was associated with observed baseline variables (age, location, baseline ERQ-CA/CBTSQ-CR),</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Social media + Official website + Recommendation from others</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>No specific inclusion criteria regarding assessment;no depression severity threshold; fluent in English; written consent from gaurdians; have access for contact; ability of using smart phone</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makarushka</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Waitlist control had unrestricted access to other mental health apps.
+Primary outcome (depressive symptoms) non-significant (d = 0.26, p = .138) .
+Predominantly female sample (86.5%) ; no exclusion criteria; universal prevention (no specific inclusion cutoff score)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Randomization process: Computerised adaptive randomisation.
+Allocation concealment: The allocation was fully automatic
+with no interference from researchers.
+Baseline balance: A stratification approach with a block size of 4 (1: 1 ratio) was
+used to ensure balance across age (12
+14 years vs. 15–16 years) and gender (male vs. female).However, baseline depression (PHQ-A) was modestly imbalanced (intervention 14.59 vs control 12.73), favoring the intervention arm.
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-registered:This trial was registered with the Australian New Zealand Clinical Trials Registry (ANZCTR):
+ACTRN12618001982202.
+All primary and secondary outcomes reported as pre-specified.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>School+Community (School and juvenile justice/community agency recruitment)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+CES-D &gt; 13 at initial screening and CES-D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 16 at baseline;
+English-speaking;
+access to high-speed Internet;
+not currently meeting DSM-IV criteria for a mood disorder. Excluded if currently met criteria for a mood disorder: Major Depression, Dysthymia, or Mania.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>30 sessions/6 weeks; encouraged to complete 1 mini-lesson per day; 1 module per week</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+pe+hw</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validation of measurement: PHQ-A(Cronbach’s
+a = .89).
+Who is in charge of assessment:  Conducted entirely online with
+limited contact from the research team; however participants are aware of allocation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validation of measurement: CES-D (α=.83 in this trial).
+Who is in charge of assessment: Computer-based self-report assessments via Survey Console; no assessor involvement.  however participants are aware of allocation.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Allocation were not blinded to the researchers.
+D4 D2 raises concern: unblinded participants, </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CESD-R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>40; no MDD/schizophrenia/bipolar;suicide-related hospitalization risk; no antidepressant or psychotropic medication use; no substance abuse; no reading impairment, no intellectual disability, visual impairment, or developmental disability</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CESD-R</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control (anti-smoking quiz website)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 modules/8 months, self-paced</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Primary outcome CESD-R is self-reported; outcome assessors were not blinded to group allocation (participants themselves); even though took attention control as control group, the author confess that participants are not actually blinded.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Due to unblinded participants in open-label design</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>This study is registered with Clinicaltrials.gov (Identifier: NCT01783652); promised outcomes were well-reported</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poppelaars et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recruited from alternative education / alternative schooling programmes for adolescents excluded or alienated from mainstream education.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CDRS-R </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30; participants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>needed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>be</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>able</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>use</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>the</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>computer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>programme</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>complete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>measures</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>remain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>enrolled</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>at</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>least</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>weeks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human + Tech</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identified by community facilitators as exhibiting low mood, negative affect, depressive presentations, or significant levels of stress; sufficient English comprehension to use and understand SPARX.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+ps+rx+pe+hw+3w</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fleming et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validattion of measurement: CESD-R. Who is in charage of assessment: Facilitators present but not assessing outcomes. However, the particants were aware of which group they were allocated into.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>School (Mass mailings + handbills during lunch hour + posters in schools)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CES-D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>20; signed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>parental</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>consent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>current</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>major</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>depression</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>excluded</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self-paced</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attrition: &lt;=20% (3% overall attrition (intervention 5%, control 1%); balanced across arms(χ²=0.95, p=.81); ITT analysis).
+Method for handling missing data: ITT + maximum-likelihood estimation (SPSS Missing Value Analysis module).
+Differences bewteen completers and non-completers: Attrition did not differ significantly across the four conditions (χ2 [3, N =
+338] = 0.95, p = .81).</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Bliding: Participants unblinded due to research design.
+Deviations: Clinical staff and assessors blinded; the differences in baseline depressive symptom were well-handled.
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validattion of measurement: Beck Depression Inventory (BDI).
+Who is in charage of assessment: Data collected by blinded research assistants. However, particpants are aware of which group they were included in</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1 - concealment; D3 - individuals are not blinded</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bohr et al.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+rx+3w</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validattion of measurement: Validated self-report measures (MFQ).
+Who is in charage of assessment: Data collected by blinded research assistants. However, participants were not blinded</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Only D2 D4raises concern due to unblinded participants in open-label design; all other domains low risk</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2467,7 +4404,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2576,6 +4513,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2597,7 +4540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2645,6 +4588,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2966,7 +4912,7 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>448</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -3017,13 +4963,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>335</v>
+        <v>291</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -3032,13 +4978,13 @@
         <v>18</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>522</v>
+        <v>477</v>
       </c>
       <c r="X1" s="17" t="s">
-        <v>511</v>
+        <v>466</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>506</v>
+        <v>462</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
@@ -3094,16 +5040,16 @@
         <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="16" t="s">
-        <v>478</v>
-      </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="S2" s="2">
         <v>0</v>
@@ -3112,25 +5058,31 @@
         <v>4</v>
       </c>
       <c r="U2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>35</v>
+      <c r="W2" s="2">
+        <v>3</v>
+      </c>
+      <c r="X2" s="2">
+        <v>1</v>
       </c>
       <c r="Y2" s="2">
         <v>0</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="AA2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="91.8" customHeight="1">
@@ -3138,16 +5090,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>510</v>
+        <v>465</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>497</v>
+        <v>453</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F3" s="2">
         <v>80</v>
@@ -3156,78 +5108,84 @@
         <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="2">
         <v>15.6</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="2">
+        <v>56</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>45</v>
+      <c r="N3" s="16" t="s">
+        <v>470</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>509</v>
+        <v>296</v>
+      </c>
+      <c r="Q3" s="16" t="s">
+        <v>552</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
       </c>
       <c r="T3" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="W3" s="2">
+        <v>1</v>
+      </c>
+      <c r="X3" s="2">
+        <v>1</v>
       </c>
       <c r="Y3" s="2">
         <v>1</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>48</v>
+      <c r="B4" s="20" t="s">
+        <v>557</v>
       </c>
       <c r="C4" s="2">
         <v>2023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>545</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
@@ -3236,78 +5194,84 @@
         <v>28</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>53</v>
+        <v>546</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>547</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>56</v>
+        <v>433</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>544</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="S4" s="2">
         <v>1</v>
       </c>
       <c r="T4" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="W4" s="2">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2">
+        <v>1</v>
       </c>
       <c r="Y4" s="2">
         <v>1</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="61.2" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>61</v>
+      <c r="B5" s="20" t="s">
+        <v>548</v>
       </c>
       <c r="C5" s="2">
         <v>2012</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2">
         <v>20</v>
@@ -3316,34 +5280,34 @@
         <v>12</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I5" s="2">
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>64</v>
+        <v>296</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>542</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>65</v>
+        <v>543</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>67</v>
+        <v>547</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>56</v>
+        <v>544</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="S5" s="2">
         <v>1</v>
@@ -3352,25 +5316,31 @@
         <v>7</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
+      </c>
+      <c r="W5" s="2">
+        <v>1</v>
+      </c>
+      <c r="X5" s="2">
+        <v>1</v>
       </c>
       <c r="Y5" s="2">
         <v>1</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="71.400000000000006" customHeight="1">
@@ -3378,16 +5348,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>2016</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2">
         <v>130</v>
@@ -3396,7 +5366,7 @@
         <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2">
         <v>14.63</v>
@@ -3405,52 +5375,58 @@
         <v>68.099999999999994</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>75</v>
+        <v>534</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>54</v>
+        <v>535</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>76</v>
+        <v>505</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>77</v>
+        <v>536</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>79</v>
+        <v>537</v>
       </c>
       <c r="S6" s="2">
         <v>1</v>
       </c>
       <c r="T6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
+      </c>
+      <c r="W6" s="2">
+        <v>1</v>
+      </c>
+      <c r="X6" s="2">
+        <v>1</v>
       </c>
       <c r="Y6" s="2">
         <v>1</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="64.8" customHeight="1">
@@ -3458,16 +5434,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>84</v>
+        <v>523</v>
       </c>
       <c r="C7" s="2">
         <v>2011</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2">
         <v>76</v>
@@ -3476,7 +5452,7 @@
         <v>85</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2">
         <v>12.7</v>
@@ -3485,25 +5461,25 @@
         <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>87</v>
+        <v>527</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>88</v>
+        <v>528</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>90</v>
+        <v>72</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>530</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>93</v>
+        <v>529</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
@@ -3512,42 +5488,48 @@
         <v>4</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
+      </c>
+      <c r="W7" s="2">
+        <v>1</v>
+      </c>
+      <c r="X7" s="2">
+        <v>1</v>
       </c>
       <c r="Y7" s="2">
         <v>1</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>81</v>
+      <c r="Z7" s="21" t="s">
+        <v>299</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="51" customHeight="1">
       <c r="A8" s="2">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>96</v>
+      <c r="B8" s="19" t="s">
+        <v>514</v>
       </c>
       <c r="C8" s="2">
         <v>2020</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F8" s="2">
         <v>98</v>
@@ -3556,7 +5538,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>99</v>
+        <v>457</v>
       </c>
       <c r="I8" s="2">
         <v>14.82</v>
@@ -3565,25 +5547,25 @@
         <v>86.5</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>101</v>
+        <v>522</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="S8" s="2">
         <v>0</v>
@@ -3592,42 +5574,48 @@
         <v>3</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>35</v>
+      <c r="W8" s="2">
+        <v>2</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
       </c>
       <c r="Y8" s="2">
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>105</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="105.6" customHeight="1">
       <c r="A9" s="2">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>96</v>
+      <c r="B9" s="19" t="s">
+        <v>514</v>
       </c>
       <c r="C9" s="2">
         <v>2025</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2">
         <v>195</v>
@@ -3645,52 +5633,55 @@
         <v>74.2</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>107</v>
+        <v>521</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>108</v>
+        <v>516</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>110</v>
+        <v>517</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>518</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>92</v>
+        <v>65</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>515</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="S9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="W9" s="2">
         <v>1</v>
       </c>
+      <c r="X9" s="2">
+        <v>1</v>
+      </c>
       <c r="Y9" s="2">
         <v>1</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="187.2" customHeight="1">
@@ -3698,16 +5689,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>114</v>
+        <v>541</v>
       </c>
       <c r="C10" s="2">
         <v>2016</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2">
         <v>51</v>
@@ -3716,7 +5707,7 @@
         <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2">
         <v>13.35</v>
@@ -3725,37 +5716,37 @@
         <v>100</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>554</v>
+        <v>509</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>479</v>
+        <v>435</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="S10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="2">
         <v>7</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="W10" s="2">
         <v>1</v>
@@ -3767,16 +5758,16 @@
         <v>1</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="81.599999999999994" customHeight="1">
@@ -3784,16 +5775,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>547</v>
+        <v>502</v>
       </c>
       <c r="C11" s="2">
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2">
         <v>58</v>
@@ -3802,46 +5793,46 @@
         <v>58</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>548</v>
+        <v>503</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>550</v>
+        <v>505</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>549</v>
+        <v>504</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>551</v>
+        <v>506</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="S11" s="2">
         <v>0</v>
       </c>
       <c r="T11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="W11" s="2">
         <v>1</v>
@@ -3853,16 +5844,16 @@
         <v>0</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>543</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="91.8" customHeight="1">
@@ -3870,16 +5861,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>542</v>
+        <v>497</v>
       </c>
       <c r="C12" s="2">
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2">
         <v>55</v>
@@ -3888,34 +5879,34 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>539</v>
+        <v>494</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>508</v>
+        <v>464</v>
       </c>
       <c r="S12" s="2">
         <v>0</v>
@@ -3924,10 +5915,10 @@
         <v>7</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="W12" s="2">
         <v>1</v>
@@ -3939,16 +5930,16 @@
         <v>1</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>544</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="105.6" customHeight="1">
@@ -3956,16 +5947,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="F13" s="2">
         <v>17</v>
@@ -3974,7 +5965,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I13" s="2">
         <v>15.2</v>
@@ -3983,25 +5974,25 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>534</v>
+        <v>489</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>535</v>
+        <v>490</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>537</v>
+        <v>492</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>536</v>
+        <v>491</v>
       </c>
       <c r="R13" s="2">
         <v>21</v>
@@ -4013,10 +6004,10 @@
         <v>6</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="W13" s="2">
         <v>1</v>
@@ -4028,16 +6019,16 @@
         <v>1</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>538</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="153" customHeight="1">
@@ -4045,7 +6036,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>346</v>
+        <v>302</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -4054,7 +6045,7 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="F14" s="2">
         <v>70</v>
@@ -4063,7 +6054,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>500</v>
+        <v>456</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -4072,25 +6063,25 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>496</v>
+        <v>452</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -4102,13 +6093,13 @@
         <v>7</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="W14" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" s="2">
         <v>1</v>
@@ -4117,16 +6108,16 @@
         <v>1</v>
       </c>
       <c r="Z14" s="16" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>541</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="295.8">
@@ -4134,16 +6125,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>540</v>
+        <v>495</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -4152,7 +6143,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -4161,40 +6152,40 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>521</v>
+        <v>476</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>515</v>
+        <v>470</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>523</v>
+        <v>478</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="S15" s="2">
         <v>1</v>
       </c>
       <c r="T15" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="W15" s="2">
         <v>1</v>
@@ -4206,16 +6197,16 @@
         <v>1</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>524</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="102">
@@ -4223,16 +6214,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>451</v>
+        <v>407</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -4241,7 +6232,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>513</v>
+        <v>468</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -4250,40 +6241,40 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>512</v>
+        <v>467</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>515</v>
+        <v>470</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>516</v>
+        <v>471</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="S16" s="2">
         <v>1</v>
       </c>
       <c r="T16" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="W16" s="2">
         <v>1</v>
@@ -4295,16 +6286,16 @@
         <v>1</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>514</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -4349,7 +6340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AE33"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="30" width="13" style="2" customWidth="1"/>
@@ -4366,88 +6357,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>327</v>
+        <v>283</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>332</v>
+        <v>288</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -4458,10 +6449,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -4488,10 +6479,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -4518,7 +6509,7 @@
         <v>15</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -4526,10 +6517,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -4556,10 +6547,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -4580,7 +6571,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -4588,10 +6579,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -4627,13 +6618,13 @@
         <v>9.74</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -4642,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -4650,10 +6641,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -4689,16 +6680,16 @@
         <v>10.93</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -4706,10 +6697,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -4745,16 +6736,16 @@
         <v>10.039999999999999</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -4762,10 +6753,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -4801,16 +6792,16 @@
         <v>9.44</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -4818,10 +6809,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -4857,13 +6848,13 @@
         <v>8.58</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -4872,7 +6863,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -4880,10 +6871,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -4907,13 +6898,13 @@
         <v>38.4</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -4940,7 +6931,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -4948,10 +6939,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -4987,13 +6978,13 @@
         <v>9.7100000000000009</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -5002,7 +6993,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -5010,10 +7001,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -5049,16 +7040,16 @@
         <v>8.5</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -5066,10 +7057,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -5105,13 +7096,13 @@
         <v>10.09</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AC12" s="2">
         <v>15</v>
@@ -5120,7 +7111,7 @@
         <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -5128,10 +7119,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -5167,16 +7158,16 @@
         <v>10.35</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -5184,10 +7175,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -5223,13 +7214,13 @@
         <v>7.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -5238,63 +7229,78 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
       <c r="A15" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E15" s="2">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="F15" s="2">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="G15" s="2">
-        <v>14.59</v>
+        <v>12.34</v>
       </c>
       <c r="H15" s="2">
-        <v>6.88</v>
+        <v>4.05</v>
       </c>
       <c r="I15" s="2">
-        <v>12.73</v>
+        <v>12.36</v>
       </c>
       <c r="J15" s="2">
-        <v>6.68</v>
-      </c>
-      <c r="K15" s="2">
-        <v>12.05</v>
-      </c>
-      <c r="L15" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="M15" s="2">
-        <v>11.27</v>
-      </c>
-      <c r="N15" s="2">
-        <v>7.12</v>
+        <v>3.88</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>163</v>
+        <v>277</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>163</v>
+        <v>286</v>
+      </c>
+      <c r="X15" s="2">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>-0.12</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>-0.35</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>65</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>36</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -5302,19 +7308,19 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D16" s="2">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="F16" s="2">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="G16" s="2">
         <v>12.34</v>
@@ -5341,96 +7347,87 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="X16" s="2">
-        <v>-0.56999999999999995</v>
+        <v>-0.45</v>
       </c>
       <c r="Y16" s="2">
-        <v>-0.12</v>
+        <v>0.05</v>
       </c>
       <c r="Z16" s="2">
-        <v>-0.35</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>65</v>
-      </c>
-      <c r="AD16" s="2">
-        <v>36</v>
+        <v>-0.2</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" ht="30.6" customHeight="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31">
       <c r="A17" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>51</v>
+      </c>
+      <c r="F17" s="2">
+        <v>51</v>
+      </c>
+      <c r="G17" s="2">
+        <v>62.61</v>
+      </c>
+      <c r="H17" s="2">
+        <v>11.97</v>
+      </c>
+      <c r="I17" s="2">
+        <v>61.9</v>
+      </c>
+      <c r="J17" s="2">
+        <v>11.97</v>
+      </c>
+      <c r="K17" s="2">
+        <v>57.88</v>
+      </c>
+      <c r="L17" s="2">
+        <v>12.57</v>
+      </c>
+      <c r="M17" s="2">
+        <v>57.74</v>
+      </c>
+      <c r="N17" s="2">
+        <v>12.56</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC17" s="2">
         <v>4</v>
       </c>
-      <c r="E17" s="2">
-        <v>102</v>
-      </c>
-      <c r="F17" s="2">
-        <v>135</v>
-      </c>
-      <c r="G17" s="2">
-        <v>12.34</v>
-      </c>
-      <c r="H17" s="2">
-        <v>4.05</v>
-      </c>
-      <c r="I17" s="2">
-        <v>12.36</v>
-      </c>
-      <c r="J17" s="2">
-        <v>3.88</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="X17" s="2">
-        <v>-0.45</v>
-      </c>
-      <c r="Y17" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="Z17" s="2">
-        <v>-0.2</v>
+      <c r="AD17" s="2">
+        <v>0</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -5438,13 +7435,13 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D18" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2">
         <v>51</v>
@@ -5465,34 +7462,28 @@
         <v>11.97</v>
       </c>
       <c r="K18" s="2">
-        <v>57.88</v>
+        <v>54.78</v>
       </c>
       <c r="L18" s="2">
-        <v>12.57</v>
+        <v>10.3</v>
       </c>
       <c r="M18" s="2">
-        <v>57.74</v>
+        <v>56.06</v>
       </c>
       <c r="N18" s="2">
-        <v>12.56</v>
+        <v>13.04</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="2">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -5500,13 +7491,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2">
         <v>51</v>
@@ -5527,28 +7518,28 @@
         <v>11.97</v>
       </c>
       <c r="K19" s="2">
-        <v>54.78</v>
+        <v>58.17</v>
       </c>
       <c r="L19" s="2">
-        <v>10.3</v>
+        <v>12.72</v>
       </c>
       <c r="M19" s="2">
-        <v>56.06</v>
+        <v>57.62</v>
       </c>
       <c r="N19" s="2">
-        <v>13.04</v>
+        <v>13.33</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -5556,13 +7547,13 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="D20" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2">
         <v>51</v>
@@ -5583,84 +7574,87 @@
         <v>11.97</v>
       </c>
       <c r="K20" s="2">
-        <v>58.17</v>
+        <v>57.08</v>
       </c>
       <c r="L20" s="2">
-        <v>12.72</v>
+        <v>14.21</v>
       </c>
       <c r="M20" s="2">
-        <v>57.62</v>
+        <v>61.22</v>
       </c>
       <c r="N20" s="2">
-        <v>13.33</v>
+        <v>15.03</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:31">
       <c r="A21" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D21" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F21" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G21" s="2">
-        <v>62.61</v>
+        <v>13.6</v>
       </c>
       <c r="H21" s="2">
-        <v>11.97</v>
+        <v>8.6</v>
       </c>
       <c r="I21" s="2">
-        <v>61.9</v>
+        <v>13.4</v>
       </c>
       <c r="J21" s="2">
-        <v>11.97</v>
+        <v>10.1</v>
       </c>
       <c r="K21" s="2">
-        <v>57.08</v>
+        <v>14.8</v>
       </c>
       <c r="L21" s="2">
-        <v>14.21</v>
+        <v>12.4</v>
       </c>
       <c r="M21" s="2">
-        <v>61.22</v>
+        <v>15</v>
       </c>
       <c r="N21" s="2">
-        <v>15.03</v>
+        <v>11.9</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE21" s="2" t="s">
-        <v>185</v>
+        <v>136</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5668,19 +7662,19 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G22" s="2">
         <v>13.6</v>
@@ -5695,146 +7689,146 @@
         <v>10.1</v>
       </c>
       <c r="K22" s="2">
-        <v>14.8</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="2">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="M22" s="2">
-        <v>15</v>
+        <v>11.7</v>
       </c>
       <c r="N22" s="2">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>3</v>
-      </c>
-      <c r="AD22" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" ht="61.2" customHeight="1">
       <c r="A23" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>55</v>
+      </c>
+      <c r="F23" s="2">
+        <v>55</v>
+      </c>
+      <c r="G23" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="H23" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>24.8</v>
+      </c>
+      <c r="J23" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="K23" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="L23" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="M23" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="N23" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="30.6" customHeight="1">
+      <c r="A24" s="2">
+        <v>13</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>17</v>
+      </c>
+      <c r="F24" s="2">
+        <v>17</v>
+      </c>
+      <c r="G24" s="2">
+        <v>48.29</v>
+      </c>
+      <c r="H24" s="2">
+        <v>6.49</v>
+      </c>
+      <c r="I24" s="2">
+        <v>45.47</v>
+      </c>
+      <c r="J24" s="2">
+        <v>9.44</v>
+      </c>
+      <c r="K24" s="2">
+        <v>30.41</v>
+      </c>
+      <c r="L24" s="2">
+        <v>7.38</v>
+      </c>
+      <c r="M24" s="2">
+        <v>36.29</v>
+      </c>
+      <c r="N24" s="2">
+        <v>13.77</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="2">
         <v>4</v>
-      </c>
-      <c r="E23" s="2">
-        <v>54</v>
-      </c>
-      <c r="F23" s="2">
-        <v>52</v>
-      </c>
-      <c r="G23" s="2">
-        <v>13.6</v>
-      </c>
-      <c r="H23" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="I23" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="J23" s="2">
-        <v>10.1</v>
-      </c>
-      <c r="K23" s="2">
-        <v>12.5</v>
-      </c>
-      <c r="L23" s="2">
-        <v>12.8</v>
-      </c>
-      <c r="M23" s="2">
-        <v>11.7</v>
-      </c>
-      <c r="N23" s="2">
-        <v>11</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="61.2" customHeight="1">
-      <c r="A24" s="2">
-        <v>12</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2">
-        <v>55</v>
-      </c>
-      <c r="F24" s="2">
-        <v>55</v>
-      </c>
-      <c r="G24" s="2">
-        <v>25.6</v>
-      </c>
-      <c r="H24" s="2">
-        <v>11.1</v>
-      </c>
-      <c r="I24" s="2">
-        <v>24.8</v>
-      </c>
-      <c r="J24" s="2">
-        <v>11.8</v>
-      </c>
-      <c r="K24" s="2">
-        <v>13.4</v>
-      </c>
-      <c r="L24" s="2">
-        <v>12.9</v>
-      </c>
-      <c r="M24" s="2">
-        <v>24.3</v>
-      </c>
-      <c r="N24" s="2">
-        <v>13.6</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="2">
-        <v>2</v>
-      </c>
-      <c r="AE24" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="30.6" customHeight="1">
@@ -5842,13 +7836,13 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>157</v>
+        <v>460</v>
       </c>
       <c r="D25" s="2">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E25" s="2">
         <v>17</v>
@@ -5869,83 +7863,86 @@
         <v>9.44</v>
       </c>
       <c r="K25" s="2">
-        <v>30.41</v>
+        <v>32.06</v>
       </c>
       <c r="L25" s="2">
-        <v>7.38</v>
+        <v>8.34</v>
       </c>
       <c r="M25" s="2">
-        <v>36.29</v>
+        <v>34</v>
       </c>
       <c r="N25" s="2">
-        <v>13.77</v>
+        <v>12.77</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC25" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="132.6" customHeight="1">
+      <c r="A26" s="2">
+        <v>14</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" ht="30.6" customHeight="1">
-      <c r="A26" s="2">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D26" s="2">
-        <v>2.5</v>
-      </c>
       <c r="E26" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F26" s="2">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G26" s="2">
-        <v>48.29</v>
+        <v>18</v>
       </c>
       <c r="H26" s="2">
-        <v>6.49</v>
+        <v>6.9</v>
       </c>
       <c r="I26" s="2">
-        <v>45.47</v>
+        <v>16</v>
       </c>
       <c r="J26" s="2">
-        <v>9.44</v>
+        <v>6.6</v>
       </c>
       <c r="K26" s="2">
-        <v>32.06</v>
+        <v>14.4</v>
       </c>
       <c r="L26" s="2">
-        <v>8.34</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M26" s="2">
-        <v>34</v>
+        <v>15.4</v>
       </c>
       <c r="N26" s="2">
-        <v>12.77</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="Q26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>28</v>
+      </c>
+      <c r="AD26" s="2">
+        <v>25</v>
+      </c>
+      <c r="AE26" s="2" t="s">
         <v>163</v>
       </c>
     </row>
@@ -5954,19 +7951,19 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="D27" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G27" s="2">
         <v>18</v>
@@ -5981,90 +7978,90 @@
         <v>6.6</v>
       </c>
       <c r="K27" s="2">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
       <c r="L27" s="2">
-        <v>9.3000000000000007</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M27" s="2">
-        <v>15.4</v>
+        <v>12.3</v>
       </c>
       <c r="N27" s="2">
-        <v>9.1999999999999993</v>
+        <v>8.9</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE27" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC27" s="2">
-        <v>28</v>
-      </c>
-      <c r="AD27" s="2">
-        <v>25</v>
-      </c>
-      <c r="AE27" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="132.6" customHeight="1">
+    </row>
+    <row r="28" spans="1:31" ht="30.6">
       <c r="A28" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>189</v>
+        <v>459</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>128</v>
+      </c>
+      <c r="F28" s="2">
+        <v>124</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1.45</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1.38</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0.42</v>
+      </c>
+      <c r="M28" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0.41</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D28" s="2">
-        <v>12</v>
-      </c>
-      <c r="E28" s="2">
-        <v>38</v>
-      </c>
-      <c r="F28" s="2">
-        <v>37</v>
-      </c>
-      <c r="G28" s="2">
-        <v>18</v>
-      </c>
-      <c r="H28" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="I28" s="2">
-        <v>16</v>
-      </c>
-      <c r="J28" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="K28" s="2">
-        <v>12.8</v>
-      </c>
-      <c r="L28" s="2">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="M28" s="2">
-        <v>12.3</v>
-      </c>
-      <c r="N28" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="P28" s="2" t="s">
-        <v>163</v>
+        <v>416</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
+      </c>
+      <c r="AC28" s="2">
+        <v>6</v>
+      </c>
+      <c r="AD28" s="2">
+        <v>8</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -6072,13 +8069,13 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="D29" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2">
         <v>128</v>
@@ -6099,34 +8096,28 @@
         <v>0.36</v>
       </c>
       <c r="K29" s="2">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="L29" s="2">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="M29" s="2">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="N29" s="2">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC29" s="2">
-        <v>6</v>
-      </c>
-      <c r="AD29" s="2">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -6134,13 +8125,13 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>503</v>
+        <v>164</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="D30" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2">
         <v>128</v>
@@ -6161,28 +8152,28 @@
         <v>0.36</v>
       </c>
       <c r="K30" s="2">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="L30" s="2">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="M30" s="2">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="N30" s="2">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>460</v>
+        <v>417</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -6190,13 +8181,13 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D31" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2">
         <v>128</v>
@@ -6217,7 +8208,7 @@
         <v>0.36</v>
       </c>
       <c r="K31" s="2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="L31" s="2">
         <v>0.46</v>
@@ -6226,19 +8217,19 @@
         <v>1.31</v>
       </c>
       <c r="N31" s="2">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -6246,13 +8237,13 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="D32" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E32" s="2">
         <v>128</v>
@@ -6273,146 +8264,90 @@
         <v>0.36</v>
       </c>
       <c r="K32" s="2">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="L32" s="2">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="M32" s="2">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="N32" s="2">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>460</v>
+        <v>417</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" ht="30.6">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" ht="51">
       <c r="A33" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>191</v>
+        <v>420</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>167</v>
+        <v>427</v>
       </c>
       <c r="D33" s="2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E33" s="2">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="F33" s="2">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="G33" s="2">
-        <v>1.45</v>
+        <v>19.2</v>
       </c>
       <c r="H33" s="2">
-        <v>0.41</v>
+        <v>7.1</v>
       </c>
       <c r="I33" s="2">
-        <v>1.38</v>
+        <v>16.8</v>
       </c>
       <c r="J33" s="2">
-        <v>0.36</v>
+        <v>4.5</v>
       </c>
       <c r="K33" s="2">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="L33" s="2">
-        <v>0.47</v>
+        <v>6.7</v>
       </c>
       <c r="M33" s="2">
-        <v>1.39</v>
+        <v>15.8</v>
       </c>
       <c r="N33" s="2">
-        <v>0.43</v>
+        <v>5.2</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>192</v>
+        <v>421</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>163</v>
+        <v>417</v>
+      </c>
+      <c r="AC33" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD33" s="2">
+        <v>5</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" ht="51">
-      <c r="A34" s="2">
-        <v>16</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2">
-        <v>12</v>
-      </c>
-      <c r="F34" s="2">
-        <v>10</v>
-      </c>
-      <c r="G34" s="2">
-        <v>19.2</v>
-      </c>
-      <c r="H34" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="I34" s="2">
-        <v>16.8</v>
-      </c>
-      <c r="J34" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="K34" s="2">
-        <v>9.4</v>
-      </c>
-      <c r="L34" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="M34" s="2">
-        <v>15.8</v>
-      </c>
-      <c r="N34" s="2">
-        <v>5.2</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="AC34" s="2">
-        <v>3</v>
-      </c>
-      <c r="AD34" s="2">
-        <v>5</v>
-      </c>
-      <c r="AE34" s="2" t="s">
-        <v>472</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -6447,46 +8382,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>507</v>
+        <v>463</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -6494,43 +8429,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>209</v>
+        <v>185</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>213</v>
+        <v>559</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>215</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6538,43 +8473,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>480</v>
+        <v>188</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>437</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>218</v>
+        <v>554</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>209</v>
+        <v>553</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>220</v>
+        <v>555</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>222</v>
+        <v>556</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -6582,43 +8517,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>209</v>
+        <v>194</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>228</v>
+        <v>549</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6626,43 +8561,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>480</v>
+        <v>200</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>292</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>480</v>
+        <v>202</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>292</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -6670,43 +8605,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>481</v>
+        <v>205</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>292</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>242</v>
+        <v>538</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>243</v>
+        <v>540</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>481</v>
+        <v>292</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>244</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -6714,43 +8649,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>499</v>
+        <v>455</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>248</v>
+        <v>532</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>490</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -6758,43 +8693,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>251</v>
+        <v>525</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>436</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>254</v>
+        <v>531</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>255</v>
+        <v>526</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>256</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -6802,43 +8737,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>260</v>
+        <v>519</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>263</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -6846,43 +8781,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>209</v>
+        <v>437</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>555</v>
+        <v>510</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>556</v>
+        <v>511</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>557</v>
+        <v>512</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>558</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -6890,43 +8825,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>553</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -6934,40 +8869,40 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>545</v>
+        <v>500</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>546</v>
+        <v>501</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -6975,40 +8910,40 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>528</v>
+        <v>483</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>532</v>
+        <v>487</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -7016,43 +8951,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>531</v>
+        <v>486</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>533</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="214.2">
@@ -7060,43 +8995,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>525</v>
+        <v>480</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>494</v>
+        <v>450</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>480</v>
+        <v>436</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="142.80000000000001">
@@ -7104,43 +9039,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="I16" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>480</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="17" spans="11:11">
@@ -7166,19 +9101,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7186,16 +9121,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>286</v>
+        <v>242</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>435</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7203,19 +9138,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>433</v>
+        <v>389</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -7223,16 +9158,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>432</v>
+        <v>388</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>413</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7240,16 +9175,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>430</v>
+        <v>386</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>431</v>
+        <v>387</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7257,19 +9192,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>487</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7277,16 +9212,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>427</v>
+        <v>383</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>428</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7294,16 +9229,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7311,16 +9246,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>424</v>
+        <v>380</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>423</v>
+        <v>379</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>425</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7328,16 +9263,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>416</v>
+        <v>372</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>417</v>
+        <v>373</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>415</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7345,16 +9280,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7362,16 +9297,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>420</v>
+        <v>376</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>421</v>
+        <v>377</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7379,16 +9314,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>419</v>
+        <v>375</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7396,16 +9331,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7413,16 +9348,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7430,16 +9365,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7447,16 +9382,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>376</v>
+        <v>332</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7464,16 +9399,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>379</v>
+        <v>335</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7481,16 +9416,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>384</v>
+        <v>340</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>382</v>
+        <v>338</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>383</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7498,16 +9433,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>385</v>
+        <v>341</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>387</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7515,16 +9450,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>391</v>
+        <v>347</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7532,16 +9467,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>396</v>
+        <v>352</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7549,16 +9484,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>399</v>
+        <v>355</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>397</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7566,16 +9501,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>403</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7583,16 +9518,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>406</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7600,16 +9535,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>408</v>
+        <v>364</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>407</v>
+        <v>363</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>409</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7617,16 +9552,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>411</v>
+        <v>367</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>415</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7634,16 +9569,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>456</v>
+        <v>412</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>455</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -7651,19 +9586,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>488</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7671,114 +9606,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>302</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>352</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>426</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>355</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>350</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>308</v>
+        <v>264</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>360</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>414</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>413</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -7798,20 +9733,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>310</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>267</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>312</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -7819,7 +9754,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>437</v>
+        <v>393</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -7827,7 +9762,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -7835,7 +9770,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -7843,7 +9778,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>316</v>
+        <v>272</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -7851,7 +9786,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -7859,7 +9794,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -7867,7 +9802,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -7875,7 +9810,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -7883,7 +9818,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -7891,7 +9826,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>441</v>
+        <v>397</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -7899,7 +9834,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -7907,7 +9842,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -7915,7 +9850,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -7923,7 +9858,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -7931,7 +9866,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>446</v>
+        <v>402</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -7939,7 +9874,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -7947,7 +9882,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>448</v>
+        <v>404</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -7955,7 +9890,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>449</v>
+        <v>405</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -7963,7 +9898,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>450</v>
+        <v>406</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -7971,15 +9906,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>457</v>
+        <v>413</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -7987,7 +9922,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B548F8FA-2858-4DE6-B2AE-7A52611AFC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2B014E-61B5-4988-96B9-D86A1525159C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,9 +357,6 @@
     <t>The Journey</t>
   </si>
   <si>
-    <t xml:space="preserve">cr+ba+ps+rx+rp+hw </t>
-  </si>
-  <si>
     <t>Clinical（CAMHS primary mental health workers）</t>
   </si>
   <si>
@@ -2305,10 +2302,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Human+Tech</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>5</t>
     </r>
@@ -4394,6 +4387,14 @@
   </si>
   <si>
     <t>Only D2 D4raises concern due to unblinded participants in open-label design; all other domains low risk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+ps+rx+rp+hw</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auto + Tech</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4912,7 +4913,7 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4963,13 +4964,13 @@
         <v>16</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>17</v>
@@ -4978,13 +4979,13 @@
         <v>18</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="X1" s="17" t="s">
-        <v>466</v>
+        <v>476</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>19</v>
@@ -5040,10 +5041,10 @@
         <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>31</v>
@@ -5073,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>35</v>
@@ -5090,10 +5091,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -5117,25 +5118,25 @@
         <v>56</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
@@ -5159,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA3" s="2" t="s">
         <v>35</v>
@@ -5168,7 +5169,7 @@
         <v>44</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
@@ -5176,13 +5177,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C4" s="2">
         <v>2023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>45</v>
@@ -5197,28 +5198,28 @@
         <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>50</v>
@@ -5254,7 +5255,7 @@
         <v>53</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="61.2" customHeight="1">
@@ -5262,7 +5263,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C5" s="2">
         <v>2012</v>
@@ -5286,25 +5287,25 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>58</v>
@@ -5334,10 +5335,10 @@
         <v>52</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AC5" s="2" t="s">
         <v>60</v>
@@ -5378,22 +5379,22 @@
         <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="P6" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="S6" s="2">
         <v>1</v>
@@ -5434,7 +5435,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C7" s="2">
         <v>2011</v>
@@ -5461,16 +5462,16 @@
         <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>73</v>
@@ -5479,7 +5480,7 @@
         <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
@@ -5503,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="Z7" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>59</v>
@@ -5520,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C8" s="2">
         <v>2020</v>
@@ -5538,7 +5539,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I8" s="2">
         <v>14.82</v>
@@ -5550,16 +5551,16 @@
         <v>79</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>80</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>74</v>
@@ -5598,7 +5599,7 @@
         <v>82</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="105.6" customHeight="1">
@@ -5606,7 +5607,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C9" s="2">
         <v>2025</v>
@@ -5633,28 +5634,28 @@
         <v>74.2</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N9" s="16" t="s">
         <v>516</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>518</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>515</v>
+        <v>560</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>85</v>
       </c>
       <c r="S9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="2">
         <v>7</v>
@@ -5689,7 +5690,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C10" s="2">
         <v>2016</v>
@@ -5719,7 +5720,7 @@
         <v>41</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>56</v>
@@ -5728,10 +5729,10 @@
         <v>57</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>90</v>
@@ -5758,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AA10" s="2" t="s">
         <v>35</v>
@@ -5775,13 +5776,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C11" s="2">
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>93</v>
@@ -5796,7 +5797,7 @@
         <v>94</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
@@ -5805,19 +5806,19 @@
         <v>95</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>80</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>96</v>
@@ -5844,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA11" s="2" t="s">
         <v>35</v>
@@ -5853,7 +5854,7 @@
         <v>98</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="91.8" customHeight="1">
@@ -5861,13 +5862,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C12" s="2">
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>99</v>
@@ -5879,19 +5880,19 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>100</v>
@@ -5900,13 +5901,13 @@
         <v>101</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="S12" s="2">
         <v>0</v>
@@ -5930,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA12" s="2" t="s">
         <v>35</v>
@@ -5939,7 +5940,7 @@
         <v>102</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="105.6" customHeight="1">
@@ -5947,7 +5948,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -5974,25 +5975,25 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>105</v>
+        <v>559</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R13" s="2">
         <v>21</v>
@@ -6019,16 +6020,16 @@
         <v>1</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="153" customHeight="1">
@@ -6036,7 +6037,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -6054,7 +6055,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -6063,10 +6064,10 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
@@ -6075,13 +6076,13 @@
         <v>101</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R14" s="2">
         <v>45</v>
@@ -6108,16 +6109,16 @@
         <v>1</v>
       </c>
       <c r="Z14" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="295.8">
@@ -6125,7 +6126,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -6134,7 +6135,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -6143,7 +6144,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -6152,16 +6153,16 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="N15" s="18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>73</v>
@@ -6170,10 +6171,10 @@
         <v>49</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S15" s="2">
         <v>1</v>
@@ -6197,16 +6198,16 @@
         <v>1</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AA15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="102">
@@ -6214,16 +6215,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -6232,7 +6233,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -6241,28 +6242,28 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M16" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="N16" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="O16" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="N16" s="18" t="s">
+      <c r="P16" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="O16" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>471</v>
-      </c>
       <c r="R16" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S16" s="2">
         <v>1</v>
@@ -6271,10 +6272,10 @@
         <v>6</v>
       </c>
       <c r="U16" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="W16" s="2">
         <v>1</v>
@@ -6286,16 +6287,16 @@
         <v>1</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -6357,88 +6358,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="X1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -6449,10 +6450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -6479,10 +6480,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -6509,7 +6510,7 @@
         <v>15</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -6517,10 +6518,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -6547,10 +6548,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -6571,7 +6572,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -6579,10 +6580,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -6621,10 +6622,10 @@
         <v>42</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -6633,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -6641,10 +6642,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -6683,13 +6684,13 @@
         <v>42</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -6697,10 +6698,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -6739,13 +6740,13 @@
         <v>42</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -6753,10 +6754,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -6795,13 +6796,13 @@
         <v>42</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -6809,10 +6810,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -6851,10 +6852,10 @@
         <v>48</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -6863,7 +6864,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -6871,10 +6872,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -6901,10 +6902,10 @@
         <v>56</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -6931,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -6939,10 +6940,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -6981,10 +6982,10 @@
         <v>48</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -6993,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -7001,10 +7002,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -7043,13 +7044,13 @@
         <v>48</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -7057,10 +7058,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -7099,10 +7100,10 @@
         <v>72</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC12" s="2">
         <v>15</v>
@@ -7111,7 +7112,7 @@
         <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -7119,10 +7120,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -7161,13 +7162,13 @@
         <v>72</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -7175,10 +7176,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -7217,10 +7218,10 @@
         <v>84</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -7229,7 +7230,7 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -7237,10 +7238,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" s="2">
         <v>1.5</v>
@@ -7279,10 +7280,10 @@
         <v>84</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="X15" s="2">
         <v>-0.56999999999999995</v>
@@ -7300,7 +7301,7 @@
         <v>36</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -7308,10 +7309,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -7350,10 +7351,10 @@
         <v>84</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="X16" s="2">
         <v>-0.45</v>
@@ -7365,7 +7366,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -7373,10 +7374,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -7412,13 +7413,13 @@
         <v>12.56</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC17" s="2">
         <v>4</v>
@@ -7427,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -7435,10 +7436,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -7474,16 +7475,16 @@
         <v>13.04</v>
       </c>
       <c r="O18" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE18" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE18" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -7491,10 +7492,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2">
         <v>6</v>
@@ -7530,16 +7531,16 @@
         <v>13.33</v>
       </c>
       <c r="O19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE19" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE19" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -7547,10 +7548,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20" s="2">
         <v>12</v>
@@ -7586,16 +7587,16 @@
         <v>15.03</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE20" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE20" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -7603,10 +7604,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -7642,13 +7643,13 @@
         <v>11.9</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC21" s="2">
         <v>3</v>
@@ -7662,10 +7663,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -7701,13 +7702,13 @@
         <v>11</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="61.2" customHeight="1">
@@ -7715,10 +7716,10 @@
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
@@ -7757,10 +7758,10 @@
         <v>100</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC23" s="2">
         <v>0</v>
@@ -7777,10 +7778,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" s="2">
         <v>1.5</v>
@@ -7819,10 +7820,10 @@
         <v>56</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC24" s="2">
         <v>1</v>
@@ -7836,10 +7837,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D25" s="2">
         <v>2.5</v>
@@ -7878,10 +7879,10 @@
         <v>56</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="132.6" customHeight="1">
@@ -7889,10 +7890,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D26" s="2">
         <v>4</v>
@@ -7931,10 +7932,10 @@
         <v>42</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC26" s="2">
         <v>28</v>
@@ -7943,7 +7944,7 @@
         <v>25</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -7951,10 +7952,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" s="2">
         <v>12</v>
@@ -7993,13 +7994,13 @@
         <v>42</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="30.6">
@@ -8007,10 +8008,10 @@
         <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -8046,13 +8047,13 @@
         <v>0.41</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC28" s="2">
         <v>6</v>
@@ -8061,7 +8062,7 @@
         <v>8</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -8069,10 +8070,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D29" s="2">
         <v>6</v>
@@ -8108,16 +8109,16 @@
         <v>0.33</v>
       </c>
       <c r="O29" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE29" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE29" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -8125,10 +8126,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="2">
         <v>12</v>
@@ -8164,16 +8165,16 @@
         <v>0.4</v>
       </c>
       <c r="O30" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE30" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE30" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -8181,10 +8182,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D31" s="2">
         <v>18</v>
@@ -8220,16 +8221,16 @@
         <v>0.35</v>
       </c>
       <c r="O31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE31" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE31" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -8237,10 +8238,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2">
         <v>24</v>
@@ -8276,16 +8277,16 @@
         <v>0.43</v>
       </c>
       <c r="O32" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE32" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE32" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="51">
@@ -8293,10 +8294,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -8332,13 +8333,13 @@
         <v>5.2</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AC33" s="2">
         <v>3</v>
@@ -8347,7 +8348,7 @@
         <v>5</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -8382,46 +8383,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -8429,43 +8430,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="M2" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8473,43 +8474,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="16" t="s">
         <v>436</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>437</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>554</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -8517,43 +8518,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="I4" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8561,43 +8562,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I5" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -8605,43 +8606,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>207</v>
-      </c>
       <c r="I6" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J6" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>540</v>
-      </c>
       <c r="M6" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -8649,43 +8650,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="I7" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>211</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -8693,43 +8694,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="I8" s="16" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -8737,43 +8738,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="M9" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -8781,43 +8782,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="M10" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8825,43 +8826,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -8869,40 +8870,40 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>437</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="M12" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -8910,40 +8911,40 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="K13" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -8951,43 +8952,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="M14" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="214.2">
@@ -8995,43 +8996,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="142.80000000000001">
@@ -9039,43 +9040,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="I16" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="17" spans="11:11">
@@ -9101,19 +9102,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="C1" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9121,16 +9122,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9138,19 +9139,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -9158,16 +9159,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9175,16 +9176,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9192,19 +9193,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9212,16 +9213,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9229,16 +9230,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9246,16 +9247,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9263,16 +9264,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>373</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9280,16 +9281,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9297,16 +9298,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>377</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -9314,16 +9315,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>375</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -9331,16 +9332,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -9348,16 +9349,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>327</v>
-      </c>
       <c r="D15" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9365,16 +9366,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -9382,16 +9383,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -9399,16 +9400,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>335</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -9416,16 +9417,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -9433,16 +9434,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -9450,16 +9451,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -9467,16 +9468,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -9484,16 +9485,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>355</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -9501,16 +9502,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -9518,16 +9519,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="D25" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -9535,16 +9536,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -9552,16 +9553,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="D27" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>368</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -9569,16 +9570,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -9586,19 +9587,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>442</v>
-      </c>
       <c r="F29" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -9606,114 +9607,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -9733,20 +9734,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -9754,7 +9755,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -9762,7 +9763,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -9770,7 +9771,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -9778,7 +9779,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -9786,7 +9787,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -9794,7 +9795,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -9802,7 +9803,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -9810,7 +9811,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -9818,7 +9819,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -9826,7 +9827,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -9834,7 +9835,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -9842,7 +9843,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -9850,7 +9851,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -9858,7 +9859,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -9866,7 +9867,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -9874,7 +9875,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -9882,7 +9883,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -9890,7 +9891,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -9898,7 +9899,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -9906,15 +9907,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -9922,7 +9923,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2B014E-61B5-4988-96B9-D86A1525159C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2E2893-A3CC-4B5F-B9FB-981328B44B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="18576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="578">
   <si>
     <t>Study_ID</t>
   </si>
@@ -268,9 +268,6 @@
     <t>NIMH SBIR R44 MH068989</t>
   </si>
   <si>
-    <t>239 randomized→161 retained (CES-D≥16 re-screen); EM imputation; differential attrition (χ²=5.30,p=.02)</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
   </si>
   <si>
     <t>PHQ-A</t>
-  </si>
-  <si>
-    <t>9 collection in total; ~20min x 9 /6 weeks</t>
   </si>
   <si>
     <t>Preprint</t>
@@ -315,12 +309,6 @@
     <t>7 levels, ~20–40 min/level, 7 weeks</t>
   </si>
   <si>
-    <t>Behavioural Science Institute, Radboud University Nijmegen</t>
-  </si>
-  <si>
-    <t>Inclusion based on sample-internal 70th percentile cutoff (RADS-2≥59) rather than published clinical cutoff (≥76); baseline M=62.61, subclinical range; flagged for sensitivity analysis</t>
-  </si>
-  <si>
     <t>iDove</t>
   </si>
   <si>
@@ -361,9 +349,6 @@
   </si>
   <si>
     <t xml:space="preserve"> MFQ ≥ 20（validation research proposes ≥20 indicates any depressive disorder）; aged 12–18; referred for low mood/depression via primary mental health worker; excluding psychosis and active suicidality</t>
-  </si>
-  <si>
-    <t>Attention control (self-help websites)</t>
   </si>
   <si>
     <t>NIHR Research for Patient Benefit (PB-PG-0609-19295)</t>
@@ -4395,6 +4380,200 @@
   </si>
   <si>
     <t>Auto + Tech</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9 collection in total; ~20min x 9 /6 weeks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Effectiveness trial.
+Targeted at AE;
+opt-in opt-out (real situation simulation);
+fully considered low motivation in help-seeking;
+alternative education time with minimal supervision;
+cared about feasibility;
+Didn't take limitation on depression severity in inclusion screening, but took those with elevated symptoms into analysis;
+allocation was finished before eliegibility assessment;
+No financial compensation
+ </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficay trial.
+High risk adolescent;
+cared about specific therapeutic effect;
+traditional recruitment procedure;
+excluded every undesirable participant before inclusion;
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficacy trial.
+Enlarging recruitment only for enough eligibilty;
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Efficacy trial.
+Although participants were recruited from community settings, the study used a small, highly selected sample, a delayed-treatment control condition, and a controlled research protocol to test whether cognitive bibliotherapy could reduce depressive symptoms under relatively favorable conditions.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial.
+Simplified recruitment by school teahcers;
+simplifeid assessment</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The author—efficacy;
+population with school conselling experience (high demand);
+at school with consellor presented;
+pilot study;
+considering they are already in school help-seeking context;
+reservation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Efficacy trial.
+At school;
+homework-oriented;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial;
+Assessment finished universally in school, but set no limit on the setting;
+adapted version of catch-it;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Inclusion based on sample-internal 70th percentile cutoff (RADS-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>59) rather than published clinical cutoff (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>76); baseline M=62.61, subclinical range; flagged for sensitivity analysis;
+all female, average age relatively small</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>239 randomized→161 retained (CES-D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>16 re-screen); EM imputation; differential attrition (χ²=5.30,p=.02);
+average age;</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Behavioural Science Institute, Radboud University Nijmegen</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial;
+Athor used the word effectiveness;
+Delivered as a computerized home-use program</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cr+ba+ps+ist+pe+hw+rp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention control (self-help websites)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Efficacy trial;
+emergency department;
+have peer violence experience;
+automated text;
+high demand(disucussion)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial.
+Recruited from CAMHS/PMHW (clinical settings);
+TAU allowed;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial.
+Recruited completely online;
+no exclusion criteria</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial.
+CAMHS;
+TAU;
+high demand;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effectiveness trial;
+Recruited in communities;
+fully considering charateristics of Inuit teenagers;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Author-efficacy trial.
+Live experience involvement;
+recruited online;
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Efficacy_or_effectiveness</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4896,24 +5075,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999"/>
   <cols>
     <col min="1" max="11" width="16" style="2" customWidth="1"/>
     <col min="12" max="12" width="30" style="2" customWidth="1"/>
     <col min="13" max="13" width="16" style="2" customWidth="1"/>
     <col min="14" max="14" width="18.44140625" style="2" customWidth="1"/>
-    <col min="15" max="16" width="16" style="2" customWidth="1"/>
-    <col min="17" max="20" width="25" style="2" customWidth="1"/>
-    <col min="21" max="28" width="16" style="2" customWidth="1"/>
-    <col min="29" max="29" width="30" style="2" customWidth="1"/>
-    <col min="30" max="30" width="8.88671875" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="8.88671875" style="2"/>
+    <col min="15" max="17" width="16" style="2" customWidth="1"/>
+    <col min="18" max="21" width="25" style="2" customWidth="1"/>
+    <col min="22" max="29" width="16" style="2" customWidth="1"/>
+    <col min="30" max="30" width="30" style="2" customWidth="1"/>
+    <col min="31" max="31" width="8.88671875" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30" ht="20.399999999999999">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4961,46 +5140,49 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>303</v>
+      <c r="S1" s="17" t="s">
+        <v>285</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="61.2" customHeight="1">
+    <row r="2" spans="1:30" ht="61.2" customHeight="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -5041,60 +5223,63 @@
         <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S2" s="2">
+      <c r="T2" s="2">
         <v>0</v>
       </c>
-      <c r="T2" s="2">
+      <c r="U2" s="2">
         <v>4</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="W2" s="2">
+      <c r="X2" s="2">
         <v>3</v>
       </c>
-      <c r="X2" s="2">
+      <c r="Y2" s="2">
         <v>1</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Z2" s="2">
         <v>0</v>
       </c>
-      <c r="Z2" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="AA2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="91.8" customHeight="1">
+    <row r="3" spans="1:30" ht="91.8" customHeight="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -5118,40 +5303,40 @@
         <v>56</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="S3" s="2">
+        <v>290</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="R3" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="T3" s="2">
         <v>0</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="2">
         <v>6</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="W3" s="2">
-        <v>1</v>
       </c>
       <c r="X3" s="2">
         <v>1</v>
@@ -5159,31 +5344,34 @@
       <c r="Y3" s="2">
         <v>1</v>
       </c>
-      <c r="Z3" s="2" t="s">
-        <v>298</v>
+      <c r="Z3" s="2">
+        <v>1</v>
       </c>
       <c r="AA3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AC3" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="40.799999999999997" customHeight="1">
+      <c r="AD3" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="40.799999999999997" customHeight="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C4" s="2">
         <v>2023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>45</v>
@@ -5198,46 +5386,46 @@
         <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>1</v>
       </c>
-      <c r="T4" s="2">
+      <c r="U4" s="2">
         <v>7</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="W4" s="2">
-        <v>1</v>
       </c>
       <c r="X4" s="2">
         <v>1</v>
@@ -5245,25 +5433,28 @@
       <c r="Y4" s="2">
         <v>1</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="Z4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AC4" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="61.2" customHeight="1">
+      <c r="AD4" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="61.2" customHeight="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C5" s="2">
         <v>2012</v>
@@ -5287,43 +5478,43 @@
         <v>14.9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>1</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>7</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="W5" s="2">
-        <v>1</v>
       </c>
       <c r="X5" s="2">
         <v>1</v>
@@ -5331,20 +5522,23 @@
       <c r="Y5" s="2">
         <v>1</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="Z5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA5" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="AB5" s="2" t="s">
-        <v>295</v>
+        <v>420</v>
       </c>
       <c r="AC5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD5" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="71.400000000000006" customHeight="1">
+    <row r="6" spans="1:30" ht="71.400000000000006" customHeight="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -5379,37 +5573,37 @@
         <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="S6" s="2">
+        <v>564</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="T6" s="2">
         <v>1</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>3</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="W6" s="2">
-        <v>1</v>
       </c>
       <c r="X6" s="2">
         <v>1</v>
@@ -5417,25 +5611,28 @@
       <c r="Y6" s="2">
         <v>1</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="Z6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AA6" s="2" t="s">
+      <c r="AB6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AC6" s="2" t="s">
+      <c r="AD6" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="64.8" customHeight="1">
+    <row r="7" spans="1:30" ht="64.8" customHeight="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C7" s="2">
         <v>2011</v>
@@ -5462,16 +5659,16 @@
         <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>73</v>
@@ -5480,22 +5677,22 @@
         <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="S7" s="2">
+        <v>559</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="T7" s="2">
         <v>0</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>4</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="W7" s="2">
-        <v>1</v>
       </c>
       <c r="X7" s="2">
         <v>1</v>
@@ -5503,34 +5700,37 @@
       <c r="Y7" s="2">
         <v>1</v>
       </c>
-      <c r="Z7" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="AA7" s="2" t="s">
+      <c r="Z7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="51" customHeight="1">
+      <c r="AD7" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="51" customHeight="1">
       <c r="A8" s="2">
         <v>8</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C8" s="2">
         <v>2020</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F8" s="2">
         <v>98</v>
@@ -5539,7 +5739,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I8" s="2">
         <v>14.82</v>
@@ -5548,75 +5748,78 @@
         <v>86.5</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="N8" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="O8" s="16" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S8" s="2">
+        <v>573</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T8" s="2">
         <v>0</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>3</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="W8" s="2">
+      <c r="X8" s="2">
         <v>2</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
       </c>
       <c r="Y8" s="2">
         <v>0</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB8" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="AC8" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="105.6" customHeight="1">
+        <v>81</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="105.6" customHeight="1">
       <c r="A9" s="2">
         <v>9</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C9" s="2">
         <v>2025</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" s="2">
         <v>195</v>
@@ -5634,40 +5837,40 @@
         <v>74.2</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="S9" s="2">
+        <v>555</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="T9" s="2">
         <v>0</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>7</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="W9" s="2">
-        <v>1</v>
       </c>
       <c r="X9" s="2">
         <v>1</v>
@@ -5675,28 +5878,31 @@
       <c r="Y9" s="2">
         <v>1</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="Z9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AA9" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="AB9" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="187.2" customHeight="1">
+        <v>84</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="187.2" customHeight="1">
       <c r="A10" s="2">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C10" s="2">
         <v>2016</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>45</v>
@@ -5708,7 +5914,7 @@
         <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2">
         <v>13.35</v>
@@ -5720,7 +5926,7 @@
         <v>41</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>56</v>
@@ -5729,28 +5935,28 @@
         <v>57</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S10" s="2">
+        <v>568</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T10" s="2">
         <v>1</v>
       </c>
-      <c r="T10" s="2">
+      <c r="U10" s="2">
         <v>7</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="W10" s="2">
-        <v>1</v>
       </c>
       <c r="X10" s="2">
         <v>1</v>
@@ -5758,34 +5964,37 @@
       <c r="Y10" s="2">
         <v>1</v>
       </c>
-      <c r="Z10" s="2" t="s">
-        <v>297</v>
+      <c r="Z10" s="2">
+        <v>1</v>
       </c>
       <c r="AA10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB10" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="AC10" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="81.599999999999994" customHeight="1">
+        <v>567</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="81.599999999999994" customHeight="1">
       <c r="A11" s="2">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C11" s="2">
         <v>2018</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F11" s="2">
         <v>58</v>
@@ -5794,84 +6003,87 @@
         <v>58</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J11" s="2">
         <v>58.6</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="S11" s="2">
+        <v>571</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T11" s="2">
         <v>0</v>
       </c>
-      <c r="T11" s="2">
+      <c r="U11" s="2">
         <v>3</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="W11" s="2">
-        <v>1</v>
+      <c r="W11" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="X11" s="2">
         <v>1</v>
       </c>
       <c r="Y11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="2">
         <v>0</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="AA11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB11" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="AC11" s="2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" ht="91.8" customHeight="1">
+        <v>94</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="91.8" customHeight="1">
       <c r="A12" s="2">
         <v>12</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C12" s="2">
         <v>2015</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F12" s="2">
         <v>55</v>
@@ -5880,49 +6092,49 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="S12" s="2">
+        <v>563</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="T12" s="2">
         <v>0</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>7</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="W12" s="2">
-        <v>1</v>
       </c>
       <c r="X12" s="2">
         <v>1</v>
@@ -5930,25 +6142,28 @@
       <c r="Y12" s="2">
         <v>1</v>
       </c>
-      <c r="Z12" s="2" t="s">
-        <v>298</v>
+      <c r="Z12" s="2">
+        <v>1</v>
       </c>
       <c r="AA12" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB12" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="AC12" s="2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="105.6" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="105.6" customHeight="1">
       <c r="A13" s="2">
         <v>13</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C13" s="2">
         <v>2014</v>
@@ -5957,7 +6172,7 @@
         <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F13" s="2">
         <v>17</v>
@@ -5975,43 +6190,43 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="R13" s="2">
+        <v>562</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="S13" s="2">
         <v>21</v>
       </c>
-      <c r="S13" s="2">
+      <c r="T13" s="2">
         <v>0</v>
       </c>
-      <c r="T13" s="2">
+      <c r="U13" s="2">
         <v>6</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="W13" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="W13" s="2">
-        <v>1</v>
       </c>
       <c r="X13" s="2">
         <v>1</v>
@@ -6019,25 +6234,28 @@
       <c r="Y13" s="2">
         <v>1</v>
       </c>
-      <c r="Z13" s="2" t="s">
-        <v>298</v>
+      <c r="Z13" s="2">
+        <v>1</v>
       </c>
       <c r="AA13" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AB13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB13" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="AC13" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="153" customHeight="1">
+        <v>290</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="153" customHeight="1">
       <c r="A14" s="2">
         <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C14" s="2">
         <v>2020</v>
@@ -6046,7 +6264,7 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F14" s="2">
         <v>70</v>
@@ -6055,7 +6273,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -6064,69 +6282,72 @@
         <v>64</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>101</v>
+        <v>569</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>107</v>
+        <v>570</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="R14" s="2">
+        <v>572</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="S14" s="2">
         <v>45</v>
       </c>
-      <c r="S14" s="2">
+      <c r="T14" s="2">
         <v>0</v>
       </c>
-      <c r="T14" s="2">
+      <c r="U14" s="2">
         <v>7</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V14" s="2" t="s">
+      <c r="W14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="W14" s="2">
+      <c r="X14" s="2">
         <v>3</v>
-      </c>
-      <c r="X14" s="2">
-        <v>1</v>
       </c>
       <c r="Y14" s="2">
         <v>1</v>
       </c>
-      <c r="Z14" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA14" s="2" t="s">
+      <c r="Z14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB14" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="AC14" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="295.8">
+        <v>103</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="295.8">
       <c r="A15" s="2">
         <v>15</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -6135,7 +6356,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F15" s="2">
         <v>128</v>
@@ -6144,7 +6365,7 @@
         <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2">
         <v>15.5</v>
@@ -6153,16 +6374,16 @@
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>73</v>
@@ -6171,25 +6392,25 @@
         <v>49</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>477</v>
+        <v>561</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="S15" s="2">
+        <v>472</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="T15" s="2">
         <v>1</v>
       </c>
-      <c r="T15" s="2">
+      <c r="U15" s="2">
         <v>6</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="W15" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="W15" s="2">
-        <v>1</v>
       </c>
       <c r="X15" s="2">
         <v>1</v>
@@ -6197,34 +6418,37 @@
       <c r="Y15" s="2">
         <v>1</v>
       </c>
-      <c r="Z15" s="2" t="s">
-        <v>297</v>
+      <c r="Z15" s="2">
+        <v>1</v>
       </c>
       <c r="AA15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="AB15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AB15" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="AC15" s="2" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="102">
+        <v>107</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="153">
       <c r="A16" s="2">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C16" s="2">
         <v>1998</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F16" s="2">
         <v>15</v>
@@ -6233,7 +6457,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -6242,43 +6466,43 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>470</v>
+        <v>560</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="S16" s="2">
+        <v>465</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="T16" s="2">
         <v>1</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>6</v>
       </c>
-      <c r="U16" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="V16" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="W16" s="2">
-        <v>1</v>
+        <v>418</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="X16" s="2">
         <v>1</v>
@@ -6286,17 +6510,20 @@
       <c r="Y16" s="2">
         <v>1</v>
       </c>
-      <c r="Z16" s="2" t="s">
-        <v>298</v>
+      <c r="Z16" s="2">
+        <v>1</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>425</v>
+        <v>293</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>295</v>
+        <v>420</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>468</v>
+        <v>290</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -6358,88 +6585,88 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="AA1" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>22</v>
@@ -6450,10 +6677,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -6480,10 +6707,10 @@
         <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="R2" s="2">
         <v>-14.34</v>
@@ -6510,7 +6737,7 @@
         <v>15</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -6518,10 +6745,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D3" s="2">
         <v>6</v>
@@ -6548,10 +6775,10 @@
         <v>30</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="R3" s="2">
         <v>-15.99</v>
@@ -6572,7 +6799,7 @@
         <v>-9.26</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -6580,10 +6807,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -6622,10 +6849,10 @@
         <v>42</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC4" s="2">
         <v>4</v>
@@ -6634,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -6642,10 +6869,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D5" s="2">
         <v>6</v>
@@ -6684,13 +6911,13 @@
         <v>42</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -6698,10 +6925,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D6" s="2">
         <v>12</v>
@@ -6740,13 +6967,13 @@
         <v>42</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -6754,10 +6981,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D7" s="2">
         <v>24</v>
@@ -6796,13 +7023,13 @@
         <v>42</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -6810,10 +7037,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -6852,10 +7079,10 @@
         <v>48</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC8" s="2">
         <v>7</v>
@@ -6864,7 +7091,7 @@
         <v>9</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -6872,10 +7099,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D9" s="2">
         <v>1.5</v>
@@ -6902,10 +7129,10 @@
         <v>56</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="R9" s="2">
         <v>-18.600000000000001</v>
@@ -6932,7 +7159,7 @@
         <v>1</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -6940,10 +7167,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -6982,10 +7209,10 @@
         <v>48</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC10" s="2">
         <v>7</v>
@@ -6994,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -7002,10 +7229,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D11" s="2">
         <v>12</v>
@@ -7044,13 +7271,13 @@
         <v>48</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -7058,10 +7285,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D12" s="2">
         <v>1.5</v>
@@ -7100,10 +7327,10 @@
         <v>72</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC12" s="2">
         <v>15</v>
@@ -7112,7 +7339,7 @@
         <v>8</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -7120,10 +7347,10 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D13" s="2">
         <v>6</v>
@@ -7162,13 +7389,13 @@
         <v>72</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="30.6" customHeight="1">
@@ -7176,10 +7403,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -7215,13 +7442,13 @@
         <v>7.2</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC14" s="2">
         <v>17</v>
@@ -7230,7 +7457,7 @@
         <v>13</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="30.6" customHeight="1">
@@ -7238,10 +7465,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D15" s="2">
         <v>1.5</v>
@@ -7277,13 +7504,13 @@
         <v>27</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="X15" s="2">
         <v>-0.56999999999999995</v>
@@ -7301,7 +7528,7 @@
         <v>36</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="30.6" customHeight="1">
@@ -7309,10 +7536,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D16" s="2">
         <v>4</v>
@@ -7348,13 +7575,13 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="X16" s="2">
         <v>-0.45</v>
@@ -7366,7 +7593,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:31">
@@ -7374,10 +7601,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -7413,13 +7640,13 @@
         <v>12.56</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC17" s="2">
         <v>4</v>
@@ -7428,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:31">
@@ -7436,10 +7663,10 @@
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D18" s="2">
         <v>3</v>
@@ -7475,16 +7702,16 @@
         <v>13.04</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE18" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:31">
@@ -7492,10 +7719,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D19" s="2">
         <v>6</v>
@@ -7531,16 +7758,16 @@
         <v>13.33</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:31">
@@ -7548,10 +7775,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D20" s="2">
         <v>12</v>
@@ -7587,16 +7814,16 @@
         <v>15.03</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:31">
@@ -7604,10 +7831,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -7643,13 +7870,13 @@
         <v>11.9</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC21" s="2">
         <v>3</v>
@@ -7663,10 +7890,10 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -7702,13 +7929,13 @@
         <v>11</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="61.2" customHeight="1">
@@ -7716,10 +7943,10 @@
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D23" s="2">
         <v>2</v>
@@ -7755,13 +7982,13 @@
         <v>13.6</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC23" s="2">
         <v>0</v>
@@ -7770,7 +7997,7 @@
         <v>2</v>
       </c>
       <c r="AE23" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:31" ht="30.6" customHeight="1">
@@ -7778,10 +8005,10 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D24" s="2">
         <v>1.5</v>
@@ -7820,10 +8047,10 @@
         <v>56</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC24" s="2">
         <v>1</v>
@@ -7837,10 +8064,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D25" s="2">
         <v>2.5</v>
@@ -7879,10 +8106,10 @@
         <v>56</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="132.6" customHeight="1">
@@ -7890,10 +8117,10 @@
         <v>14</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D26" s="2">
         <v>4</v>
@@ -7932,10 +8159,10 @@
         <v>42</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC26" s="2">
         <v>28</v>
@@ -7944,7 +8171,7 @@
         <v>25</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="132.6" customHeight="1">
@@ -7952,10 +8179,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D27" s="2">
         <v>12</v>
@@ -7994,13 +8221,13 @@
         <v>42</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE27" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="30.6">
@@ -8008,10 +8235,10 @@
         <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -8047,13 +8274,13 @@
         <v>0.41</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AC28" s="2">
         <v>6</v>
@@ -8062,7 +8289,7 @@
         <v>8</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:31" ht="30.6">
@@ -8070,10 +8297,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D29" s="2">
         <v>6</v>
@@ -8109,16 +8336,16 @@
         <v>0.33</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE29" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:31" ht="30.6">
@@ -8126,10 +8353,10 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D30" s="2">
         <v>12</v>
@@ -8165,16 +8392,16 @@
         <v>0.4</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:31" ht="30.6">
@@ -8182,10 +8409,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D31" s="2">
         <v>18</v>
@@ -8221,16 +8448,16 @@
         <v>0.35</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:31" ht="30.6">
@@ -8238,10 +8465,10 @@
         <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D32" s="2">
         <v>24</v>
@@ -8277,16 +8504,16 @@
         <v>0.43</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="51">
@@ -8294,10 +8521,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
@@ -8333,13 +8560,13 @@
         <v>5.2</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AC33" s="2">
         <v>3</v>
@@ -8348,7 +8575,7 @@
         <v>5</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -8383,46 +8610,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="234.6" customHeight="1">
@@ -8430,43 +8657,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="M2" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8474,43 +8701,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -8518,43 +8745,43 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="M4" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8562,43 +8789,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="M5" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="173.4" customHeight="1">
@@ -8606,43 +8833,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -8650,43 +8877,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -8694,43 +8921,43 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -8738,43 +8965,43 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -8782,43 +9009,43 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8826,43 +9053,43 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -8870,40 +9097,40 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -8911,40 +9138,40 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -8952,43 +9179,43 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="214.2">
@@ -8996,43 +9223,43 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="142.80000000000001">
@@ -9040,43 +9267,43 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="11:11">
@@ -9102,19 +9329,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9122,16 +9349,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9139,19 +9366,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="13.2">
@@ -9159,16 +9386,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9176,16 +9403,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9193,19 +9420,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9213,16 +9440,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9230,16 +9457,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9247,16 +9474,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9264,16 +9491,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9281,16 +9508,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9298,16 +9525,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -9315,16 +9542,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -9332,16 +9559,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -9349,16 +9576,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9366,16 +9593,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -9383,16 +9610,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -9400,16 +9627,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -9417,16 +9644,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -9434,16 +9661,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -9451,16 +9678,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -9468,16 +9695,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -9485,16 +9712,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -9502,16 +9729,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -9519,16 +9746,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -9536,16 +9763,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -9553,16 +9780,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -9570,16 +9797,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30.6">
@@ -9587,19 +9814,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -9607,114 +9834,114 @@
     </row>
     <row r="31" spans="1:6">
       <c r="D31" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="D32" s="4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="4:5">
       <c r="D35" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="4:5">
       <c r="D37" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="4:5">
       <c r="D39" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="4:5">
       <c r="D40" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41" spans="4:5">
       <c r="D41" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43" spans="4:5">
       <c r="D43" s="4" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -9734,20 +9961,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B4" s="4">
         <v>2748</v>
@@ -9755,7 +9982,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B6" s="4">
         <v>785</v>
@@ -9763,7 +9990,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B7" s="4">
         <v>1963</v>
@@ -9771,7 +9998,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B9" s="4">
         <v>1963</v>
@@ -9779,7 +10006,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B10" s="4">
         <v>1918</v>
@@ -9787,7 +10014,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B12" s="4">
         <v>46</v>
@@ -9795,7 +10022,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B13" s="4">
         <v>28</v>
@@ -9803,7 +10030,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B14" s="4">
         <v>3</v>
@@ -9811,7 +10038,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B15" s="4">
         <v>2</v>
@@ -9819,7 +10046,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B16" s="4">
         <v>3</v>
@@ -9827,7 +10054,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B17" s="4">
         <v>6</v>
@@ -9835,7 +10062,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B18" s="4">
         <v>6</v>
@@ -9843,7 +10070,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B19" s="4">
         <v>3</v>
@@ -9851,7 +10078,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="4" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -9859,7 +10086,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="4" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
@@ -9867,7 +10094,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -9875,7 +10102,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="4" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -9883,7 +10110,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -9891,7 +10118,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -9899,7 +10126,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="15" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B26" s="4">
         <v>3</v>
@@ -9907,15 +10134,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="4" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B29" s="4">
         <v>16</v>
@@ -9923,7 +10150,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B30" s="4">
         <v>16</v>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32283\OneDrive\바탕 화면\meta-analysis\meta-analysis-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2E2893-A3CC-4B5F-B9FB-981328B44B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B5FCE3-00FF-4ECC-A034-CF2FF21A83BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="18576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15396" yWindow="0" windowWidth="15216" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study_Info" sheetId="1" r:id="rId1"/>
@@ -1566,10 +1566,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>TAU</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>WL (active monitoring)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -4574,6 +4570,10 @@
   </si>
   <si>
     <t>Efficacy_or_effectiveness</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAU with delayed access to BlueIce after 6-month assessment</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -5092,7 +5092,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="20.399999999999999">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5140,7 +5140,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>16</v>
@@ -5161,13 +5161,13 @@
         <v>18</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>19</v>
@@ -5223,16 +5223,16 @@
         <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>428</v>
+        <v>577</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>32</v>
@@ -5276,10 +5276,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -5303,16 +5303,16 @@
         <v>56</v>
       </c>
       <c r="K3" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O3" s="16" t="s">
         <v>426</v>
@@ -5321,10 +5321,10 @@
         <v>290</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="T3" s="2">
         <v>0</v>
@@ -5365,13 +5365,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C4" s="2">
         <v>2023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>45</v>
@@ -5395,22 +5395,22 @@
         <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="O4" s="16" t="s">
         <v>427</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>50</v>
@@ -5454,7 +5454,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C5" s="2">
         <v>2012</v>
@@ -5481,25 +5481,25 @@
         <v>290</v>
       </c>
       <c r="K5" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="O5" s="16" t="s">
         <v>427</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>58</v>
@@ -5573,25 +5573,25 @@
         <v>41</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="T6" s="2">
         <v>1</v>
@@ -5632,7 +5632,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C7" s="2">
         <v>2011</v>
@@ -5659,16 +5659,16 @@
         <v>56</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>73</v>
@@ -5677,10 +5677,10 @@
         <v>74</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
@@ -5713,7 +5713,7 @@
         <v>75</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="51" customHeight="1">
@@ -5721,7 +5721,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C8" s="2">
         <v>2020</v>
@@ -5739,7 +5739,7 @@
         <v>95</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I8" s="2">
         <v>14.82</v>
@@ -5751,13 +5751,13 @@
         <v>78</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="O8" s="16" t="s">
         <v>427</v>
@@ -5766,7 +5766,7 @@
         <v>74</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>80</v>
@@ -5802,7 +5802,7 @@
         <v>81</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="105.6" customHeight="1">
@@ -5810,7 +5810,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C9" s="2">
         <v>2025</v>
@@ -5837,28 +5837,28 @@
         <v>74.2</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L9" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="16" t="s">
         <v>510</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>511</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="P9" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="T9" s="2">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C10" s="2">
         <v>2016</v>
@@ -5926,7 +5926,7 @@
         <v>41</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>56</v>
@@ -5935,13 +5935,13 @@
         <v>57</v>
       </c>
       <c r="O10" s="16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P10" s="16" t="s">
         <v>417</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>88</v>
@@ -5974,10 +5974,10 @@
         <v>35</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="81.599999999999994" customHeight="1">
@@ -5985,7 +5985,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C11" s="2">
         <v>2018</v>
@@ -6015,22 +6015,22 @@
         <v>91</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="O11" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="Q11" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>92</v>
@@ -6066,7 +6066,7 @@
         <v>94</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="91.8" customHeight="1">
@@ -6074,7 +6074,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C12" s="2">
         <v>2015</v>
@@ -6092,7 +6092,7 @@
         <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>290</v>
@@ -6104,7 +6104,7 @@
         <v>41</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>96</v>
@@ -6119,10 +6119,10 @@
         <v>295</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="T12" s="2">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>98</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="105.6" customHeight="1">
@@ -6190,28 +6190,28 @@
         <v>41</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S13" s="2">
         <v>21</v>
@@ -6247,7 +6247,7 @@
         <v>290</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="153" customHeight="1">
@@ -6273,7 +6273,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I14" s="2">
         <v>15</v>
@@ -6291,19 +6291,19 @@
         <v>30</v>
       </c>
       <c r="N14" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>31</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="S14" s="2">
         <v>45</v>
@@ -6339,7 +6339,7 @@
         <v>103</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="295.8">
@@ -6347,7 +6347,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C15" s="2">
         <v>2015</v>
@@ -6377,13 +6377,13 @@
         <v>105</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>106</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>73</v>
@@ -6392,10 +6392,10 @@
         <v>49</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>290</v>
@@ -6431,7 +6431,7 @@
         <v>107</v>
       </c>
       <c r="AD15" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="153">
@@ -6457,7 +6457,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I16" s="2">
         <v>15.89</v>
@@ -6466,16 +6466,16 @@
         <v>63.6</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>415</v>
       </c>
       <c r="N16" s="18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O16" s="16" t="s">
         <v>416</v>
@@ -6484,10 +6484,10 @@
         <v>417</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>290</v>
@@ -6523,7 +6523,7 @@
         <v>290</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="14:14">
@@ -6861,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -6917,7 +6917,7 @@
         <v>130</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -7029,7 +7029,7 @@
         <v>130</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="20.399999999999999" customHeight="1">
@@ -7285,7 +7285,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>124</v>
@@ -7347,7 +7347,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>127</v>
@@ -8067,7 +8067,7 @@
         <v>155</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D25" s="2">
         <v>2.5</v>
@@ -8235,7 +8235,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>124</v>
@@ -8297,7 +8297,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>127</v>
@@ -8610,7 +8610,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="40.799999999999997" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>163</v>
@@ -8646,7 +8646,7 @@
         <v>173</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>174</v>
@@ -8666,7 +8666,7 @@
         <v>177</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>178</v>
@@ -8678,10 +8678,10 @@
         <v>179</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>176</v>
@@ -8690,10 +8690,10 @@
         <v>180</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -8704,40 +8704,40 @@
         <v>181</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>182</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>176</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I3" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>183</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="112.2" customHeight="1">
@@ -8748,13 +8748,13 @@
         <v>184</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>185</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>186</v>
@@ -8766,13 +8766,13 @@
         <v>188</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>189</v>
@@ -8798,7 +8798,7 @@
         <v>192</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>193</v>
@@ -8836,13 +8836,13 @@
         <v>198</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>199</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>200</v>
@@ -8857,19 +8857,19 @@
         <v>286</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>176</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>286</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="173.4" customHeight="1">
@@ -8877,43 +8877,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>202</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>203</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>204</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>205</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" customHeight="1">
@@ -8924,13 +8924,13 @@
         <v>206</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>207</v>
@@ -8942,22 +8942,22 @@
         <v>208</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>176</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="132.6" customHeight="1">
@@ -8974,19 +8974,19 @@
         <v>210</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>211</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>212</v>
@@ -8998,10 +8998,10 @@
         <v>213</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" customHeight="1">
@@ -9012,28 +9012,28 @@
         <v>214</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>215</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>286</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>176</v>
@@ -9042,10 +9042,10 @@
         <v>216</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="163.19999999999999" customHeight="1">
@@ -9062,16 +9062,16 @@
         <v>218</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>176</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>176</v>
@@ -9080,16 +9080,16 @@
         <v>219</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>220</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="173.4" customHeight="1">
@@ -9106,10 +9106,10 @@
         <v>222</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>176</v>
@@ -9121,16 +9121,16 @@
         <v>176</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>224</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="91.8" customHeight="1">
@@ -9144,13 +9144,13 @@
         <v>176</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>176</v>
@@ -9168,10 +9168,10 @@
         <v>176</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="51" customHeight="1">
@@ -9185,25 +9185,25 @@
         <v>176</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>187</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>286</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>176</v>
@@ -9215,7 +9215,7 @@
         <v>286</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="214.2">
@@ -9229,34 +9229,34 @@
         <v>176</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="K15" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>231</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>232</v>
@@ -9270,7 +9270,7 @@
         <v>423</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>424</v>
@@ -9279,31 +9279,31 @@
         <v>286</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>286</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>425</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>286</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="11:11">
@@ -9429,10 +9429,10 @@
         <v>237</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9814,19 +9814,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>434</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>435</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>384</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -10137,7 +10137,7 @@
         <v>407</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:2">
